--- a/planilhas/Planilha de Base para Cotacao.xlsx
+++ b/planilhas/Planilha de Base para Cotacao.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27029"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27126"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/0a19316afdd125d6/Documentos/GitHub/hawks-automations/planilhas/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="34" documentId="8_{B6B05E56-6ADC-4554-A921-81DFAB966C0D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{23C3C222-9546-4B10-82B8-A65D6D2EFB03}"/>
+  <xr:revisionPtr revIDLastSave="70" documentId="8_{B6B05E56-6ADC-4554-A921-81DFAB966C0D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3A4F1FFD-D5BE-4EBF-9D34-ACCAE02760C1}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="21840" windowHeight="13140" xr2:uid="{AB0A4C4E-1938-46F3-8FAE-9EC8B05F0B3E}"/>
   </bookViews>
@@ -63,7 +63,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4">
+  <fonts count="3">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -78,11 +78,6 @@
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color theme="1"/>
-      <name val="Var(--font-family-montserrat)"/>
     </font>
     <font>
       <sz val="10"/>
@@ -110,7 +105,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -119,9 +114,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -478,78 +470,81 @@
       </c>
     </row>
     <row r="2" spans="1:7">
-      <c r="A2" s="5"/>
-      <c r="C2" s="4"/>
+      <c r="A2" s="4"/>
+      <c r="G2" s="1" t="e">
+        <f>MEDIAN(C2,D2,E2,F2)*1.8</f>
+        <v>#NUM!</v>
+      </c>
     </row>
     <row r="3" spans="1:7">
-      <c r="A3" s="5"/>
+      <c r="A3" s="4"/>
       <c r="B3" s="3"/>
     </row>
     <row r="4" spans="1:7">
-      <c r="A4" s="5"/>
+      <c r="A4" s="4"/>
     </row>
     <row r="5" spans="1:7">
-      <c r="A5" s="5"/>
+      <c r="A5" s="4"/>
     </row>
     <row r="6" spans="1:7">
-      <c r="A6" s="5"/>
+      <c r="A6" s="4"/>
     </row>
     <row r="7" spans="1:7">
-      <c r="A7" s="5"/>
+      <c r="A7" s="4"/>
     </row>
     <row r="8" spans="1:7">
-      <c r="A8" s="5"/>
+      <c r="A8" s="4"/>
     </row>
     <row r="9" spans="1:7">
-      <c r="A9" s="5"/>
+      <c r="A9" s="4"/>
     </row>
     <row r="10" spans="1:7">
-      <c r="A10" s="5"/>
+      <c r="A10" s="4"/>
     </row>
     <row r="11" spans="1:7">
-      <c r="A11" s="5"/>
+      <c r="A11" s="4"/>
     </row>
     <row r="12" spans="1:7">
-      <c r="A12" s="5"/>
+      <c r="A12" s="4"/>
     </row>
     <row r="13" spans="1:7">
-      <c r="A13" s="5"/>
+      <c r="A13" s="4"/>
     </row>
     <row r="14" spans="1:7">
-      <c r="A14" s="5"/>
+      <c r="A14" s="4"/>
     </row>
     <row r="15" spans="1:7">
-      <c r="A15" s="5"/>
+      <c r="A15" s="4"/>
     </row>
     <row r="16" spans="1:7">
-      <c r="A16" s="5"/>
+      <c r="A16" s="4"/>
     </row>
     <row r="17" spans="1:1">
-      <c r="A17" s="5"/>
+      <c r="A17" s="4"/>
     </row>
     <row r="18" spans="1:1">
-      <c r="A18" s="5"/>
+      <c r="A18" s="4"/>
     </row>
     <row r="19" spans="1:1">
-      <c r="A19" s="5"/>
+      <c r="A19" s="4"/>
     </row>
     <row r="20" spans="1:1">
-      <c r="A20" s="5"/>
+      <c r="A20" s="4"/>
     </row>
     <row r="21" spans="1:1">
-      <c r="A21" s="5"/>
+      <c r="A21" s="4"/>
     </row>
     <row r="22" spans="1:1">
-      <c r="A22" s="5"/>
+      <c r="A22" s="4"/>
     </row>
     <row r="23" spans="1:1">
-      <c r="A23" s="5"/>
+      <c r="A23" s="4"/>
     </row>
     <row r="24" spans="1:1">
-      <c r="A24" s="5"/>
+      <c r="A24" s="4"/>
     </row>
     <row r="25" spans="1:1">
-      <c r="A25" s="5"/>
+      <c r="A25" s="4"/>
     </row>
   </sheetData>
   <mergeCells count="8">

--- a/planilhas/Planilha de Base para Cotacao.xlsx
+++ b/planilhas/Planilha de Base para Cotacao.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/0a19316afdd125d6/Documentos/GitHub/hawks-automations/planilhas/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="70" documentId="8_{B6B05E56-6ADC-4554-A921-81DFAB966C0D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3A4F1FFD-D5BE-4EBF-9D34-ACCAE02760C1}"/>
+  <xr:revisionPtr revIDLastSave="102" documentId="8_{B6B05E56-6ADC-4554-A921-81DFAB966C0D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6312C9EA-B1ED-4883-9FA8-8ABCD49C1767}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="21840" windowHeight="13140" xr2:uid="{AB0A4C4E-1938-46F3-8FAE-9EC8B05F0B3E}"/>
   </bookViews>
@@ -433,7 +433,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EA940922-860D-4863-B9A5-E7EE2A94C235}">
-  <dimension ref="A1:G25"/>
+  <dimension ref="A1:G433"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="17.7109375" style="1" customWidth="1"/>
@@ -546,8 +546,1237 @@
     <row r="25" spans="1:1">
       <c r="A25" s="4"/>
     </row>
+    <row r="26" spans="1:1">
+      <c r="A26" s="4"/>
+    </row>
+    <row r="27" spans="1:1">
+      <c r="A27" s="4"/>
+    </row>
+    <row r="28" spans="1:1">
+      <c r="A28" s="4"/>
+    </row>
+    <row r="29" spans="1:1">
+      <c r="A29" s="4"/>
+    </row>
+    <row r="30" spans="1:1">
+      <c r="A30" s="4"/>
+    </row>
+    <row r="31" spans="1:1">
+      <c r="A31" s="4"/>
+    </row>
+    <row r="32" spans="1:1">
+      <c r="A32" s="4"/>
+    </row>
+    <row r="33" spans="1:1">
+      <c r="A33" s="4"/>
+    </row>
+    <row r="34" spans="1:1">
+      <c r="A34" s="4"/>
+    </row>
+    <row r="35" spans="1:1">
+      <c r="A35" s="4"/>
+    </row>
+    <row r="36" spans="1:1">
+      <c r="A36" s="4"/>
+    </row>
+    <row r="37" spans="1:1">
+      <c r="A37" s="4"/>
+    </row>
+    <row r="38" spans="1:1">
+      <c r="A38" s="4"/>
+    </row>
+    <row r="39" spans="1:1">
+      <c r="A39" s="4"/>
+    </row>
+    <row r="40" spans="1:1">
+      <c r="A40" s="4"/>
+    </row>
+    <row r="41" spans="1:1">
+      <c r="A41" s="4"/>
+    </row>
+    <row r="42" spans="1:1">
+      <c r="A42" s="4"/>
+    </row>
+    <row r="43" spans="1:1">
+      <c r="A43" s="4"/>
+    </row>
+    <row r="44" spans="1:1">
+      <c r="A44" s="4"/>
+    </row>
+    <row r="45" spans="1:1">
+      <c r="A45" s="4"/>
+    </row>
+    <row r="46" spans="1:1">
+      <c r="A46" s="4"/>
+    </row>
+    <row r="47" spans="1:1">
+      <c r="A47" s="4"/>
+    </row>
+    <row r="48" spans="1:1">
+      <c r="A48" s="4"/>
+    </row>
+    <row r="49" spans="1:1">
+      <c r="A49" s="4"/>
+    </row>
+    <row r="50" spans="1:1">
+      <c r="A50" s="4"/>
+    </row>
+    <row r="51" spans="1:1">
+      <c r="A51" s="4"/>
+    </row>
+    <row r="52" spans="1:1">
+      <c r="A52" s="4"/>
+    </row>
+    <row r="53" spans="1:1">
+      <c r="A53" s="4"/>
+    </row>
+    <row r="54" spans="1:1">
+      <c r="A54" s="4"/>
+    </row>
+    <row r="55" spans="1:1">
+      <c r="A55" s="4"/>
+    </row>
+    <row r="56" spans="1:1">
+      <c r="A56" s="4"/>
+    </row>
+    <row r="57" spans="1:1">
+      <c r="A57" s="4"/>
+    </row>
+    <row r="58" spans="1:1">
+      <c r="A58" s="4"/>
+    </row>
+    <row r="59" spans="1:1">
+      <c r="A59" s="4"/>
+    </row>
+    <row r="60" spans="1:1">
+      <c r="A60" s="4"/>
+    </row>
+    <row r="61" spans="1:1">
+      <c r="A61" s="4"/>
+    </row>
+    <row r="62" spans="1:1">
+      <c r="A62" s="4"/>
+    </row>
+    <row r="63" spans="1:1">
+      <c r="A63" s="4"/>
+    </row>
+    <row r="64" spans="1:1">
+      <c r="A64" s="4"/>
+    </row>
+    <row r="65" spans="1:1">
+      <c r="A65" s="4"/>
+    </row>
+    <row r="66" spans="1:1">
+      <c r="A66" s="4"/>
+    </row>
+    <row r="67" spans="1:1">
+      <c r="A67" s="4"/>
+    </row>
+    <row r="68" spans="1:1">
+      <c r="A68" s="4"/>
+    </row>
+    <row r="69" spans="1:1">
+      <c r="A69" s="4"/>
+    </row>
+    <row r="70" spans="1:1">
+      <c r="A70" s="4"/>
+    </row>
+    <row r="71" spans="1:1">
+      <c r="A71" s="4"/>
+    </row>
+    <row r="72" spans="1:1">
+      <c r="A72" s="4"/>
+    </row>
+    <row r="73" spans="1:1">
+      <c r="A73" s="4"/>
+    </row>
+    <row r="74" spans="1:1">
+      <c r="A74" s="4"/>
+    </row>
+    <row r="75" spans="1:1">
+      <c r="A75" s="4"/>
+    </row>
+    <row r="76" spans="1:1">
+      <c r="A76" s="4"/>
+    </row>
+    <row r="77" spans="1:1">
+      <c r="A77" s="4"/>
+    </row>
+    <row r="78" spans="1:1">
+      <c r="A78" s="4"/>
+    </row>
+    <row r="79" spans="1:1">
+      <c r="A79" s="4"/>
+    </row>
+    <row r="80" spans="1:1">
+      <c r="A80" s="4"/>
+    </row>
+    <row r="81" spans="1:1">
+      <c r="A81" s="4"/>
+    </row>
+    <row r="82" spans="1:1">
+      <c r="A82" s="4"/>
+    </row>
+    <row r="83" spans="1:1">
+      <c r="A83" s="4"/>
+    </row>
+    <row r="84" spans="1:1">
+      <c r="A84" s="4"/>
+    </row>
+    <row r="85" spans="1:1">
+      <c r="A85" s="4"/>
+    </row>
+    <row r="86" spans="1:1">
+      <c r="A86" s="4"/>
+    </row>
+    <row r="87" spans="1:1">
+      <c r="A87" s="4"/>
+    </row>
+    <row r="88" spans="1:1">
+      <c r="A88" s="4"/>
+    </row>
+    <row r="89" spans="1:1">
+      <c r="A89" s="4"/>
+    </row>
+    <row r="90" spans="1:1">
+      <c r="A90" s="4"/>
+    </row>
+    <row r="91" spans="1:1">
+      <c r="A91" s="4"/>
+    </row>
+    <row r="92" spans="1:1">
+      <c r="A92" s="4"/>
+    </row>
+    <row r="93" spans="1:1">
+      <c r="A93" s="4"/>
+    </row>
+    <row r="94" spans="1:1">
+      <c r="A94" s="4"/>
+    </row>
+    <row r="95" spans="1:1">
+      <c r="A95" s="4"/>
+    </row>
+    <row r="96" spans="1:1">
+      <c r="A96" s="4"/>
+    </row>
+    <row r="97" spans="1:1">
+      <c r="A97" s="4"/>
+    </row>
+    <row r="98" spans="1:1">
+      <c r="A98" s="4"/>
+    </row>
+    <row r="99" spans="1:1">
+      <c r="A99" s="4"/>
+    </row>
+    <row r="100" spans="1:1">
+      <c r="A100" s="4"/>
+    </row>
+    <row r="101" spans="1:1">
+      <c r="A101" s="4"/>
+    </row>
+    <row r="102" spans="1:1">
+      <c r="A102" s="4"/>
+    </row>
+    <row r="103" spans="1:1">
+      <c r="A103" s="4"/>
+    </row>
+    <row r="104" spans="1:1">
+      <c r="A104" s="4"/>
+    </row>
+    <row r="105" spans="1:1">
+      <c r="A105" s="4"/>
+    </row>
+    <row r="106" spans="1:1">
+      <c r="A106" s="4"/>
+    </row>
+    <row r="107" spans="1:1">
+      <c r="A107" s="4"/>
+    </row>
+    <row r="108" spans="1:1">
+      <c r="A108" s="4"/>
+    </row>
+    <row r="109" spans="1:1">
+      <c r="A109" s="4"/>
+    </row>
+    <row r="110" spans="1:1">
+      <c r="A110" s="4"/>
+    </row>
+    <row r="111" spans="1:1">
+      <c r="A111" s="4"/>
+    </row>
+    <row r="112" spans="1:1">
+      <c r="A112" s="4"/>
+    </row>
+    <row r="113" spans="1:1">
+      <c r="A113" s="4"/>
+    </row>
+    <row r="114" spans="1:1">
+      <c r="A114" s="4"/>
+    </row>
+    <row r="115" spans="1:1">
+      <c r="A115" s="4"/>
+    </row>
+    <row r="116" spans="1:1">
+      <c r="A116" s="4"/>
+    </row>
+    <row r="117" spans="1:1">
+      <c r="A117" s="4"/>
+    </row>
+    <row r="118" spans="1:1">
+      <c r="A118" s="4"/>
+    </row>
+    <row r="119" spans="1:1">
+      <c r="A119" s="4"/>
+    </row>
+    <row r="120" spans="1:1">
+      <c r="A120" s="4"/>
+    </row>
+    <row r="121" spans="1:1">
+      <c r="A121" s="4"/>
+    </row>
+    <row r="122" spans="1:1">
+      <c r="A122" s="4"/>
+    </row>
+    <row r="123" spans="1:1">
+      <c r="A123" s="4"/>
+    </row>
+    <row r="124" spans="1:1">
+      <c r="A124" s="4"/>
+    </row>
+    <row r="125" spans="1:1">
+      <c r="A125" s="4"/>
+    </row>
+    <row r="126" spans="1:1">
+      <c r="A126" s="4"/>
+    </row>
+    <row r="127" spans="1:1">
+      <c r="A127" s="4"/>
+    </row>
+    <row r="128" spans="1:1">
+      <c r="A128" s="4"/>
+    </row>
+    <row r="129" spans="1:1">
+      <c r="A129" s="4"/>
+    </row>
+    <row r="130" spans="1:1">
+      <c r="A130" s="4"/>
+    </row>
+    <row r="131" spans="1:1">
+      <c r="A131" s="4"/>
+    </row>
+    <row r="132" spans="1:1">
+      <c r="A132" s="4"/>
+    </row>
+    <row r="133" spans="1:1">
+      <c r="A133" s="4"/>
+    </row>
+    <row r="134" spans="1:1">
+      <c r="A134" s="4"/>
+    </row>
+    <row r="135" spans="1:1">
+      <c r="A135" s="4"/>
+    </row>
+    <row r="136" spans="1:1">
+      <c r="A136" s="4"/>
+    </row>
+    <row r="137" spans="1:1">
+      <c r="A137" s="4"/>
+    </row>
+    <row r="138" spans="1:1">
+      <c r="A138" s="4"/>
+    </row>
+    <row r="139" spans="1:1">
+      <c r="A139" s="4"/>
+    </row>
+    <row r="140" spans="1:1">
+      <c r="A140" s="4"/>
+    </row>
+    <row r="141" spans="1:1">
+      <c r="A141" s="4"/>
+    </row>
+    <row r="142" spans="1:1">
+      <c r="A142" s="4"/>
+    </row>
+    <row r="143" spans="1:1">
+      <c r="A143" s="4"/>
+    </row>
+    <row r="144" spans="1:1">
+      <c r="A144" s="4"/>
+    </row>
+    <row r="145" spans="1:1">
+      <c r="A145" s="4"/>
+    </row>
+    <row r="146" spans="1:1">
+      <c r="A146" s="4"/>
+    </row>
+    <row r="147" spans="1:1">
+      <c r="A147" s="4"/>
+    </row>
+    <row r="148" spans="1:1">
+      <c r="A148" s="4"/>
+    </row>
+    <row r="149" spans="1:1">
+      <c r="A149" s="4"/>
+    </row>
+    <row r="150" spans="1:1">
+      <c r="A150" s="4"/>
+    </row>
+    <row r="151" spans="1:1">
+      <c r="A151" s="4"/>
+    </row>
+    <row r="152" spans="1:1">
+      <c r="A152" s="4"/>
+    </row>
+    <row r="153" spans="1:1">
+      <c r="A153" s="4"/>
+    </row>
+    <row r="154" spans="1:1">
+      <c r="A154" s="4"/>
+    </row>
+    <row r="155" spans="1:1">
+      <c r="A155" s="4"/>
+    </row>
+    <row r="156" spans="1:1">
+      <c r="A156" s="4"/>
+    </row>
+    <row r="157" spans="1:1">
+      <c r="A157" s="4"/>
+    </row>
+    <row r="158" spans="1:1">
+      <c r="A158" s="4"/>
+    </row>
+    <row r="159" spans="1:1">
+      <c r="A159" s="4"/>
+    </row>
+    <row r="160" spans="1:1">
+      <c r="A160" s="4"/>
+    </row>
+    <row r="161" spans="1:1">
+      <c r="A161" s="4"/>
+    </row>
+    <row r="162" spans="1:1">
+      <c r="A162" s="4"/>
+    </row>
+    <row r="163" spans="1:1">
+      <c r="A163" s="4"/>
+    </row>
+    <row r="164" spans="1:1">
+      <c r="A164" s="4"/>
+    </row>
+    <row r="165" spans="1:1">
+      <c r="A165" s="4"/>
+    </row>
+    <row r="166" spans="1:1">
+      <c r="A166" s="4"/>
+    </row>
+    <row r="167" spans="1:1">
+      <c r="A167" s="4"/>
+    </row>
+    <row r="168" spans="1:1">
+      <c r="A168" s="4"/>
+    </row>
+    <row r="169" spans="1:1">
+      <c r="A169" s="4"/>
+    </row>
+    <row r="170" spans="1:1">
+      <c r="A170" s="4"/>
+    </row>
+    <row r="171" spans="1:1">
+      <c r="A171" s="4"/>
+    </row>
+    <row r="172" spans="1:1">
+      <c r="A172" s="4"/>
+    </row>
+    <row r="173" spans="1:1">
+      <c r="A173" s="4"/>
+    </row>
+    <row r="174" spans="1:1">
+      <c r="A174" s="4"/>
+    </row>
+    <row r="175" spans="1:1">
+      <c r="A175" s="4"/>
+    </row>
+    <row r="176" spans="1:1">
+      <c r="A176" s="4"/>
+    </row>
+    <row r="177" spans="1:1">
+      <c r="A177" s="4"/>
+    </row>
+    <row r="178" spans="1:1">
+      <c r="A178" s="4"/>
+    </row>
+    <row r="179" spans="1:1">
+      <c r="A179" s="4"/>
+    </row>
+    <row r="180" spans="1:1">
+      <c r="A180" s="4"/>
+    </row>
+    <row r="181" spans="1:1">
+      <c r="A181" s="4"/>
+    </row>
+    <row r="182" spans="1:1">
+      <c r="A182" s="4"/>
+    </row>
+    <row r="183" spans="1:1">
+      <c r="A183" s="4"/>
+    </row>
+    <row r="184" spans="1:1">
+      <c r="A184" s="4"/>
+    </row>
+    <row r="185" spans="1:1">
+      <c r="A185" s="4"/>
+    </row>
+    <row r="186" spans="1:1">
+      <c r="A186" s="4"/>
+    </row>
+    <row r="187" spans="1:1">
+      <c r="A187" s="4"/>
+    </row>
+    <row r="188" spans="1:1">
+      <c r="A188" s="4"/>
+    </row>
+    <row r="189" spans="1:1">
+      <c r="A189" s="4"/>
+    </row>
+    <row r="190" spans="1:1">
+      <c r="A190" s="4"/>
+    </row>
+    <row r="191" spans="1:1">
+      <c r="A191" s="4"/>
+    </row>
+    <row r="192" spans="1:1">
+      <c r="A192" s="4"/>
+    </row>
+    <row r="193" spans="1:1">
+      <c r="A193" s="4"/>
+    </row>
+    <row r="194" spans="1:1">
+      <c r="A194" s="4"/>
+    </row>
+    <row r="195" spans="1:1">
+      <c r="A195" s="4"/>
+    </row>
+    <row r="196" spans="1:1">
+      <c r="A196" s="4"/>
+    </row>
+    <row r="197" spans="1:1">
+      <c r="A197" s="4"/>
+    </row>
+    <row r="198" spans="1:1">
+      <c r="A198" s="4"/>
+    </row>
+    <row r="199" spans="1:1">
+      <c r="A199" s="4"/>
+    </row>
+    <row r="200" spans="1:1">
+      <c r="A200" s="4"/>
+    </row>
+    <row r="201" spans="1:1">
+      <c r="A201" s="4"/>
+    </row>
+    <row r="202" spans="1:1">
+      <c r="A202" s="4"/>
+    </row>
+    <row r="203" spans="1:1">
+      <c r="A203" s="4"/>
+    </row>
+    <row r="204" spans="1:1">
+      <c r="A204" s="4"/>
+    </row>
+    <row r="205" spans="1:1">
+      <c r="A205" s="4"/>
+    </row>
+    <row r="206" spans="1:1">
+      <c r="A206" s="4"/>
+    </row>
+    <row r="207" spans="1:1">
+      <c r="A207" s="4"/>
+    </row>
+    <row r="208" spans="1:1">
+      <c r="A208" s="4"/>
+    </row>
+    <row r="209" spans="1:1">
+      <c r="A209" s="4"/>
+    </row>
+    <row r="210" spans="1:1">
+      <c r="A210" s="4"/>
+    </row>
+    <row r="211" spans="1:1">
+      <c r="A211" s="4"/>
+    </row>
+    <row r="212" spans="1:1">
+      <c r="A212" s="4"/>
+    </row>
+    <row r="213" spans="1:1">
+      <c r="A213" s="4"/>
+    </row>
+    <row r="214" spans="1:1">
+      <c r="A214" s="4"/>
+    </row>
+    <row r="215" spans="1:1">
+      <c r="A215" s="4"/>
+    </row>
+    <row r="216" spans="1:1">
+      <c r="A216" s="4"/>
+    </row>
+    <row r="217" spans="1:1">
+      <c r="A217" s="4"/>
+    </row>
+    <row r="218" spans="1:1">
+      <c r="A218" s="4"/>
+    </row>
+    <row r="219" spans="1:1">
+      <c r="A219" s="4"/>
+    </row>
+    <row r="220" spans="1:1">
+      <c r="A220" s="4"/>
+    </row>
+    <row r="221" spans="1:1">
+      <c r="A221" s="4"/>
+    </row>
+    <row r="222" spans="1:1">
+      <c r="A222" s="4"/>
+    </row>
+    <row r="223" spans="1:1">
+      <c r="A223" s="4"/>
+    </row>
+    <row r="224" spans="1:1">
+      <c r="A224" s="4"/>
+    </row>
+    <row r="225" spans="1:1">
+      <c r="A225" s="4"/>
+    </row>
+    <row r="226" spans="1:1">
+      <c r="A226" s="4"/>
+    </row>
+    <row r="227" spans="1:1">
+      <c r="A227" s="4"/>
+    </row>
+    <row r="228" spans="1:1">
+      <c r="A228" s="4"/>
+    </row>
+    <row r="229" spans="1:1">
+      <c r="A229" s="4"/>
+    </row>
+    <row r="230" spans="1:1">
+      <c r="A230" s="4"/>
+    </row>
+    <row r="231" spans="1:1">
+      <c r="A231" s="4"/>
+    </row>
+    <row r="232" spans="1:1">
+      <c r="A232" s="4"/>
+    </row>
+    <row r="233" spans="1:1">
+      <c r="A233" s="4"/>
+    </row>
+    <row r="234" spans="1:1">
+      <c r="A234" s="4"/>
+    </row>
+    <row r="235" spans="1:1">
+      <c r="A235" s="4"/>
+    </row>
+    <row r="236" spans="1:1">
+      <c r="A236" s="4"/>
+    </row>
+    <row r="237" spans="1:1">
+      <c r="A237" s="4"/>
+    </row>
+    <row r="238" spans="1:1">
+      <c r="A238" s="4"/>
+    </row>
+    <row r="239" spans="1:1">
+      <c r="A239" s="4"/>
+    </row>
+    <row r="240" spans="1:1">
+      <c r="A240" s="4"/>
+    </row>
+    <row r="241" spans="1:1">
+      <c r="A241" s="4"/>
+    </row>
+    <row r="242" spans="1:1">
+      <c r="A242" s="4"/>
+    </row>
+    <row r="243" spans="1:1">
+      <c r="A243" s="4"/>
+    </row>
+    <row r="244" spans="1:1">
+      <c r="A244" s="4"/>
+    </row>
+    <row r="245" spans="1:1">
+      <c r="A245" s="4"/>
+    </row>
+    <row r="246" spans="1:1">
+      <c r="A246" s="4"/>
+    </row>
+    <row r="247" spans="1:1">
+      <c r="A247" s="4"/>
+    </row>
+    <row r="248" spans="1:1">
+      <c r="A248" s="4"/>
+    </row>
+    <row r="249" spans="1:1">
+      <c r="A249" s="4"/>
+    </row>
+    <row r="250" spans="1:1">
+      <c r="A250" s="4"/>
+    </row>
+    <row r="251" spans="1:1">
+      <c r="A251" s="4"/>
+    </row>
+    <row r="252" spans="1:1">
+      <c r="A252" s="4"/>
+    </row>
+    <row r="253" spans="1:1">
+      <c r="A253" s="4"/>
+    </row>
+    <row r="254" spans="1:1">
+      <c r="A254" s="4"/>
+    </row>
+    <row r="255" spans="1:1">
+      <c r="A255" s="4"/>
+    </row>
+    <row r="256" spans="1:1">
+      <c r="A256" s="4"/>
+    </row>
+    <row r="257" spans="1:1">
+      <c r="A257" s="4"/>
+    </row>
+    <row r="258" spans="1:1">
+      <c r="A258" s="4"/>
+    </row>
+    <row r="259" spans="1:1">
+      <c r="A259" s="4"/>
+    </row>
+    <row r="260" spans="1:1">
+      <c r="A260" s="4"/>
+    </row>
+    <row r="261" spans="1:1">
+      <c r="A261" s="4"/>
+    </row>
+    <row r="262" spans="1:1">
+      <c r="A262" s="4"/>
+    </row>
+    <row r="263" spans="1:1">
+      <c r="A263" s="4"/>
+    </row>
+    <row r="264" spans="1:1">
+      <c r="A264" s="4"/>
+    </row>
+    <row r="265" spans="1:1">
+      <c r="A265" s="4"/>
+    </row>
+    <row r="266" spans="1:1">
+      <c r="A266" s="4"/>
+    </row>
+    <row r="267" spans="1:1">
+      <c r="A267" s="4"/>
+    </row>
+    <row r="268" spans="1:1">
+      <c r="A268" s="4"/>
+    </row>
+    <row r="269" spans="1:1">
+      <c r="A269" s="4"/>
+    </row>
+    <row r="270" spans="1:1">
+      <c r="A270" s="4"/>
+    </row>
+    <row r="271" spans="1:1">
+      <c r="A271" s="4"/>
+    </row>
+    <row r="272" spans="1:1">
+      <c r="A272" s="4"/>
+    </row>
+    <row r="273" spans="1:1">
+      <c r="A273" s="4"/>
+    </row>
+    <row r="274" spans="1:1">
+      <c r="A274" s="4"/>
+    </row>
+    <row r="275" spans="1:1">
+      <c r="A275" s="4"/>
+    </row>
+    <row r="276" spans="1:1">
+      <c r="A276" s="4"/>
+    </row>
+    <row r="277" spans="1:1">
+      <c r="A277" s="4"/>
+    </row>
+    <row r="278" spans="1:1">
+      <c r="A278" s="4"/>
+    </row>
+    <row r="279" spans="1:1">
+      <c r="A279" s="4"/>
+    </row>
+    <row r="280" spans="1:1">
+      <c r="A280" s="4"/>
+    </row>
+    <row r="281" spans="1:1">
+      <c r="A281" s="4"/>
+    </row>
+    <row r="282" spans="1:1">
+      <c r="A282" s="4"/>
+    </row>
+    <row r="283" spans="1:1">
+      <c r="A283" s="4"/>
+    </row>
+    <row r="284" spans="1:1">
+      <c r="A284" s="4"/>
+    </row>
+    <row r="285" spans="1:1">
+      <c r="A285" s="4"/>
+    </row>
+    <row r="286" spans="1:1">
+      <c r="A286" s="4"/>
+    </row>
+    <row r="287" spans="1:1">
+      <c r="A287" s="4"/>
+    </row>
+    <row r="288" spans="1:1">
+      <c r="A288" s="4"/>
+    </row>
+    <row r="289" spans="1:1">
+      <c r="A289" s="4"/>
+    </row>
+    <row r="290" spans="1:1">
+      <c r="A290" s="4"/>
+    </row>
+    <row r="291" spans="1:1">
+      <c r="A291" s="4"/>
+    </row>
+    <row r="292" spans="1:1">
+      <c r="A292" s="4"/>
+    </row>
+    <row r="293" spans="1:1">
+      <c r="A293" s="4"/>
+    </row>
+    <row r="294" spans="1:1">
+      <c r="A294" s="4"/>
+    </row>
+    <row r="295" spans="1:1">
+      <c r="A295" s="4"/>
+    </row>
+    <row r="296" spans="1:1">
+      <c r="A296" s="4"/>
+    </row>
+    <row r="297" spans="1:1">
+      <c r="A297" s="4"/>
+    </row>
+    <row r="298" spans="1:1">
+      <c r="A298" s="4"/>
+    </row>
+    <row r="299" spans="1:1">
+      <c r="A299" s="4"/>
+    </row>
+    <row r="300" spans="1:1">
+      <c r="A300" s="4"/>
+    </row>
+    <row r="301" spans="1:1">
+      <c r="A301" s="4"/>
+    </row>
+    <row r="302" spans="1:1">
+      <c r="A302" s="4"/>
+    </row>
+    <row r="303" spans="1:1">
+      <c r="A303" s="4"/>
+    </row>
+    <row r="304" spans="1:1">
+      <c r="A304" s="4"/>
+    </row>
+    <row r="305" spans="1:1">
+      <c r="A305" s="4"/>
+    </row>
+    <row r="306" spans="1:1">
+      <c r="A306" s="4"/>
+    </row>
+    <row r="307" spans="1:1">
+      <c r="A307" s="4"/>
+    </row>
+    <row r="308" spans="1:1">
+      <c r="A308" s="4"/>
+    </row>
+    <row r="309" spans="1:1">
+      <c r="A309" s="4"/>
+    </row>
+    <row r="310" spans="1:1">
+      <c r="A310" s="4"/>
+    </row>
+    <row r="311" spans="1:1">
+      <c r="A311" s="4"/>
+    </row>
+    <row r="312" spans="1:1">
+      <c r="A312" s="4"/>
+    </row>
+    <row r="313" spans="1:1">
+      <c r="A313" s="4"/>
+    </row>
+    <row r="314" spans="1:1">
+      <c r="A314" s="4"/>
+    </row>
+    <row r="315" spans="1:1">
+      <c r="A315" s="4"/>
+    </row>
+    <row r="316" spans="1:1">
+      <c r="A316" s="4"/>
+    </row>
+    <row r="317" spans="1:1">
+      <c r="A317" s="4"/>
+    </row>
+    <row r="318" spans="1:1">
+      <c r="A318" s="4"/>
+    </row>
+    <row r="319" spans="1:1">
+      <c r="A319" s="4"/>
+    </row>
+    <row r="320" spans="1:1">
+      <c r="A320" s="4"/>
+    </row>
+    <row r="321" spans="1:1">
+      <c r="A321" s="4"/>
+    </row>
+    <row r="322" spans="1:1">
+      <c r="A322" s="4"/>
+    </row>
+    <row r="323" spans="1:1">
+      <c r="A323" s="4"/>
+    </row>
+    <row r="324" spans="1:1">
+      <c r="A324" s="4"/>
+    </row>
+    <row r="325" spans="1:1">
+      <c r="A325" s="4"/>
+    </row>
+    <row r="326" spans="1:1">
+      <c r="A326" s="4"/>
+    </row>
+    <row r="327" spans="1:1">
+      <c r="A327" s="4"/>
+    </row>
+    <row r="328" spans="1:1">
+      <c r="A328" s="4"/>
+    </row>
+    <row r="329" spans="1:1">
+      <c r="A329" s="4"/>
+    </row>
+    <row r="330" spans="1:1">
+      <c r="A330" s="4"/>
+    </row>
+    <row r="331" spans="1:1">
+      <c r="A331" s="4"/>
+    </row>
+    <row r="332" spans="1:1">
+      <c r="A332" s="4"/>
+    </row>
+    <row r="333" spans="1:1">
+      <c r="A333" s="4"/>
+    </row>
+    <row r="334" spans="1:1">
+      <c r="A334" s="4"/>
+    </row>
+    <row r="335" spans="1:1">
+      <c r="A335" s="4"/>
+    </row>
+    <row r="336" spans="1:1">
+      <c r="A336" s="4"/>
+    </row>
+    <row r="337" spans="1:1">
+      <c r="A337" s="4"/>
+    </row>
+    <row r="338" spans="1:1">
+      <c r="A338" s="4"/>
+    </row>
+    <row r="339" spans="1:1">
+      <c r="A339" s="4"/>
+    </row>
+    <row r="340" spans="1:1">
+      <c r="A340" s="4"/>
+    </row>
+    <row r="341" spans="1:1">
+      <c r="A341" s="4"/>
+    </row>
+    <row r="342" spans="1:1">
+      <c r="A342" s="4"/>
+    </row>
+    <row r="343" spans="1:1">
+      <c r="A343" s="4"/>
+    </row>
+    <row r="344" spans="1:1">
+      <c r="A344" s="4"/>
+    </row>
+    <row r="345" spans="1:1">
+      <c r="A345" s="4"/>
+    </row>
+    <row r="346" spans="1:1">
+      <c r="A346" s="4"/>
+    </row>
+    <row r="347" spans="1:1">
+      <c r="A347" s="4"/>
+    </row>
+    <row r="348" spans="1:1">
+      <c r="A348" s="4"/>
+    </row>
+    <row r="349" spans="1:1">
+      <c r="A349" s="4"/>
+    </row>
+    <row r="350" spans="1:1">
+      <c r="A350" s="4"/>
+    </row>
+    <row r="351" spans="1:1">
+      <c r="A351" s="4"/>
+    </row>
+    <row r="352" spans="1:1">
+      <c r="A352" s="4"/>
+    </row>
+    <row r="353" spans="1:1">
+      <c r="A353" s="4"/>
+    </row>
+    <row r="354" spans="1:1">
+      <c r="A354" s="4"/>
+    </row>
+    <row r="355" spans="1:1">
+      <c r="A355" s="4"/>
+    </row>
+    <row r="356" spans="1:1">
+      <c r="A356" s="4"/>
+    </row>
+    <row r="357" spans="1:1">
+      <c r="A357" s="4"/>
+    </row>
+    <row r="358" spans="1:1">
+      <c r="A358" s="4"/>
+    </row>
+    <row r="359" spans="1:1">
+      <c r="A359" s="4"/>
+    </row>
+    <row r="360" spans="1:1">
+      <c r="A360" s="4"/>
+    </row>
+    <row r="361" spans="1:1">
+      <c r="A361" s="4"/>
+    </row>
+    <row r="362" spans="1:1">
+      <c r="A362" s="4"/>
+    </row>
+    <row r="363" spans="1:1">
+      <c r="A363" s="4"/>
+    </row>
+    <row r="364" spans="1:1">
+      <c r="A364" s="4"/>
+    </row>
+    <row r="365" spans="1:1">
+      <c r="A365" s="4"/>
+    </row>
+    <row r="366" spans="1:1">
+      <c r="A366" s="4"/>
+    </row>
+    <row r="367" spans="1:1">
+      <c r="A367" s="4"/>
+    </row>
+    <row r="368" spans="1:1">
+      <c r="A368" s="4"/>
+    </row>
+    <row r="369" spans="1:1">
+      <c r="A369" s="4"/>
+    </row>
+    <row r="370" spans="1:1">
+      <c r="A370" s="4"/>
+    </row>
+    <row r="371" spans="1:1">
+      <c r="A371" s="4"/>
+    </row>
+    <row r="372" spans="1:1">
+      <c r="A372" s="4"/>
+    </row>
+    <row r="373" spans="1:1">
+      <c r="A373" s="4"/>
+    </row>
+    <row r="374" spans="1:1">
+      <c r="A374" s="4"/>
+    </row>
+    <row r="375" spans="1:1">
+      <c r="A375" s="4"/>
+    </row>
+    <row r="376" spans="1:1">
+      <c r="A376" s="4"/>
+    </row>
+    <row r="377" spans="1:1">
+      <c r="A377" s="4"/>
+    </row>
+    <row r="378" spans="1:1">
+      <c r="A378" s="4"/>
+    </row>
+    <row r="379" spans="1:1">
+      <c r="A379" s="4"/>
+    </row>
+    <row r="380" spans="1:1">
+      <c r="A380" s="4"/>
+    </row>
+    <row r="381" spans="1:1">
+      <c r="A381" s="4"/>
+    </row>
+    <row r="382" spans="1:1">
+      <c r="A382" s="4"/>
+    </row>
+    <row r="383" spans="1:1">
+      <c r="A383" s="4"/>
+    </row>
+    <row r="384" spans="1:1">
+      <c r="A384" s="4"/>
+    </row>
+    <row r="385" spans="1:1">
+      <c r="A385" s="4"/>
+    </row>
+    <row r="386" spans="1:1">
+      <c r="A386" s="4"/>
+    </row>
+    <row r="387" spans="1:1">
+      <c r="A387" s="4"/>
+    </row>
+    <row r="388" spans="1:1">
+      <c r="A388" s="4"/>
+    </row>
+    <row r="389" spans="1:1">
+      <c r="A389" s="4"/>
+    </row>
+    <row r="390" spans="1:1">
+      <c r="A390" s="4"/>
+    </row>
+    <row r="391" spans="1:1">
+      <c r="A391" s="4"/>
+    </row>
+    <row r="392" spans="1:1">
+      <c r="A392" s="4"/>
+    </row>
+    <row r="393" spans="1:1">
+      <c r="A393" s="4"/>
+    </row>
+    <row r="394" spans="1:1">
+      <c r="A394" s="4"/>
+    </row>
+    <row r="395" spans="1:1">
+      <c r="A395" s="4"/>
+    </row>
+    <row r="396" spans="1:1">
+      <c r="A396" s="4"/>
+    </row>
+    <row r="397" spans="1:1">
+      <c r="A397" s="4"/>
+    </row>
+    <row r="398" spans="1:1">
+      <c r="A398" s="4"/>
+    </row>
+    <row r="399" spans="1:1">
+      <c r="A399" s="4"/>
+    </row>
+    <row r="400" spans="1:1">
+      <c r="A400" s="4"/>
+    </row>
+    <row r="401" spans="1:1">
+      <c r="A401" s="4"/>
+    </row>
+    <row r="402" spans="1:1">
+      <c r="A402" s="4"/>
+    </row>
+    <row r="403" spans="1:1">
+      <c r="A403" s="4"/>
+    </row>
+    <row r="404" spans="1:1">
+      <c r="A404" s="4"/>
+    </row>
+    <row r="405" spans="1:1">
+      <c r="A405" s="4"/>
+    </row>
+    <row r="406" spans="1:1">
+      <c r="A406" s="4"/>
+    </row>
+    <row r="407" spans="1:1">
+      <c r="A407" s="4"/>
+    </row>
+    <row r="408" spans="1:1">
+      <c r="A408" s="4"/>
+    </row>
+    <row r="409" spans="1:1">
+      <c r="A409" s="4"/>
+    </row>
+    <row r="410" spans="1:1">
+      <c r="A410" s="4"/>
+    </row>
+    <row r="411" spans="1:1">
+      <c r="A411" s="4"/>
+    </row>
+    <row r="412" spans="1:1">
+      <c r="A412" s="4"/>
+    </row>
+    <row r="413" spans="1:1">
+      <c r="A413" s="4"/>
+    </row>
+    <row r="414" spans="1:1">
+      <c r="A414" s="4"/>
+    </row>
+    <row r="415" spans="1:1">
+      <c r="A415" s="4"/>
+    </row>
+    <row r="416" spans="1:1">
+      <c r="A416" s="4"/>
+    </row>
+    <row r="417" spans="1:1">
+      <c r="A417" s="4"/>
+    </row>
+    <row r="418" spans="1:1">
+      <c r="A418" s="4"/>
+    </row>
+    <row r="419" spans="1:1">
+      <c r="A419" s="4"/>
+    </row>
+    <row r="420" spans="1:1">
+      <c r="A420" s="4"/>
+    </row>
+    <row r="421" spans="1:1">
+      <c r="A421" s="4"/>
+    </row>
+    <row r="422" spans="1:1">
+      <c r="A422" s="4"/>
+    </row>
+    <row r="423" spans="1:1">
+      <c r="A423" s="4"/>
+    </row>
+    <row r="424" spans="1:1">
+      <c r="A424" s="4"/>
+    </row>
+    <row r="425" spans="1:1">
+      <c r="A425" s="4"/>
+    </row>
+    <row r="426" spans="1:1">
+      <c r="A426" s="4"/>
+    </row>
+    <row r="427" spans="1:1">
+      <c r="A427" s="4"/>
+    </row>
+    <row r="428" spans="1:1">
+      <c r="A428" s="4"/>
+    </row>
+    <row r="429" spans="1:1">
+      <c r="A429" s="4"/>
+    </row>
+    <row r="430" spans="1:1">
+      <c r="A430" s="4"/>
+    </row>
+    <row r="431" spans="1:1">
+      <c r="A431" s="4"/>
+    </row>
+    <row r="432" spans="1:1">
+      <c r="A432" s="4"/>
+    </row>
+    <row r="433" spans="1:1">
+      <c r="A433" s="4"/>
+    </row>
   </sheetData>
-  <mergeCells count="8">
+  <mergeCells count="144">
+    <mergeCell ref="A26:A28"/>
+    <mergeCell ref="A29:A31"/>
+    <mergeCell ref="A32:A34"/>
+    <mergeCell ref="A35:A37"/>
+    <mergeCell ref="A38:A40"/>
     <mergeCell ref="A17:A19"/>
     <mergeCell ref="A20:A22"/>
     <mergeCell ref="A23:A25"/>
@@ -556,7 +1785,139 @@
     <mergeCell ref="A8:A10"/>
     <mergeCell ref="A11:A13"/>
     <mergeCell ref="A14:A16"/>
+    <mergeCell ref="A56:A58"/>
+    <mergeCell ref="A59:A61"/>
+    <mergeCell ref="A62:A64"/>
+    <mergeCell ref="A65:A67"/>
+    <mergeCell ref="A68:A70"/>
+    <mergeCell ref="A41:A43"/>
+    <mergeCell ref="A44:A46"/>
+    <mergeCell ref="A47:A49"/>
+    <mergeCell ref="A50:A52"/>
+    <mergeCell ref="A53:A55"/>
+    <mergeCell ref="A86:A88"/>
+    <mergeCell ref="A89:A91"/>
+    <mergeCell ref="A92:A94"/>
+    <mergeCell ref="A95:A97"/>
+    <mergeCell ref="A98:A100"/>
+    <mergeCell ref="A71:A73"/>
+    <mergeCell ref="A74:A76"/>
+    <mergeCell ref="A77:A79"/>
+    <mergeCell ref="A80:A82"/>
+    <mergeCell ref="A83:A85"/>
+    <mergeCell ref="A116:A118"/>
+    <mergeCell ref="A119:A121"/>
+    <mergeCell ref="A122:A124"/>
+    <mergeCell ref="A125:A127"/>
+    <mergeCell ref="A128:A130"/>
+    <mergeCell ref="A101:A103"/>
+    <mergeCell ref="A104:A106"/>
+    <mergeCell ref="A107:A109"/>
+    <mergeCell ref="A110:A112"/>
+    <mergeCell ref="A113:A115"/>
+    <mergeCell ref="A146:A148"/>
+    <mergeCell ref="A149:A151"/>
+    <mergeCell ref="A152:A154"/>
+    <mergeCell ref="A155:A157"/>
+    <mergeCell ref="A158:A160"/>
+    <mergeCell ref="A131:A133"/>
+    <mergeCell ref="A134:A136"/>
+    <mergeCell ref="A137:A139"/>
+    <mergeCell ref="A140:A142"/>
+    <mergeCell ref="A143:A145"/>
+    <mergeCell ref="A176:A178"/>
+    <mergeCell ref="A179:A181"/>
+    <mergeCell ref="A182:A184"/>
+    <mergeCell ref="A185:A187"/>
+    <mergeCell ref="A188:A190"/>
+    <mergeCell ref="A161:A163"/>
+    <mergeCell ref="A164:A166"/>
+    <mergeCell ref="A167:A169"/>
+    <mergeCell ref="A170:A172"/>
+    <mergeCell ref="A173:A175"/>
+    <mergeCell ref="A206:A208"/>
+    <mergeCell ref="A209:A211"/>
+    <mergeCell ref="A212:A214"/>
+    <mergeCell ref="A215:A217"/>
+    <mergeCell ref="A218:A220"/>
+    <mergeCell ref="A191:A193"/>
+    <mergeCell ref="A194:A196"/>
+    <mergeCell ref="A197:A199"/>
+    <mergeCell ref="A200:A202"/>
+    <mergeCell ref="A203:A205"/>
+    <mergeCell ref="A236:A238"/>
+    <mergeCell ref="A239:A241"/>
+    <mergeCell ref="A242:A244"/>
+    <mergeCell ref="A245:A247"/>
+    <mergeCell ref="A248:A250"/>
+    <mergeCell ref="A221:A223"/>
+    <mergeCell ref="A224:A226"/>
+    <mergeCell ref="A227:A229"/>
+    <mergeCell ref="A230:A232"/>
+    <mergeCell ref="A233:A235"/>
+    <mergeCell ref="A266:A268"/>
+    <mergeCell ref="A269:A271"/>
+    <mergeCell ref="A272:A274"/>
+    <mergeCell ref="A275:A277"/>
+    <mergeCell ref="A278:A280"/>
+    <mergeCell ref="A251:A253"/>
+    <mergeCell ref="A254:A256"/>
+    <mergeCell ref="A257:A259"/>
+    <mergeCell ref="A260:A262"/>
+    <mergeCell ref="A263:A265"/>
+    <mergeCell ref="A296:A298"/>
+    <mergeCell ref="A299:A301"/>
+    <mergeCell ref="A302:A304"/>
+    <mergeCell ref="A305:A307"/>
+    <mergeCell ref="A308:A310"/>
+    <mergeCell ref="A281:A283"/>
+    <mergeCell ref="A284:A286"/>
+    <mergeCell ref="A287:A289"/>
+    <mergeCell ref="A290:A292"/>
+    <mergeCell ref="A293:A295"/>
+    <mergeCell ref="A326:A328"/>
+    <mergeCell ref="A329:A331"/>
+    <mergeCell ref="A332:A334"/>
+    <mergeCell ref="A335:A337"/>
+    <mergeCell ref="A338:A340"/>
+    <mergeCell ref="A311:A313"/>
+    <mergeCell ref="A314:A316"/>
+    <mergeCell ref="A317:A319"/>
+    <mergeCell ref="A320:A322"/>
+    <mergeCell ref="A323:A325"/>
+    <mergeCell ref="A356:A358"/>
+    <mergeCell ref="A359:A361"/>
+    <mergeCell ref="A362:A364"/>
+    <mergeCell ref="A365:A367"/>
+    <mergeCell ref="A368:A370"/>
+    <mergeCell ref="A341:A343"/>
+    <mergeCell ref="A344:A346"/>
+    <mergeCell ref="A347:A349"/>
+    <mergeCell ref="A350:A352"/>
+    <mergeCell ref="A353:A355"/>
+    <mergeCell ref="A386:A388"/>
+    <mergeCell ref="A389:A391"/>
+    <mergeCell ref="A392:A394"/>
+    <mergeCell ref="A395:A397"/>
+    <mergeCell ref="A398:A400"/>
+    <mergeCell ref="A371:A373"/>
+    <mergeCell ref="A374:A376"/>
+    <mergeCell ref="A377:A379"/>
+    <mergeCell ref="A380:A382"/>
+    <mergeCell ref="A383:A385"/>
+    <mergeCell ref="A431:A433"/>
+    <mergeCell ref="A416:A418"/>
+    <mergeCell ref="A419:A421"/>
+    <mergeCell ref="A422:A424"/>
+    <mergeCell ref="A425:A427"/>
+    <mergeCell ref="A428:A430"/>
+    <mergeCell ref="A401:A403"/>
+    <mergeCell ref="A404:A406"/>
+    <mergeCell ref="A407:A409"/>
+    <mergeCell ref="A410:A412"/>
+    <mergeCell ref="A413:A415"/>
   </mergeCells>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" r:id="rId1"/>
 </worksheet>
 </file>
--- a/planilhas/Planilha de Base para Cotacao.xlsx
+++ b/planilhas/Planilha de Base para Cotacao.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/0a19316afdd125d6/Documentos/GitHub/hawks-automations/planilhas/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="102" documentId="8_{B6B05E56-6ADC-4554-A921-81DFAB966C0D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6312C9EA-B1ED-4883-9FA8-8ABCD49C1767}"/>
+  <xr:revisionPtr revIDLastSave="120" documentId="8_{B6B05E56-6ADC-4554-A921-81DFAB966C0D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C3DA2ADD-C9EA-4CC3-8D51-49BBE95BCFBA}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="21840" windowHeight="13140" xr2:uid="{AB0A4C4E-1938-46F3-8FAE-9EC8B05F0B3E}"/>
   </bookViews>
@@ -137,9 +137,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Tema do Office">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Tema do Office 2013 - 2022">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -177,7 +177,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -283,7 +283,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -425,7 +425,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -438,10 +438,9 @@
   <cols>
     <col min="1" max="1" width="17.7109375" style="1" customWidth="1"/>
     <col min="2" max="2" width="11.7109375" style="1" customWidth="1"/>
-    <col min="3" max="3" width="11.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="13.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="11.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="9.140625" style="1"/>
+    <col min="5" max="6" width="11.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="22" style="1" bestFit="1" customWidth="1"/>
     <col min="8" max="16384" width="9.140625" style="1"/>
   </cols>
@@ -1772,6 +1771,137 @@
     </row>
   </sheetData>
   <mergeCells count="144">
+    <mergeCell ref="A431:A433"/>
+    <mergeCell ref="A416:A418"/>
+    <mergeCell ref="A419:A421"/>
+    <mergeCell ref="A422:A424"/>
+    <mergeCell ref="A425:A427"/>
+    <mergeCell ref="A428:A430"/>
+    <mergeCell ref="A401:A403"/>
+    <mergeCell ref="A404:A406"/>
+    <mergeCell ref="A407:A409"/>
+    <mergeCell ref="A410:A412"/>
+    <mergeCell ref="A413:A415"/>
+    <mergeCell ref="A386:A388"/>
+    <mergeCell ref="A389:A391"/>
+    <mergeCell ref="A392:A394"/>
+    <mergeCell ref="A395:A397"/>
+    <mergeCell ref="A398:A400"/>
+    <mergeCell ref="A371:A373"/>
+    <mergeCell ref="A374:A376"/>
+    <mergeCell ref="A377:A379"/>
+    <mergeCell ref="A380:A382"/>
+    <mergeCell ref="A383:A385"/>
+    <mergeCell ref="A356:A358"/>
+    <mergeCell ref="A359:A361"/>
+    <mergeCell ref="A362:A364"/>
+    <mergeCell ref="A365:A367"/>
+    <mergeCell ref="A368:A370"/>
+    <mergeCell ref="A341:A343"/>
+    <mergeCell ref="A344:A346"/>
+    <mergeCell ref="A347:A349"/>
+    <mergeCell ref="A350:A352"/>
+    <mergeCell ref="A353:A355"/>
+    <mergeCell ref="A326:A328"/>
+    <mergeCell ref="A329:A331"/>
+    <mergeCell ref="A332:A334"/>
+    <mergeCell ref="A335:A337"/>
+    <mergeCell ref="A338:A340"/>
+    <mergeCell ref="A311:A313"/>
+    <mergeCell ref="A314:A316"/>
+    <mergeCell ref="A317:A319"/>
+    <mergeCell ref="A320:A322"/>
+    <mergeCell ref="A323:A325"/>
+    <mergeCell ref="A296:A298"/>
+    <mergeCell ref="A299:A301"/>
+    <mergeCell ref="A302:A304"/>
+    <mergeCell ref="A305:A307"/>
+    <mergeCell ref="A308:A310"/>
+    <mergeCell ref="A281:A283"/>
+    <mergeCell ref="A284:A286"/>
+    <mergeCell ref="A287:A289"/>
+    <mergeCell ref="A290:A292"/>
+    <mergeCell ref="A293:A295"/>
+    <mergeCell ref="A266:A268"/>
+    <mergeCell ref="A269:A271"/>
+    <mergeCell ref="A272:A274"/>
+    <mergeCell ref="A275:A277"/>
+    <mergeCell ref="A278:A280"/>
+    <mergeCell ref="A251:A253"/>
+    <mergeCell ref="A254:A256"/>
+    <mergeCell ref="A257:A259"/>
+    <mergeCell ref="A260:A262"/>
+    <mergeCell ref="A263:A265"/>
+    <mergeCell ref="A236:A238"/>
+    <mergeCell ref="A239:A241"/>
+    <mergeCell ref="A242:A244"/>
+    <mergeCell ref="A245:A247"/>
+    <mergeCell ref="A248:A250"/>
+    <mergeCell ref="A221:A223"/>
+    <mergeCell ref="A224:A226"/>
+    <mergeCell ref="A227:A229"/>
+    <mergeCell ref="A230:A232"/>
+    <mergeCell ref="A233:A235"/>
+    <mergeCell ref="A206:A208"/>
+    <mergeCell ref="A209:A211"/>
+    <mergeCell ref="A212:A214"/>
+    <mergeCell ref="A215:A217"/>
+    <mergeCell ref="A218:A220"/>
+    <mergeCell ref="A191:A193"/>
+    <mergeCell ref="A194:A196"/>
+    <mergeCell ref="A197:A199"/>
+    <mergeCell ref="A200:A202"/>
+    <mergeCell ref="A203:A205"/>
+    <mergeCell ref="A176:A178"/>
+    <mergeCell ref="A179:A181"/>
+    <mergeCell ref="A182:A184"/>
+    <mergeCell ref="A185:A187"/>
+    <mergeCell ref="A188:A190"/>
+    <mergeCell ref="A161:A163"/>
+    <mergeCell ref="A164:A166"/>
+    <mergeCell ref="A167:A169"/>
+    <mergeCell ref="A170:A172"/>
+    <mergeCell ref="A173:A175"/>
+    <mergeCell ref="A146:A148"/>
+    <mergeCell ref="A149:A151"/>
+    <mergeCell ref="A152:A154"/>
+    <mergeCell ref="A155:A157"/>
+    <mergeCell ref="A158:A160"/>
+    <mergeCell ref="A131:A133"/>
+    <mergeCell ref="A134:A136"/>
+    <mergeCell ref="A137:A139"/>
+    <mergeCell ref="A140:A142"/>
+    <mergeCell ref="A143:A145"/>
+    <mergeCell ref="A116:A118"/>
+    <mergeCell ref="A119:A121"/>
+    <mergeCell ref="A122:A124"/>
+    <mergeCell ref="A125:A127"/>
+    <mergeCell ref="A128:A130"/>
+    <mergeCell ref="A101:A103"/>
+    <mergeCell ref="A104:A106"/>
+    <mergeCell ref="A107:A109"/>
+    <mergeCell ref="A110:A112"/>
+    <mergeCell ref="A113:A115"/>
+    <mergeCell ref="A86:A88"/>
+    <mergeCell ref="A89:A91"/>
+    <mergeCell ref="A92:A94"/>
+    <mergeCell ref="A95:A97"/>
+    <mergeCell ref="A98:A100"/>
+    <mergeCell ref="A71:A73"/>
+    <mergeCell ref="A74:A76"/>
+    <mergeCell ref="A77:A79"/>
+    <mergeCell ref="A80:A82"/>
+    <mergeCell ref="A83:A85"/>
+    <mergeCell ref="A56:A58"/>
+    <mergeCell ref="A59:A61"/>
+    <mergeCell ref="A62:A64"/>
+    <mergeCell ref="A65:A67"/>
+    <mergeCell ref="A68:A70"/>
+    <mergeCell ref="A41:A43"/>
+    <mergeCell ref="A44:A46"/>
+    <mergeCell ref="A47:A49"/>
+    <mergeCell ref="A50:A52"/>
+    <mergeCell ref="A53:A55"/>
     <mergeCell ref="A26:A28"/>
     <mergeCell ref="A29:A31"/>
     <mergeCell ref="A32:A34"/>
@@ -1785,137 +1915,6 @@
     <mergeCell ref="A8:A10"/>
     <mergeCell ref="A11:A13"/>
     <mergeCell ref="A14:A16"/>
-    <mergeCell ref="A56:A58"/>
-    <mergeCell ref="A59:A61"/>
-    <mergeCell ref="A62:A64"/>
-    <mergeCell ref="A65:A67"/>
-    <mergeCell ref="A68:A70"/>
-    <mergeCell ref="A41:A43"/>
-    <mergeCell ref="A44:A46"/>
-    <mergeCell ref="A47:A49"/>
-    <mergeCell ref="A50:A52"/>
-    <mergeCell ref="A53:A55"/>
-    <mergeCell ref="A86:A88"/>
-    <mergeCell ref="A89:A91"/>
-    <mergeCell ref="A92:A94"/>
-    <mergeCell ref="A95:A97"/>
-    <mergeCell ref="A98:A100"/>
-    <mergeCell ref="A71:A73"/>
-    <mergeCell ref="A74:A76"/>
-    <mergeCell ref="A77:A79"/>
-    <mergeCell ref="A80:A82"/>
-    <mergeCell ref="A83:A85"/>
-    <mergeCell ref="A116:A118"/>
-    <mergeCell ref="A119:A121"/>
-    <mergeCell ref="A122:A124"/>
-    <mergeCell ref="A125:A127"/>
-    <mergeCell ref="A128:A130"/>
-    <mergeCell ref="A101:A103"/>
-    <mergeCell ref="A104:A106"/>
-    <mergeCell ref="A107:A109"/>
-    <mergeCell ref="A110:A112"/>
-    <mergeCell ref="A113:A115"/>
-    <mergeCell ref="A146:A148"/>
-    <mergeCell ref="A149:A151"/>
-    <mergeCell ref="A152:A154"/>
-    <mergeCell ref="A155:A157"/>
-    <mergeCell ref="A158:A160"/>
-    <mergeCell ref="A131:A133"/>
-    <mergeCell ref="A134:A136"/>
-    <mergeCell ref="A137:A139"/>
-    <mergeCell ref="A140:A142"/>
-    <mergeCell ref="A143:A145"/>
-    <mergeCell ref="A176:A178"/>
-    <mergeCell ref="A179:A181"/>
-    <mergeCell ref="A182:A184"/>
-    <mergeCell ref="A185:A187"/>
-    <mergeCell ref="A188:A190"/>
-    <mergeCell ref="A161:A163"/>
-    <mergeCell ref="A164:A166"/>
-    <mergeCell ref="A167:A169"/>
-    <mergeCell ref="A170:A172"/>
-    <mergeCell ref="A173:A175"/>
-    <mergeCell ref="A206:A208"/>
-    <mergeCell ref="A209:A211"/>
-    <mergeCell ref="A212:A214"/>
-    <mergeCell ref="A215:A217"/>
-    <mergeCell ref="A218:A220"/>
-    <mergeCell ref="A191:A193"/>
-    <mergeCell ref="A194:A196"/>
-    <mergeCell ref="A197:A199"/>
-    <mergeCell ref="A200:A202"/>
-    <mergeCell ref="A203:A205"/>
-    <mergeCell ref="A236:A238"/>
-    <mergeCell ref="A239:A241"/>
-    <mergeCell ref="A242:A244"/>
-    <mergeCell ref="A245:A247"/>
-    <mergeCell ref="A248:A250"/>
-    <mergeCell ref="A221:A223"/>
-    <mergeCell ref="A224:A226"/>
-    <mergeCell ref="A227:A229"/>
-    <mergeCell ref="A230:A232"/>
-    <mergeCell ref="A233:A235"/>
-    <mergeCell ref="A266:A268"/>
-    <mergeCell ref="A269:A271"/>
-    <mergeCell ref="A272:A274"/>
-    <mergeCell ref="A275:A277"/>
-    <mergeCell ref="A278:A280"/>
-    <mergeCell ref="A251:A253"/>
-    <mergeCell ref="A254:A256"/>
-    <mergeCell ref="A257:A259"/>
-    <mergeCell ref="A260:A262"/>
-    <mergeCell ref="A263:A265"/>
-    <mergeCell ref="A296:A298"/>
-    <mergeCell ref="A299:A301"/>
-    <mergeCell ref="A302:A304"/>
-    <mergeCell ref="A305:A307"/>
-    <mergeCell ref="A308:A310"/>
-    <mergeCell ref="A281:A283"/>
-    <mergeCell ref="A284:A286"/>
-    <mergeCell ref="A287:A289"/>
-    <mergeCell ref="A290:A292"/>
-    <mergeCell ref="A293:A295"/>
-    <mergeCell ref="A326:A328"/>
-    <mergeCell ref="A329:A331"/>
-    <mergeCell ref="A332:A334"/>
-    <mergeCell ref="A335:A337"/>
-    <mergeCell ref="A338:A340"/>
-    <mergeCell ref="A311:A313"/>
-    <mergeCell ref="A314:A316"/>
-    <mergeCell ref="A317:A319"/>
-    <mergeCell ref="A320:A322"/>
-    <mergeCell ref="A323:A325"/>
-    <mergeCell ref="A356:A358"/>
-    <mergeCell ref="A359:A361"/>
-    <mergeCell ref="A362:A364"/>
-    <mergeCell ref="A365:A367"/>
-    <mergeCell ref="A368:A370"/>
-    <mergeCell ref="A341:A343"/>
-    <mergeCell ref="A344:A346"/>
-    <mergeCell ref="A347:A349"/>
-    <mergeCell ref="A350:A352"/>
-    <mergeCell ref="A353:A355"/>
-    <mergeCell ref="A386:A388"/>
-    <mergeCell ref="A389:A391"/>
-    <mergeCell ref="A392:A394"/>
-    <mergeCell ref="A395:A397"/>
-    <mergeCell ref="A398:A400"/>
-    <mergeCell ref="A371:A373"/>
-    <mergeCell ref="A374:A376"/>
-    <mergeCell ref="A377:A379"/>
-    <mergeCell ref="A380:A382"/>
-    <mergeCell ref="A383:A385"/>
-    <mergeCell ref="A431:A433"/>
-    <mergeCell ref="A416:A418"/>
-    <mergeCell ref="A419:A421"/>
-    <mergeCell ref="A422:A424"/>
-    <mergeCell ref="A425:A427"/>
-    <mergeCell ref="A428:A430"/>
-    <mergeCell ref="A401:A403"/>
-    <mergeCell ref="A404:A406"/>
-    <mergeCell ref="A407:A409"/>
-    <mergeCell ref="A410:A412"/>
-    <mergeCell ref="A413:A415"/>
   </mergeCells>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" r:id="rId1"/>

--- a/planilhas/Planilha de Base para Cotacao.xlsx
+++ b/planilhas/Planilha de Base para Cotacao.xlsx
@@ -8,13 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/0a19316afdd125d6/Documentos/GitHub/hawks-automations/planilhas/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="120" documentId="8_{B6B05E56-6ADC-4554-A921-81DFAB966C0D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C3DA2ADD-C9EA-4CC3-8D51-49BBE95BCFBA}"/>
+  <xr:revisionPtr revIDLastSave="276" documentId="8_{B6B05E56-6ADC-4554-A921-81DFAB966C0D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FA88737E-75B2-4ED2-AA61-A48FA5D38C95}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="21840" windowHeight="13140" xr2:uid="{AB0A4C4E-1938-46F3-8FAE-9EC8B05F0B3E}"/>
   </bookViews>
   <sheets>
     <sheet name="Planilha1" sheetId="1" r:id="rId1"/>
   </sheets>
+  <definedNames>
+    <definedName name="B3c2">Planilha1!$B$3</definedName>
+  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -114,7 +117,7 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -433,7 +436,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EA940922-860D-4863-B9A5-E7EE2A94C235}">
-  <dimension ref="A1:G433"/>
+  <dimension ref="A1:J433"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="17.7109375" style="1" customWidth="1"/>
@@ -445,7 +448,7 @@
     <col min="8" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" s="2" customFormat="1">
+    <row r="1" spans="1:10" s="2" customFormat="1">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -468,54 +471,55 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:7">
+    <row r="2" spans="1:10">
       <c r="A2" s="4"/>
       <c r="G2" s="1" t="e">
         <f>MEDIAN(C2,D2,E2,F2)*1.8</f>
         <v>#NUM!</v>
       </c>
     </row>
-    <row r="3" spans="1:7">
+    <row r="3" spans="1:10">
       <c r="A3" s="4"/>
-      <c r="B3" s="3"/>
-    </row>
-    <row r="4" spans="1:7">
+    </row>
+    <row r="4" spans="1:10">
       <c r="A4" s="4"/>
     </row>
-    <row r="5" spans="1:7">
+    <row r="5" spans="1:10">
       <c r="A5" s="4"/>
     </row>
-    <row r="6" spans="1:7">
+    <row r="6" spans="1:10">
       <c r="A6" s="4"/>
     </row>
-    <row r="7" spans="1:7">
+    <row r="7" spans="1:10">
       <c r="A7" s="4"/>
-    </row>
-    <row r="8" spans="1:7">
+      <c r="I7" s="3"/>
+    </row>
+    <row r="8" spans="1:10">
       <c r="A8" s="4"/>
     </row>
-    <row r="9" spans="1:7">
+    <row r="9" spans="1:10">
       <c r="A9" s="4"/>
     </row>
-    <row r="10" spans="1:7">
+    <row r="10" spans="1:10">
       <c r="A10" s="4"/>
     </row>
-    <row r="11" spans="1:7">
+    <row r="11" spans="1:10">
       <c r="A11" s="4"/>
     </row>
-    <row r="12" spans="1:7">
+    <row r="12" spans="1:10">
       <c r="A12" s="4"/>
-    </row>
-    <row r="13" spans="1:7">
+      <c r="J12" s="2"/>
+    </row>
+    <row r="13" spans="1:10">
       <c r="A13" s="4"/>
     </row>
-    <row r="14" spans="1:7">
+    <row r="14" spans="1:10">
       <c r="A14" s="4"/>
     </row>
-    <row r="15" spans="1:7">
+    <row r="15" spans="1:10">
       <c r="A15" s="4"/>
     </row>
-    <row r="16" spans="1:7">
+    <row r="16" spans="1:10">
       <c r="A16" s="4"/>
     </row>
     <row r="17" spans="1:1">
@@ -1771,137 +1775,6 @@
     </row>
   </sheetData>
   <mergeCells count="144">
-    <mergeCell ref="A431:A433"/>
-    <mergeCell ref="A416:A418"/>
-    <mergeCell ref="A419:A421"/>
-    <mergeCell ref="A422:A424"/>
-    <mergeCell ref="A425:A427"/>
-    <mergeCell ref="A428:A430"/>
-    <mergeCell ref="A401:A403"/>
-    <mergeCell ref="A404:A406"/>
-    <mergeCell ref="A407:A409"/>
-    <mergeCell ref="A410:A412"/>
-    <mergeCell ref="A413:A415"/>
-    <mergeCell ref="A386:A388"/>
-    <mergeCell ref="A389:A391"/>
-    <mergeCell ref="A392:A394"/>
-    <mergeCell ref="A395:A397"/>
-    <mergeCell ref="A398:A400"/>
-    <mergeCell ref="A371:A373"/>
-    <mergeCell ref="A374:A376"/>
-    <mergeCell ref="A377:A379"/>
-    <mergeCell ref="A380:A382"/>
-    <mergeCell ref="A383:A385"/>
-    <mergeCell ref="A356:A358"/>
-    <mergeCell ref="A359:A361"/>
-    <mergeCell ref="A362:A364"/>
-    <mergeCell ref="A365:A367"/>
-    <mergeCell ref="A368:A370"/>
-    <mergeCell ref="A341:A343"/>
-    <mergeCell ref="A344:A346"/>
-    <mergeCell ref="A347:A349"/>
-    <mergeCell ref="A350:A352"/>
-    <mergeCell ref="A353:A355"/>
-    <mergeCell ref="A326:A328"/>
-    <mergeCell ref="A329:A331"/>
-    <mergeCell ref="A332:A334"/>
-    <mergeCell ref="A335:A337"/>
-    <mergeCell ref="A338:A340"/>
-    <mergeCell ref="A311:A313"/>
-    <mergeCell ref="A314:A316"/>
-    <mergeCell ref="A317:A319"/>
-    <mergeCell ref="A320:A322"/>
-    <mergeCell ref="A323:A325"/>
-    <mergeCell ref="A296:A298"/>
-    <mergeCell ref="A299:A301"/>
-    <mergeCell ref="A302:A304"/>
-    <mergeCell ref="A305:A307"/>
-    <mergeCell ref="A308:A310"/>
-    <mergeCell ref="A281:A283"/>
-    <mergeCell ref="A284:A286"/>
-    <mergeCell ref="A287:A289"/>
-    <mergeCell ref="A290:A292"/>
-    <mergeCell ref="A293:A295"/>
-    <mergeCell ref="A266:A268"/>
-    <mergeCell ref="A269:A271"/>
-    <mergeCell ref="A272:A274"/>
-    <mergeCell ref="A275:A277"/>
-    <mergeCell ref="A278:A280"/>
-    <mergeCell ref="A251:A253"/>
-    <mergeCell ref="A254:A256"/>
-    <mergeCell ref="A257:A259"/>
-    <mergeCell ref="A260:A262"/>
-    <mergeCell ref="A263:A265"/>
-    <mergeCell ref="A236:A238"/>
-    <mergeCell ref="A239:A241"/>
-    <mergeCell ref="A242:A244"/>
-    <mergeCell ref="A245:A247"/>
-    <mergeCell ref="A248:A250"/>
-    <mergeCell ref="A221:A223"/>
-    <mergeCell ref="A224:A226"/>
-    <mergeCell ref="A227:A229"/>
-    <mergeCell ref="A230:A232"/>
-    <mergeCell ref="A233:A235"/>
-    <mergeCell ref="A206:A208"/>
-    <mergeCell ref="A209:A211"/>
-    <mergeCell ref="A212:A214"/>
-    <mergeCell ref="A215:A217"/>
-    <mergeCell ref="A218:A220"/>
-    <mergeCell ref="A191:A193"/>
-    <mergeCell ref="A194:A196"/>
-    <mergeCell ref="A197:A199"/>
-    <mergeCell ref="A200:A202"/>
-    <mergeCell ref="A203:A205"/>
-    <mergeCell ref="A176:A178"/>
-    <mergeCell ref="A179:A181"/>
-    <mergeCell ref="A182:A184"/>
-    <mergeCell ref="A185:A187"/>
-    <mergeCell ref="A188:A190"/>
-    <mergeCell ref="A161:A163"/>
-    <mergeCell ref="A164:A166"/>
-    <mergeCell ref="A167:A169"/>
-    <mergeCell ref="A170:A172"/>
-    <mergeCell ref="A173:A175"/>
-    <mergeCell ref="A146:A148"/>
-    <mergeCell ref="A149:A151"/>
-    <mergeCell ref="A152:A154"/>
-    <mergeCell ref="A155:A157"/>
-    <mergeCell ref="A158:A160"/>
-    <mergeCell ref="A131:A133"/>
-    <mergeCell ref="A134:A136"/>
-    <mergeCell ref="A137:A139"/>
-    <mergeCell ref="A140:A142"/>
-    <mergeCell ref="A143:A145"/>
-    <mergeCell ref="A116:A118"/>
-    <mergeCell ref="A119:A121"/>
-    <mergeCell ref="A122:A124"/>
-    <mergeCell ref="A125:A127"/>
-    <mergeCell ref="A128:A130"/>
-    <mergeCell ref="A101:A103"/>
-    <mergeCell ref="A104:A106"/>
-    <mergeCell ref="A107:A109"/>
-    <mergeCell ref="A110:A112"/>
-    <mergeCell ref="A113:A115"/>
-    <mergeCell ref="A86:A88"/>
-    <mergeCell ref="A89:A91"/>
-    <mergeCell ref="A92:A94"/>
-    <mergeCell ref="A95:A97"/>
-    <mergeCell ref="A98:A100"/>
-    <mergeCell ref="A71:A73"/>
-    <mergeCell ref="A74:A76"/>
-    <mergeCell ref="A77:A79"/>
-    <mergeCell ref="A80:A82"/>
-    <mergeCell ref="A83:A85"/>
-    <mergeCell ref="A56:A58"/>
-    <mergeCell ref="A59:A61"/>
-    <mergeCell ref="A62:A64"/>
-    <mergeCell ref="A65:A67"/>
-    <mergeCell ref="A68:A70"/>
-    <mergeCell ref="A41:A43"/>
-    <mergeCell ref="A44:A46"/>
-    <mergeCell ref="A47:A49"/>
-    <mergeCell ref="A50:A52"/>
-    <mergeCell ref="A53:A55"/>
     <mergeCell ref="A26:A28"/>
     <mergeCell ref="A29:A31"/>
     <mergeCell ref="A32:A34"/>
@@ -1915,6 +1788,137 @@
     <mergeCell ref="A8:A10"/>
     <mergeCell ref="A11:A13"/>
     <mergeCell ref="A14:A16"/>
+    <mergeCell ref="A56:A58"/>
+    <mergeCell ref="A59:A61"/>
+    <mergeCell ref="A62:A64"/>
+    <mergeCell ref="A65:A67"/>
+    <mergeCell ref="A68:A70"/>
+    <mergeCell ref="A41:A43"/>
+    <mergeCell ref="A44:A46"/>
+    <mergeCell ref="A47:A49"/>
+    <mergeCell ref="A50:A52"/>
+    <mergeCell ref="A53:A55"/>
+    <mergeCell ref="A86:A88"/>
+    <mergeCell ref="A89:A91"/>
+    <mergeCell ref="A92:A94"/>
+    <mergeCell ref="A95:A97"/>
+    <mergeCell ref="A98:A100"/>
+    <mergeCell ref="A71:A73"/>
+    <mergeCell ref="A74:A76"/>
+    <mergeCell ref="A77:A79"/>
+    <mergeCell ref="A80:A82"/>
+    <mergeCell ref="A83:A85"/>
+    <mergeCell ref="A116:A118"/>
+    <mergeCell ref="A119:A121"/>
+    <mergeCell ref="A122:A124"/>
+    <mergeCell ref="A125:A127"/>
+    <mergeCell ref="A128:A130"/>
+    <mergeCell ref="A101:A103"/>
+    <mergeCell ref="A104:A106"/>
+    <mergeCell ref="A107:A109"/>
+    <mergeCell ref="A110:A112"/>
+    <mergeCell ref="A113:A115"/>
+    <mergeCell ref="A146:A148"/>
+    <mergeCell ref="A149:A151"/>
+    <mergeCell ref="A152:A154"/>
+    <mergeCell ref="A155:A157"/>
+    <mergeCell ref="A158:A160"/>
+    <mergeCell ref="A131:A133"/>
+    <mergeCell ref="A134:A136"/>
+    <mergeCell ref="A137:A139"/>
+    <mergeCell ref="A140:A142"/>
+    <mergeCell ref="A143:A145"/>
+    <mergeCell ref="A176:A178"/>
+    <mergeCell ref="A179:A181"/>
+    <mergeCell ref="A182:A184"/>
+    <mergeCell ref="A185:A187"/>
+    <mergeCell ref="A188:A190"/>
+    <mergeCell ref="A161:A163"/>
+    <mergeCell ref="A164:A166"/>
+    <mergeCell ref="A167:A169"/>
+    <mergeCell ref="A170:A172"/>
+    <mergeCell ref="A173:A175"/>
+    <mergeCell ref="A206:A208"/>
+    <mergeCell ref="A209:A211"/>
+    <mergeCell ref="A212:A214"/>
+    <mergeCell ref="A215:A217"/>
+    <mergeCell ref="A218:A220"/>
+    <mergeCell ref="A191:A193"/>
+    <mergeCell ref="A194:A196"/>
+    <mergeCell ref="A197:A199"/>
+    <mergeCell ref="A200:A202"/>
+    <mergeCell ref="A203:A205"/>
+    <mergeCell ref="A236:A238"/>
+    <mergeCell ref="A239:A241"/>
+    <mergeCell ref="A242:A244"/>
+    <mergeCell ref="A245:A247"/>
+    <mergeCell ref="A248:A250"/>
+    <mergeCell ref="A221:A223"/>
+    <mergeCell ref="A224:A226"/>
+    <mergeCell ref="A227:A229"/>
+    <mergeCell ref="A230:A232"/>
+    <mergeCell ref="A233:A235"/>
+    <mergeCell ref="A266:A268"/>
+    <mergeCell ref="A269:A271"/>
+    <mergeCell ref="A272:A274"/>
+    <mergeCell ref="A275:A277"/>
+    <mergeCell ref="A278:A280"/>
+    <mergeCell ref="A251:A253"/>
+    <mergeCell ref="A254:A256"/>
+    <mergeCell ref="A257:A259"/>
+    <mergeCell ref="A260:A262"/>
+    <mergeCell ref="A263:A265"/>
+    <mergeCell ref="A296:A298"/>
+    <mergeCell ref="A299:A301"/>
+    <mergeCell ref="A302:A304"/>
+    <mergeCell ref="A305:A307"/>
+    <mergeCell ref="A308:A310"/>
+    <mergeCell ref="A281:A283"/>
+    <mergeCell ref="A284:A286"/>
+    <mergeCell ref="A287:A289"/>
+    <mergeCell ref="A290:A292"/>
+    <mergeCell ref="A293:A295"/>
+    <mergeCell ref="A326:A328"/>
+    <mergeCell ref="A329:A331"/>
+    <mergeCell ref="A332:A334"/>
+    <mergeCell ref="A335:A337"/>
+    <mergeCell ref="A338:A340"/>
+    <mergeCell ref="A311:A313"/>
+    <mergeCell ref="A314:A316"/>
+    <mergeCell ref="A317:A319"/>
+    <mergeCell ref="A320:A322"/>
+    <mergeCell ref="A323:A325"/>
+    <mergeCell ref="A356:A358"/>
+    <mergeCell ref="A359:A361"/>
+    <mergeCell ref="A362:A364"/>
+    <mergeCell ref="A365:A367"/>
+    <mergeCell ref="A368:A370"/>
+    <mergeCell ref="A341:A343"/>
+    <mergeCell ref="A344:A346"/>
+    <mergeCell ref="A347:A349"/>
+    <mergeCell ref="A350:A352"/>
+    <mergeCell ref="A353:A355"/>
+    <mergeCell ref="A386:A388"/>
+    <mergeCell ref="A389:A391"/>
+    <mergeCell ref="A392:A394"/>
+    <mergeCell ref="A395:A397"/>
+    <mergeCell ref="A398:A400"/>
+    <mergeCell ref="A371:A373"/>
+    <mergeCell ref="A374:A376"/>
+    <mergeCell ref="A377:A379"/>
+    <mergeCell ref="A380:A382"/>
+    <mergeCell ref="A383:A385"/>
+    <mergeCell ref="A431:A433"/>
+    <mergeCell ref="A416:A418"/>
+    <mergeCell ref="A419:A421"/>
+    <mergeCell ref="A422:A424"/>
+    <mergeCell ref="A425:A427"/>
+    <mergeCell ref="A428:A430"/>
+    <mergeCell ref="A401:A403"/>
+    <mergeCell ref="A404:A406"/>
+    <mergeCell ref="A407:A409"/>
+    <mergeCell ref="A410:A412"/>
+    <mergeCell ref="A413:A415"/>
   </mergeCells>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" r:id="rId1"/>

--- a/planilhas/Planilha de Base para Cotacao.xlsx
+++ b/planilhas/Planilha de Base para Cotacao.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/0a19316afdd125d6/Documentos/GitHub/hawks-automations/planilhas/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="276" documentId="8_{B6B05E56-6ADC-4554-A921-81DFAB966C0D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FA88737E-75B2-4ED2-AA61-A48FA5D38C95}"/>
+  <xr:revisionPtr revIDLastSave="302" documentId="8_{B6B05E56-6ADC-4554-A921-81DFAB966C0D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{344E19ED-30AF-41AA-9098-68BEF30CFCC4}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="21840" windowHeight="13140" xr2:uid="{AB0A4C4E-1938-46F3-8FAE-9EC8B05F0B3E}"/>
   </bookViews>

--- a/planilhas/Planilha de Base para Cotacao.xlsx
+++ b/planilhas/Planilha de Base para Cotacao.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/0a19316afdd125d6/Documentos/GitHub/hawks-automations/planilhas/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="302" documentId="8_{B6B05E56-6ADC-4554-A921-81DFAB966C0D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{344E19ED-30AF-41AA-9098-68BEF30CFCC4}"/>
+  <xr:revisionPtr revIDLastSave="390" documentId="8_{B6B05E56-6ADC-4554-A921-81DFAB966C0D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0B32C1AE-7E22-4C86-A523-74AF08821354}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="21840" windowHeight="13140" xr2:uid="{AB0A4C4E-1938-46F3-8FAE-9EC8B05F0B3E}"/>
   </bookViews>
@@ -108,19 +108,27 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -439,13 +447,13 @@
   <dimension ref="A1:J433"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="17.7109375" style="1" customWidth="1"/>
-    <col min="2" max="2" width="11.7109375" style="1" customWidth="1"/>
-    <col min="3" max="3" width="11.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="11.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="22" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="16384" width="9.140625" style="1"/>
+    <col min="1" max="1" width="45" style="3" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.7109375" style="3" customWidth="1"/>
+    <col min="3" max="3" width="11.85546875" style="3" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.7109375" style="3" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="11.85546875" style="3" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="22" style="3" bestFit="1" customWidth="1"/>
+    <col min="8" max="16384" width="9.140625" style="3"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:10" s="2" customFormat="1">
@@ -472,1309 +480,1438 @@
       </c>
     </row>
     <row r="2" spans="1:10">
-      <c r="A2" s="4"/>
-      <c r="G2" s="1" t="e">
-        <f>MEDIAN(C2,D2,E2,F2)*1.8</f>
-        <v>#NUM!</v>
-      </c>
+      <c r="A2" s="5"/>
     </row>
     <row r="3" spans="1:10">
-      <c r="A3" s="4"/>
+      <c r="A3" s="5"/>
+      <c r="G3" s="1"/>
     </row>
     <row r="4" spans="1:10">
-      <c r="A4" s="4"/>
+      <c r="A4" s="5"/>
+      <c r="G4" s="1"/>
     </row>
     <row r="5" spans="1:10">
-      <c r="A5" s="4"/>
+      <c r="A5" s="5"/>
     </row>
     <row r="6" spans="1:10">
-      <c r="A6" s="4"/>
+      <c r="A6" s="5"/>
     </row>
     <row r="7" spans="1:10">
-      <c r="A7" s="4"/>
-      <c r="I7" s="3"/>
+      <c r="A7" s="5"/>
+      <c r="I7" s="4"/>
     </row>
     <row r="8" spans="1:10">
-      <c r="A8" s="4"/>
+      <c r="A8" s="5"/>
     </row>
     <row r="9" spans="1:10">
-      <c r="A9" s="4"/>
+      <c r="A9" s="5"/>
     </row>
     <row r="10" spans="1:10">
-      <c r="A10" s="4"/>
+      <c r="A10" s="5"/>
     </row>
     <row r="11" spans="1:10">
-      <c r="A11" s="4"/>
+      <c r="A11" s="5"/>
     </row>
     <row r="12" spans="1:10">
-      <c r="A12" s="4"/>
+      <c r="A12" s="5"/>
       <c r="J12" s="2"/>
     </row>
     <row r="13" spans="1:10">
-      <c r="A13" s="4"/>
+      <c r="A13" s="5"/>
     </row>
     <row r="14" spans="1:10">
-      <c r="A14" s="4"/>
+      <c r="A14" s="5"/>
     </row>
     <row r="15" spans="1:10">
-      <c r="A15" s="4"/>
+      <c r="A15" s="5"/>
     </row>
     <row r="16" spans="1:10">
-      <c r="A16" s="4"/>
+      <c r="A16" s="5"/>
     </row>
     <row r="17" spans="1:1">
-      <c r="A17" s="4"/>
+      <c r="A17" s="5"/>
     </row>
     <row r="18" spans="1:1">
-      <c r="A18" s="4"/>
+      <c r="A18" s="5"/>
     </row>
     <row r="19" spans="1:1">
-      <c r="A19" s="4"/>
+      <c r="A19" s="5"/>
     </row>
     <row r="20" spans="1:1">
-      <c r="A20" s="4"/>
+      <c r="A20" s="5"/>
     </row>
     <row r="21" spans="1:1">
-      <c r="A21" s="4"/>
+      <c r="A21" s="5"/>
     </row>
     <row r="22" spans="1:1">
-      <c r="A22" s="4"/>
+      <c r="A22" s="5"/>
     </row>
     <row r="23" spans="1:1">
-      <c r="A23" s="4"/>
+      <c r="A23" s="5"/>
     </row>
     <row r="24" spans="1:1">
-      <c r="A24" s="4"/>
+      <c r="A24" s="5"/>
     </row>
     <row r="25" spans="1:1">
-      <c r="A25" s="4"/>
+      <c r="A25" s="5"/>
     </row>
     <row r="26" spans="1:1">
-      <c r="A26" s="4"/>
+      <c r="A26" s="5"/>
     </row>
     <row r="27" spans="1:1">
-      <c r="A27" s="4"/>
+      <c r="A27" s="5"/>
     </row>
     <row r="28" spans="1:1">
-      <c r="A28" s="4"/>
+      <c r="A28" s="5"/>
     </row>
     <row r="29" spans="1:1">
-      <c r="A29" s="4"/>
+      <c r="A29" s="5"/>
     </row>
     <row r="30" spans="1:1">
-      <c r="A30" s="4"/>
+      <c r="A30" s="5"/>
     </row>
     <row r="31" spans="1:1">
-      <c r="A31" s="4"/>
+      <c r="A31" s="5"/>
     </row>
     <row r="32" spans="1:1">
-      <c r="A32" s="4"/>
+      <c r="A32" s="5"/>
     </row>
     <row r="33" spans="1:1">
-      <c r="A33" s="4"/>
+      <c r="A33" s="5"/>
     </row>
     <row r="34" spans="1:1">
-      <c r="A34" s="4"/>
+      <c r="A34" s="5"/>
     </row>
     <row r="35" spans="1:1">
-      <c r="A35" s="4"/>
+      <c r="A35" s="5"/>
     </row>
     <row r="36" spans="1:1">
-      <c r="A36" s="4"/>
+      <c r="A36" s="5"/>
     </row>
     <row r="37" spans="1:1">
-      <c r="A37" s="4"/>
+      <c r="A37" s="5"/>
     </row>
     <row r="38" spans="1:1">
-      <c r="A38" s="4"/>
+      <c r="A38" s="5"/>
     </row>
     <row r="39" spans="1:1">
-      <c r="A39" s="4"/>
+      <c r="A39" s="5"/>
     </row>
     <row r="40" spans="1:1">
-      <c r="A40" s="4"/>
+      <c r="A40" s="5"/>
     </row>
     <row r="41" spans="1:1">
-      <c r="A41" s="4"/>
+      <c r="A41" s="5"/>
     </row>
     <row r="42" spans="1:1">
-      <c r="A42" s="4"/>
+      <c r="A42" s="5"/>
     </row>
     <row r="43" spans="1:1">
-      <c r="A43" s="4"/>
+      <c r="A43" s="5"/>
     </row>
     <row r="44" spans="1:1">
-      <c r="A44" s="4"/>
+      <c r="A44" s="5"/>
     </row>
     <row r="45" spans="1:1">
-      <c r="A45" s="4"/>
+      <c r="A45" s="5"/>
     </row>
     <row r="46" spans="1:1">
-      <c r="A46" s="4"/>
+      <c r="A46" s="5"/>
     </row>
     <row r="47" spans="1:1">
-      <c r="A47" s="4"/>
+      <c r="A47" s="5"/>
     </row>
     <row r="48" spans="1:1">
-      <c r="A48" s="4"/>
+      <c r="A48" s="5"/>
     </row>
     <row r="49" spans="1:1">
-      <c r="A49" s="4"/>
+      <c r="A49" s="5"/>
     </row>
     <row r="50" spans="1:1">
-      <c r="A50" s="4"/>
+      <c r="A50" s="5"/>
     </row>
     <row r="51" spans="1:1">
-      <c r="A51" s="4"/>
+      <c r="A51" s="5"/>
     </row>
     <row r="52" spans="1:1">
-      <c r="A52" s="4"/>
+      <c r="A52" s="5"/>
     </row>
     <row r="53" spans="1:1">
-      <c r="A53" s="4"/>
+      <c r="A53" s="5"/>
     </row>
     <row r="54" spans="1:1">
-      <c r="A54" s="4"/>
+      <c r="A54" s="5"/>
     </row>
     <row r="55" spans="1:1">
-      <c r="A55" s="4"/>
+      <c r="A55" s="5"/>
     </row>
     <row r="56" spans="1:1">
-      <c r="A56" s="4"/>
+      <c r="A56" s="5"/>
     </row>
     <row r="57" spans="1:1">
-      <c r="A57" s="4"/>
+      <c r="A57" s="5"/>
     </row>
     <row r="58" spans="1:1">
-      <c r="A58" s="4"/>
+      <c r="A58" s="5"/>
     </row>
     <row r="59" spans="1:1">
-      <c r="A59" s="4"/>
+      <c r="A59" s="5"/>
     </row>
     <row r="60" spans="1:1">
-      <c r="A60" s="4"/>
+      <c r="A60" s="5"/>
     </row>
     <row r="61" spans="1:1">
-      <c r="A61" s="4"/>
+      <c r="A61" s="5"/>
     </row>
     <row r="62" spans="1:1">
-      <c r="A62" s="4"/>
+      <c r="A62" s="5"/>
     </row>
     <row r="63" spans="1:1">
-      <c r="A63" s="4"/>
+      <c r="A63" s="5"/>
     </row>
     <row r="64" spans="1:1">
-      <c r="A64" s="4"/>
+      <c r="A64" s="5"/>
     </row>
     <row r="65" spans="1:1">
-      <c r="A65" s="4"/>
+      <c r="A65" s="5"/>
     </row>
     <row r="66" spans="1:1">
-      <c r="A66" s="4"/>
+      <c r="A66" s="5"/>
     </row>
     <row r="67" spans="1:1">
-      <c r="A67" s="4"/>
+      <c r="A67" s="5"/>
     </row>
     <row r="68" spans="1:1">
-      <c r="A68" s="4"/>
+      <c r="A68" s="5"/>
     </row>
     <row r="69" spans="1:1">
-      <c r="A69" s="4"/>
+      <c r="A69" s="5"/>
     </row>
     <row r="70" spans="1:1">
-      <c r="A70" s="4"/>
+      <c r="A70" s="5"/>
     </row>
     <row r="71" spans="1:1">
-      <c r="A71" s="4"/>
+      <c r="A71" s="5"/>
     </row>
     <row r="72" spans="1:1">
-      <c r="A72" s="4"/>
+      <c r="A72" s="5"/>
     </row>
     <row r="73" spans="1:1">
-      <c r="A73" s="4"/>
+      <c r="A73" s="5"/>
     </row>
     <row r="74" spans="1:1">
-      <c r="A74" s="4"/>
+      <c r="A74" s="5"/>
     </row>
     <row r="75" spans="1:1">
-      <c r="A75" s="4"/>
+      <c r="A75" s="5"/>
     </row>
     <row r="76" spans="1:1">
-      <c r="A76" s="4"/>
+      <c r="A76" s="5"/>
     </row>
     <row r="77" spans="1:1">
-      <c r="A77" s="4"/>
+      <c r="A77" s="5"/>
     </row>
     <row r="78" spans="1:1">
-      <c r="A78" s="4"/>
+      <c r="A78" s="5"/>
     </row>
     <row r="79" spans="1:1">
-      <c r="A79" s="4"/>
+      <c r="A79" s="5"/>
     </row>
     <row r="80" spans="1:1">
-      <c r="A80" s="4"/>
+      <c r="A80" s="5"/>
     </row>
     <row r="81" spans="1:1">
-      <c r="A81" s="4"/>
+      <c r="A81" s="5"/>
     </row>
     <row r="82" spans="1:1">
-      <c r="A82" s="4"/>
+      <c r="A82" s="5"/>
     </row>
     <row r="83" spans="1:1">
-      <c r="A83" s="4"/>
+      <c r="A83" s="5"/>
     </row>
     <row r="84" spans="1:1">
-      <c r="A84" s="4"/>
+      <c r="A84" s="5"/>
     </row>
     <row r="85" spans="1:1">
-      <c r="A85" s="4"/>
+      <c r="A85" s="5"/>
     </row>
     <row r="86" spans="1:1">
-      <c r="A86" s="4"/>
+      <c r="A86" s="5"/>
     </row>
     <row r="87" spans="1:1">
-      <c r="A87" s="4"/>
+      <c r="A87" s="5"/>
     </row>
     <row r="88" spans="1:1">
-      <c r="A88" s="4"/>
+      <c r="A88" s="5"/>
     </row>
     <row r="89" spans="1:1">
-      <c r="A89" s="4"/>
+      <c r="A89" s="5"/>
     </row>
     <row r="90" spans="1:1">
-      <c r="A90" s="4"/>
+      <c r="A90" s="5"/>
     </row>
     <row r="91" spans="1:1">
-      <c r="A91" s="4"/>
+      <c r="A91" s="5"/>
     </row>
     <row r="92" spans="1:1">
-      <c r="A92" s="4"/>
+      <c r="A92" s="5"/>
     </row>
     <row r="93" spans="1:1">
-      <c r="A93" s="4"/>
+      <c r="A93" s="5"/>
     </row>
     <row r="94" spans="1:1">
-      <c r="A94" s="4"/>
+      <c r="A94" s="5"/>
     </row>
     <row r="95" spans="1:1">
-      <c r="A95" s="4"/>
+      <c r="A95" s="5"/>
     </row>
     <row r="96" spans="1:1">
-      <c r="A96" s="4"/>
+      <c r="A96" s="5"/>
     </row>
     <row r="97" spans="1:1">
-      <c r="A97" s="4"/>
+      <c r="A97" s="5"/>
     </row>
     <row r="98" spans="1:1">
-      <c r="A98" s="4"/>
+      <c r="A98" s="5"/>
     </row>
     <row r="99" spans="1:1">
-      <c r="A99" s="4"/>
+      <c r="A99" s="5"/>
     </row>
     <row r="100" spans="1:1">
-      <c r="A100" s="4"/>
+      <c r="A100" s="5"/>
     </row>
     <row r="101" spans="1:1">
-      <c r="A101" s="4"/>
+      <c r="A101" s="5"/>
     </row>
     <row r="102" spans="1:1">
-      <c r="A102" s="4"/>
+      <c r="A102" s="5"/>
     </row>
     <row r="103" spans="1:1">
-      <c r="A103" s="4"/>
+      <c r="A103" s="5"/>
     </row>
     <row r="104" spans="1:1">
-      <c r="A104" s="4"/>
+      <c r="A104" s="5"/>
     </row>
     <row r="105" spans="1:1">
-      <c r="A105" s="4"/>
+      <c r="A105" s="5"/>
     </row>
     <row r="106" spans="1:1">
-      <c r="A106" s="4"/>
+      <c r="A106" s="5"/>
     </row>
     <row r="107" spans="1:1">
-      <c r="A107" s="4"/>
+      <c r="A107" s="5"/>
     </row>
     <row r="108" spans="1:1">
-      <c r="A108" s="4"/>
+      <c r="A108" s="5"/>
     </row>
     <row r="109" spans="1:1">
-      <c r="A109" s="4"/>
+      <c r="A109" s="5"/>
     </row>
     <row r="110" spans="1:1">
-      <c r="A110" s="4"/>
+      <c r="A110" s="5"/>
     </row>
     <row r="111" spans="1:1">
-      <c r="A111" s="4"/>
+      <c r="A111" s="5"/>
     </row>
     <row r="112" spans="1:1">
-      <c r="A112" s="4"/>
+      <c r="A112" s="5"/>
     </row>
     <row r="113" spans="1:1">
-      <c r="A113" s="4"/>
+      <c r="A113" s="5"/>
     </row>
     <row r="114" spans="1:1">
-      <c r="A114" s="4"/>
+      <c r="A114" s="5"/>
     </row>
     <row r="115" spans="1:1">
-      <c r="A115" s="4"/>
+      <c r="A115" s="5"/>
     </row>
     <row r="116" spans="1:1">
-      <c r="A116" s="4"/>
+      <c r="A116" s="5"/>
     </row>
     <row r="117" spans="1:1">
-      <c r="A117" s="4"/>
+      <c r="A117" s="5"/>
     </row>
     <row r="118" spans="1:1">
-      <c r="A118" s="4"/>
+      <c r="A118" s="5"/>
     </row>
     <row r="119" spans="1:1">
-      <c r="A119" s="4"/>
+      <c r="A119" s="5"/>
     </row>
     <row r="120" spans="1:1">
-      <c r="A120" s="4"/>
+      <c r="A120" s="5"/>
     </row>
     <row r="121" spans="1:1">
-      <c r="A121" s="4"/>
+      <c r="A121" s="5"/>
     </row>
     <row r="122" spans="1:1">
-      <c r="A122" s="4"/>
+      <c r="A122" s="5"/>
     </row>
     <row r="123" spans="1:1">
-      <c r="A123" s="4"/>
+      <c r="A123" s="5"/>
     </row>
     <row r="124" spans="1:1">
-      <c r="A124" s="4"/>
+      <c r="A124" s="5"/>
     </row>
     <row r="125" spans="1:1">
-      <c r="A125" s="4"/>
+      <c r="A125" s="5"/>
     </row>
     <row r="126" spans="1:1">
-      <c r="A126" s="4"/>
+      <c r="A126" s="5"/>
     </row>
     <row r="127" spans="1:1">
-      <c r="A127" s="4"/>
+      <c r="A127" s="5"/>
     </row>
     <row r="128" spans="1:1">
-      <c r="A128" s="4"/>
+      <c r="A128" s="5"/>
     </row>
     <row r="129" spans="1:1">
-      <c r="A129" s="4"/>
+      <c r="A129" s="5"/>
     </row>
     <row r="130" spans="1:1">
-      <c r="A130" s="4"/>
+      <c r="A130" s="5"/>
     </row>
     <row r="131" spans="1:1">
-      <c r="A131" s="4"/>
+      <c r="A131" s="5"/>
     </row>
     <row r="132" spans="1:1">
-      <c r="A132" s="4"/>
+      <c r="A132" s="5"/>
     </row>
     <row r="133" spans="1:1">
-      <c r="A133" s="4"/>
+      <c r="A133" s="5"/>
     </row>
     <row r="134" spans="1:1">
-      <c r="A134" s="4"/>
+      <c r="A134" s="5"/>
     </row>
     <row r="135" spans="1:1">
-      <c r="A135" s="4"/>
+      <c r="A135" s="5"/>
     </row>
     <row r="136" spans="1:1">
-      <c r="A136" s="4"/>
+      <c r="A136" s="5"/>
     </row>
     <row r="137" spans="1:1">
-      <c r="A137" s="4"/>
+      <c r="A137" s="5"/>
     </row>
     <row r="138" spans="1:1">
-      <c r="A138" s="4"/>
+      <c r="A138" s="5"/>
     </row>
     <row r="139" spans="1:1">
-      <c r="A139" s="4"/>
+      <c r="A139" s="5"/>
     </row>
     <row r="140" spans="1:1">
-      <c r="A140" s="4"/>
+      <c r="A140" s="5"/>
     </row>
     <row r="141" spans="1:1">
-      <c r="A141" s="4"/>
+      <c r="A141" s="5"/>
     </row>
     <row r="142" spans="1:1">
-      <c r="A142" s="4"/>
+      <c r="A142" s="5"/>
     </row>
     <row r="143" spans="1:1">
-      <c r="A143" s="4"/>
+      <c r="A143" s="5"/>
     </row>
     <row r="144" spans="1:1">
-      <c r="A144" s="4"/>
+      <c r="A144" s="5"/>
     </row>
     <row r="145" spans="1:1">
-      <c r="A145" s="4"/>
+      <c r="A145" s="5"/>
     </row>
     <row r="146" spans="1:1">
-      <c r="A146" s="4"/>
+      <c r="A146" s="5"/>
     </row>
     <row r="147" spans="1:1">
-      <c r="A147" s="4"/>
+      <c r="A147" s="5"/>
     </row>
     <row r="148" spans="1:1">
-      <c r="A148" s="4"/>
+      <c r="A148" s="5"/>
     </row>
     <row r="149" spans="1:1">
-      <c r="A149" s="4"/>
+      <c r="A149" s="5"/>
     </row>
     <row r="150" spans="1:1">
-      <c r="A150" s="4"/>
+      <c r="A150" s="5"/>
     </row>
     <row r="151" spans="1:1">
-      <c r="A151" s="4"/>
+      <c r="A151" s="5"/>
     </row>
     <row r="152" spans="1:1">
-      <c r="A152" s="4"/>
+      <c r="A152" s="5"/>
     </row>
     <row r="153" spans="1:1">
-      <c r="A153" s="4"/>
+      <c r="A153" s="5"/>
     </row>
     <row r="154" spans="1:1">
-      <c r="A154" s="4"/>
+      <c r="A154" s="5"/>
     </row>
     <row r="155" spans="1:1">
-      <c r="A155" s="4"/>
+      <c r="A155" s="5"/>
     </row>
     <row r="156" spans="1:1">
-      <c r="A156" s="4"/>
+      <c r="A156" s="5"/>
     </row>
     <row r="157" spans="1:1">
-      <c r="A157" s="4"/>
+      <c r="A157" s="5"/>
     </row>
     <row r="158" spans="1:1">
-      <c r="A158" s="4"/>
+      <c r="A158" s="5"/>
     </row>
     <row r="159" spans="1:1">
-      <c r="A159" s="4"/>
+      <c r="A159" s="5"/>
     </row>
     <row r="160" spans="1:1">
-      <c r="A160" s="4"/>
+      <c r="A160" s="5"/>
     </row>
     <row r="161" spans="1:1">
-      <c r="A161" s="4"/>
+      <c r="A161" s="5"/>
     </row>
     <row r="162" spans="1:1">
-      <c r="A162" s="4"/>
+      <c r="A162" s="5"/>
     </row>
     <row r="163" spans="1:1">
-      <c r="A163" s="4"/>
+      <c r="A163" s="5"/>
     </row>
     <row r="164" spans="1:1">
-      <c r="A164" s="4"/>
+      <c r="A164" s="5"/>
     </row>
     <row r="165" spans="1:1">
-      <c r="A165" s="4"/>
+      <c r="A165" s="5"/>
     </row>
     <row r="166" spans="1:1">
-      <c r="A166" s="4"/>
+      <c r="A166" s="5"/>
     </row>
     <row r="167" spans="1:1">
-      <c r="A167" s="4"/>
+      <c r="A167" s="5"/>
     </row>
     <row r="168" spans="1:1">
-      <c r="A168" s="4"/>
+      <c r="A168" s="5"/>
     </row>
     <row r="169" spans="1:1">
-      <c r="A169" s="4"/>
+      <c r="A169" s="5"/>
     </row>
     <row r="170" spans="1:1">
-      <c r="A170" s="4"/>
+      <c r="A170" s="5"/>
     </row>
     <row r="171" spans="1:1">
-      <c r="A171" s="4"/>
+      <c r="A171" s="5"/>
     </row>
     <row r="172" spans="1:1">
-      <c r="A172" s="4"/>
+      <c r="A172" s="5"/>
     </row>
     <row r="173" spans="1:1">
-      <c r="A173" s="4"/>
+      <c r="A173" s="5"/>
     </row>
     <row r="174" spans="1:1">
-      <c r="A174" s="4"/>
+      <c r="A174" s="5"/>
     </row>
     <row r="175" spans="1:1">
-      <c r="A175" s="4"/>
+      <c r="A175" s="5"/>
     </row>
     <row r="176" spans="1:1">
-      <c r="A176" s="4"/>
+      <c r="A176" s="5"/>
     </row>
     <row r="177" spans="1:1">
-      <c r="A177" s="4"/>
+      <c r="A177" s="5"/>
     </row>
     <row r="178" spans="1:1">
-      <c r="A178" s="4"/>
+      <c r="A178" s="5"/>
     </row>
     <row r="179" spans="1:1">
-      <c r="A179" s="4"/>
+      <c r="A179" s="5"/>
     </row>
     <row r="180" spans="1:1">
-      <c r="A180" s="4"/>
+      <c r="A180" s="5"/>
     </row>
     <row r="181" spans="1:1">
-      <c r="A181" s="4"/>
+      <c r="A181" s="5"/>
     </row>
     <row r="182" spans="1:1">
-      <c r="A182" s="4"/>
+      <c r="A182" s="5"/>
     </row>
     <row r="183" spans="1:1">
-      <c r="A183" s="4"/>
+      <c r="A183" s="5"/>
     </row>
     <row r="184" spans="1:1">
-      <c r="A184" s="4"/>
+      <c r="A184" s="5"/>
     </row>
     <row r="185" spans="1:1">
-      <c r="A185" s="4"/>
+      <c r="A185" s="5"/>
     </row>
     <row r="186" spans="1:1">
-      <c r="A186" s="4"/>
+      <c r="A186" s="5"/>
     </row>
     <row r="187" spans="1:1">
-      <c r="A187" s="4"/>
+      <c r="A187" s="5"/>
     </row>
     <row r="188" spans="1:1">
-      <c r="A188" s="4"/>
+      <c r="A188" s="5"/>
     </row>
     <row r="189" spans="1:1">
-      <c r="A189" s="4"/>
+      <c r="A189" s="5"/>
     </row>
     <row r="190" spans="1:1">
-      <c r="A190" s="4"/>
+      <c r="A190" s="5"/>
     </row>
     <row r="191" spans="1:1">
-      <c r="A191" s="4"/>
+      <c r="A191" s="5"/>
     </row>
     <row r="192" spans="1:1">
-      <c r="A192" s="4"/>
+      <c r="A192" s="5"/>
     </row>
     <row r="193" spans="1:1">
-      <c r="A193" s="4"/>
+      <c r="A193" s="5"/>
     </row>
     <row r="194" spans="1:1">
-      <c r="A194" s="4"/>
+      <c r="A194" s="5"/>
     </row>
     <row r="195" spans="1:1">
-      <c r="A195" s="4"/>
+      <c r="A195" s="5"/>
     </row>
     <row r="196" spans="1:1">
-      <c r="A196" s="4"/>
+      <c r="A196" s="5"/>
     </row>
     <row r="197" spans="1:1">
-      <c r="A197" s="4"/>
+      <c r="A197" s="5"/>
     </row>
     <row r="198" spans="1:1">
-      <c r="A198" s="4"/>
+      <c r="A198" s="5"/>
     </row>
     <row r="199" spans="1:1">
-      <c r="A199" s="4"/>
+      <c r="A199" s="5"/>
     </row>
     <row r="200" spans="1:1">
-      <c r="A200" s="4"/>
+      <c r="A200" s="5"/>
     </row>
     <row r="201" spans="1:1">
-      <c r="A201" s="4"/>
+      <c r="A201" s="5"/>
     </row>
     <row r="202" spans="1:1">
-      <c r="A202" s="4"/>
+      <c r="A202" s="5"/>
     </row>
     <row r="203" spans="1:1">
-      <c r="A203" s="4"/>
+      <c r="A203" s="5"/>
     </row>
     <row r="204" spans="1:1">
-      <c r="A204" s="4"/>
+      <c r="A204" s="5"/>
     </row>
     <row r="205" spans="1:1">
-      <c r="A205" s="4"/>
+      <c r="A205" s="5"/>
     </row>
     <row r="206" spans="1:1">
-      <c r="A206" s="4"/>
+      <c r="A206" s="5"/>
     </row>
     <row r="207" spans="1:1">
-      <c r="A207" s="4"/>
+      <c r="A207" s="5"/>
     </row>
     <row r="208" spans="1:1">
-      <c r="A208" s="4"/>
+      <c r="A208" s="5"/>
     </row>
     <row r="209" spans="1:1">
-      <c r="A209" s="4"/>
+      <c r="A209" s="5"/>
     </row>
     <row r="210" spans="1:1">
-      <c r="A210" s="4"/>
+      <c r="A210" s="5"/>
     </row>
     <row r="211" spans="1:1">
-      <c r="A211" s="4"/>
+      <c r="A211" s="5"/>
     </row>
     <row r="212" spans="1:1">
-      <c r="A212" s="4"/>
+      <c r="A212" s="5"/>
     </row>
     <row r="213" spans="1:1">
-      <c r="A213" s="4"/>
+      <c r="A213" s="5"/>
     </row>
     <row r="214" spans="1:1">
-      <c r="A214" s="4"/>
+      <c r="A214" s="5"/>
     </row>
     <row r="215" spans="1:1">
-      <c r="A215" s="4"/>
+      <c r="A215" s="5"/>
     </row>
     <row r="216" spans="1:1">
-      <c r="A216" s="4"/>
+      <c r="A216" s="5"/>
     </row>
     <row r="217" spans="1:1">
-      <c r="A217" s="4"/>
+      <c r="A217" s="5"/>
     </row>
     <row r="218" spans="1:1">
-      <c r="A218" s="4"/>
+      <c r="A218" s="5"/>
     </row>
     <row r="219" spans="1:1">
-      <c r="A219" s="4"/>
+      <c r="A219" s="5"/>
     </row>
     <row r="220" spans="1:1">
-      <c r="A220" s="4"/>
+      <c r="A220" s="5"/>
     </row>
     <row r="221" spans="1:1">
-      <c r="A221" s="4"/>
+      <c r="A221" s="5"/>
     </row>
     <row r="222" spans="1:1">
-      <c r="A222" s="4"/>
+      <c r="A222" s="5"/>
     </row>
     <row r="223" spans="1:1">
-      <c r="A223" s="4"/>
+      <c r="A223" s="5"/>
     </row>
     <row r="224" spans="1:1">
-      <c r="A224" s="4"/>
+      <c r="A224" s="5"/>
     </row>
     <row r="225" spans="1:1">
-      <c r="A225" s="4"/>
+      <c r="A225" s="5"/>
     </row>
     <row r="226" spans="1:1">
-      <c r="A226" s="4"/>
+      <c r="A226" s="5"/>
     </row>
     <row r="227" spans="1:1">
-      <c r="A227" s="4"/>
+      <c r="A227" s="5"/>
     </row>
     <row r="228" spans="1:1">
-      <c r="A228" s="4"/>
+      <c r="A228" s="5"/>
     </row>
     <row r="229" spans="1:1">
-      <c r="A229" s="4"/>
+      <c r="A229" s="5"/>
     </row>
     <row r="230" spans="1:1">
-      <c r="A230" s="4"/>
+      <c r="A230" s="5"/>
     </row>
     <row r="231" spans="1:1">
-      <c r="A231" s="4"/>
+      <c r="A231" s="5"/>
     </row>
     <row r="232" spans="1:1">
-      <c r="A232" s="4"/>
+      <c r="A232" s="5"/>
     </row>
     <row r="233" spans="1:1">
-      <c r="A233" s="4"/>
+      <c r="A233" s="5"/>
     </row>
     <row r="234" spans="1:1">
-      <c r="A234" s="4"/>
+      <c r="A234" s="5"/>
     </row>
     <row r="235" spans="1:1">
-      <c r="A235" s="4"/>
+      <c r="A235" s="5"/>
     </row>
     <row r="236" spans="1:1">
-      <c r="A236" s="4"/>
+      <c r="A236" s="5"/>
     </row>
     <row r="237" spans="1:1">
-      <c r="A237" s="4"/>
+      <c r="A237" s="5"/>
     </row>
     <row r="238" spans="1:1">
-      <c r="A238" s="4"/>
+      <c r="A238" s="5"/>
     </row>
     <row r="239" spans="1:1">
-      <c r="A239" s="4"/>
+      <c r="A239" s="5"/>
     </row>
     <row r="240" spans="1:1">
-      <c r="A240" s="4"/>
+      <c r="A240" s="5"/>
     </row>
     <row r="241" spans="1:1">
-      <c r="A241" s="4"/>
+      <c r="A241" s="5"/>
     </row>
     <row r="242" spans="1:1">
-      <c r="A242" s="4"/>
+      <c r="A242" s="5"/>
     </row>
     <row r="243" spans="1:1">
-      <c r="A243" s="4"/>
+      <c r="A243" s="5"/>
     </row>
     <row r="244" spans="1:1">
-      <c r="A244" s="4"/>
+      <c r="A244" s="5"/>
     </row>
     <row r="245" spans="1:1">
-      <c r="A245" s="4"/>
+      <c r="A245" s="5"/>
     </row>
     <row r="246" spans="1:1">
-      <c r="A246" s="4"/>
+      <c r="A246" s="5"/>
     </row>
     <row r="247" spans="1:1">
-      <c r="A247" s="4"/>
+      <c r="A247" s="5"/>
     </row>
     <row r="248" spans="1:1">
-      <c r="A248" s="4"/>
+      <c r="A248" s="5"/>
     </row>
     <row r="249" spans="1:1">
-      <c r="A249" s="4"/>
+      <c r="A249" s="5"/>
     </row>
     <row r="250" spans="1:1">
-      <c r="A250" s="4"/>
+      <c r="A250" s="5"/>
     </row>
     <row r="251" spans="1:1">
-      <c r="A251" s="4"/>
+      <c r="A251" s="5"/>
     </row>
     <row r="252" spans="1:1">
-      <c r="A252" s="4"/>
+      <c r="A252" s="5"/>
     </row>
     <row r="253" spans="1:1">
-      <c r="A253" s="4"/>
+      <c r="A253" s="5"/>
     </row>
     <row r="254" spans="1:1">
-      <c r="A254" s="4"/>
+      <c r="A254" s="5"/>
     </row>
     <row r="255" spans="1:1">
-      <c r="A255" s="4"/>
+      <c r="A255" s="5"/>
     </row>
     <row r="256" spans="1:1">
-      <c r="A256" s="4"/>
+      <c r="A256" s="5"/>
     </row>
     <row r="257" spans="1:1">
-      <c r="A257" s="4"/>
+      <c r="A257" s="5"/>
     </row>
     <row r="258" spans="1:1">
-      <c r="A258" s="4"/>
+      <c r="A258" s="5"/>
     </row>
     <row r="259" spans="1:1">
-      <c r="A259" s="4"/>
+      <c r="A259" s="5"/>
     </row>
     <row r="260" spans="1:1">
-      <c r="A260" s="4"/>
+      <c r="A260" s="5"/>
     </row>
     <row r="261" spans="1:1">
-      <c r="A261" s="4"/>
+      <c r="A261" s="5"/>
     </row>
     <row r="262" spans="1:1">
-      <c r="A262" s="4"/>
+      <c r="A262" s="5"/>
     </row>
     <row r="263" spans="1:1">
-      <c r="A263" s="4"/>
+      <c r="A263" s="5"/>
     </row>
     <row r="264" spans="1:1">
-      <c r="A264" s="4"/>
+      <c r="A264" s="5"/>
     </row>
     <row r="265" spans="1:1">
-      <c r="A265" s="4"/>
+      <c r="A265" s="5"/>
     </row>
     <row r="266" spans="1:1">
-      <c r="A266" s="4"/>
+      <c r="A266" s="5"/>
     </row>
     <row r="267" spans="1:1">
-      <c r="A267" s="4"/>
+      <c r="A267" s="5"/>
     </row>
     <row r="268" spans="1:1">
-      <c r="A268" s="4"/>
+      <c r="A268" s="5"/>
     </row>
     <row r="269" spans="1:1">
-      <c r="A269" s="4"/>
+      <c r="A269" s="5"/>
     </row>
     <row r="270" spans="1:1">
-      <c r="A270" s="4"/>
+      <c r="A270" s="5"/>
     </row>
     <row r="271" spans="1:1">
-      <c r="A271" s="4"/>
+      <c r="A271" s="5"/>
     </row>
     <row r="272" spans="1:1">
-      <c r="A272" s="4"/>
+      <c r="A272" s="5"/>
     </row>
     <row r="273" spans="1:1">
-      <c r="A273" s="4"/>
+      <c r="A273" s="5"/>
     </row>
     <row r="274" spans="1:1">
-      <c r="A274" s="4"/>
+      <c r="A274" s="5"/>
     </row>
     <row r="275" spans="1:1">
-      <c r="A275" s="4"/>
+      <c r="A275" s="5"/>
     </row>
     <row r="276" spans="1:1">
-      <c r="A276" s="4"/>
+      <c r="A276" s="5"/>
     </row>
     <row r="277" spans="1:1">
-      <c r="A277" s="4"/>
+      <c r="A277" s="5"/>
     </row>
     <row r="278" spans="1:1">
-      <c r="A278" s="4"/>
+      <c r="A278" s="5"/>
     </row>
     <row r="279" spans="1:1">
-      <c r="A279" s="4"/>
+      <c r="A279" s="5"/>
     </row>
     <row r="280" spans="1:1">
-      <c r="A280" s="4"/>
+      <c r="A280" s="5"/>
     </row>
     <row r="281" spans="1:1">
-      <c r="A281" s="4"/>
+      <c r="A281" s="5"/>
     </row>
     <row r="282" spans="1:1">
-      <c r="A282" s="4"/>
+      <c r="A282" s="5"/>
     </row>
     <row r="283" spans="1:1">
-      <c r="A283" s="4"/>
+      <c r="A283" s="5"/>
     </row>
     <row r="284" spans="1:1">
-      <c r="A284" s="4"/>
+      <c r="A284" s="5"/>
     </row>
     <row r="285" spans="1:1">
-      <c r="A285" s="4"/>
+      <c r="A285" s="5"/>
     </row>
     <row r="286" spans="1:1">
-      <c r="A286" s="4"/>
+      <c r="A286" s="5"/>
     </row>
     <row r="287" spans="1:1">
-      <c r="A287" s="4"/>
+      <c r="A287" s="5"/>
     </row>
     <row r="288" spans="1:1">
-      <c r="A288" s="4"/>
+      <c r="A288" s="5"/>
     </row>
     <row r="289" spans="1:1">
-      <c r="A289" s="4"/>
+      <c r="A289" s="5"/>
     </row>
     <row r="290" spans="1:1">
-      <c r="A290" s="4"/>
+      <c r="A290" s="5"/>
     </row>
     <row r="291" spans="1:1">
-      <c r="A291" s="4"/>
+      <c r="A291" s="5"/>
     </row>
     <row r="292" spans="1:1">
-      <c r="A292" s="4"/>
+      <c r="A292" s="5"/>
     </row>
     <row r="293" spans="1:1">
-      <c r="A293" s="4"/>
+      <c r="A293" s="5"/>
     </row>
     <row r="294" spans="1:1">
-      <c r="A294" s="4"/>
+      <c r="A294" s="5"/>
     </row>
     <row r="295" spans="1:1">
-      <c r="A295" s="4"/>
+      <c r="A295" s="5"/>
     </row>
     <row r="296" spans="1:1">
-      <c r="A296" s="4"/>
+      <c r="A296" s="5"/>
     </row>
     <row r="297" spans="1:1">
-      <c r="A297" s="4"/>
+      <c r="A297" s="5"/>
     </row>
     <row r="298" spans="1:1">
-      <c r="A298" s="4"/>
+      <c r="A298" s="5"/>
     </row>
     <row r="299" spans="1:1">
-      <c r="A299" s="4"/>
+      <c r="A299" s="5"/>
     </row>
     <row r="300" spans="1:1">
-      <c r="A300" s="4"/>
+      <c r="A300" s="5"/>
     </row>
     <row r="301" spans="1:1">
-      <c r="A301" s="4"/>
+      <c r="A301" s="5"/>
     </row>
     <row r="302" spans="1:1">
-      <c r="A302" s="4"/>
+      <c r="A302" s="5"/>
     </row>
     <row r="303" spans="1:1">
-      <c r="A303" s="4"/>
+      <c r="A303" s="5"/>
     </row>
     <row r="304" spans="1:1">
-      <c r="A304" s="4"/>
+      <c r="A304" s="5"/>
     </row>
     <row r="305" spans="1:1">
-      <c r="A305" s="4"/>
+      <c r="A305" s="5"/>
     </row>
     <row r="306" spans="1:1">
-      <c r="A306" s="4"/>
+      <c r="A306" s="5"/>
     </row>
     <row r="307" spans="1:1">
-      <c r="A307" s="4"/>
+      <c r="A307" s="5"/>
     </row>
     <row r="308" spans="1:1">
-      <c r="A308" s="4"/>
+      <c r="A308" s="5"/>
     </row>
     <row r="309" spans="1:1">
-      <c r="A309" s="4"/>
+      <c r="A309" s="5"/>
     </row>
     <row r="310" spans="1:1">
-      <c r="A310" s="4"/>
+      <c r="A310" s="5"/>
     </row>
     <row r="311" spans="1:1">
-      <c r="A311" s="4"/>
+      <c r="A311" s="5"/>
     </row>
     <row r="312" spans="1:1">
-      <c r="A312" s="4"/>
+      <c r="A312" s="5"/>
     </row>
     <row r="313" spans="1:1">
-      <c r="A313" s="4"/>
+      <c r="A313" s="5"/>
     </row>
     <row r="314" spans="1:1">
-      <c r="A314" s="4"/>
+      <c r="A314" s="5"/>
     </row>
     <row r="315" spans="1:1">
-      <c r="A315" s="4"/>
+      <c r="A315" s="5"/>
     </row>
     <row r="316" spans="1:1">
-      <c r="A316" s="4"/>
+      <c r="A316" s="5"/>
     </row>
     <row r="317" spans="1:1">
-      <c r="A317" s="4"/>
+      <c r="A317" s="5"/>
     </row>
     <row r="318" spans="1:1">
-      <c r="A318" s="4"/>
+      <c r="A318" s="5"/>
     </row>
     <row r="319" spans="1:1">
-      <c r="A319" s="4"/>
+      <c r="A319" s="5"/>
     </row>
     <row r="320" spans="1:1">
-      <c r="A320" s="4"/>
+      <c r="A320" s="5"/>
     </row>
     <row r="321" spans="1:1">
-      <c r="A321" s="4"/>
+      <c r="A321" s="5"/>
     </row>
     <row r="322" spans="1:1">
-      <c r="A322" s="4"/>
+      <c r="A322" s="5"/>
     </row>
     <row r="323" spans="1:1">
-      <c r="A323" s="4"/>
+      <c r="A323" s="5"/>
     </row>
     <row r="324" spans="1:1">
-      <c r="A324" s="4"/>
+      <c r="A324" s="5"/>
     </row>
     <row r="325" spans="1:1">
-      <c r="A325" s="4"/>
+      <c r="A325" s="5"/>
     </row>
     <row r="326" spans="1:1">
-      <c r="A326" s="4"/>
+      <c r="A326" s="5"/>
     </row>
     <row r="327" spans="1:1">
-      <c r="A327" s="4"/>
+      <c r="A327" s="5"/>
     </row>
     <row r="328" spans="1:1">
-      <c r="A328" s="4"/>
+      <c r="A328" s="5"/>
     </row>
     <row r="329" spans="1:1">
-      <c r="A329" s="4"/>
+      <c r="A329" s="5"/>
     </row>
     <row r="330" spans="1:1">
-      <c r="A330" s="4"/>
+      <c r="A330" s="5"/>
     </row>
     <row r="331" spans="1:1">
-      <c r="A331" s="4"/>
+      <c r="A331" s="5"/>
     </row>
     <row r="332" spans="1:1">
-      <c r="A332" s="4"/>
+      <c r="A332" s="5"/>
     </row>
     <row r="333" spans="1:1">
-      <c r="A333" s="4"/>
+      <c r="A333" s="5"/>
     </row>
     <row r="334" spans="1:1">
-      <c r="A334" s="4"/>
+      <c r="A334" s="5"/>
     </row>
     <row r="335" spans="1:1">
-      <c r="A335" s="4"/>
+      <c r="A335" s="5"/>
     </row>
     <row r="336" spans="1:1">
-      <c r="A336" s="4"/>
+      <c r="A336" s="5"/>
     </row>
     <row r="337" spans="1:1">
-      <c r="A337" s="4"/>
+      <c r="A337" s="5"/>
     </row>
     <row r="338" spans="1:1">
-      <c r="A338" s="4"/>
+      <c r="A338" s="5"/>
     </row>
     <row r="339" spans="1:1">
-      <c r="A339" s="4"/>
+      <c r="A339" s="5"/>
     </row>
     <row r="340" spans="1:1">
-      <c r="A340" s="4"/>
+      <c r="A340" s="5"/>
     </row>
     <row r="341" spans="1:1">
-      <c r="A341" s="4"/>
+      <c r="A341" s="5"/>
     </row>
     <row r="342" spans="1:1">
-      <c r="A342" s="4"/>
+      <c r="A342" s="5"/>
     </row>
     <row r="343" spans="1:1">
-      <c r="A343" s="4"/>
+      <c r="A343" s="5"/>
     </row>
     <row r="344" spans="1:1">
-      <c r="A344" s="4"/>
+      <c r="A344" s="5"/>
     </row>
     <row r="345" spans="1:1">
-      <c r="A345" s="4"/>
+      <c r="A345" s="5"/>
     </row>
     <row r="346" spans="1:1">
-      <c r="A346" s="4"/>
+      <c r="A346" s="5"/>
     </row>
     <row r="347" spans="1:1">
-      <c r="A347" s="4"/>
+      <c r="A347" s="5"/>
     </row>
     <row r="348" spans="1:1">
-      <c r="A348" s="4"/>
+      <c r="A348" s="5"/>
     </row>
     <row r="349" spans="1:1">
-      <c r="A349" s="4"/>
+      <c r="A349" s="5"/>
     </row>
     <row r="350" spans="1:1">
-      <c r="A350" s="4"/>
+      <c r="A350" s="5"/>
     </row>
     <row r="351" spans="1:1">
-      <c r="A351" s="4"/>
+      <c r="A351" s="5"/>
     </row>
     <row r="352" spans="1:1">
-      <c r="A352" s="4"/>
+      <c r="A352" s="5"/>
     </row>
     <row r="353" spans="1:1">
-      <c r="A353" s="4"/>
+      <c r="A353" s="5"/>
     </row>
     <row r="354" spans="1:1">
-      <c r="A354" s="4"/>
+      <c r="A354" s="5"/>
     </row>
     <row r="355" spans="1:1">
-      <c r="A355" s="4"/>
+      <c r="A355" s="5"/>
     </row>
     <row r="356" spans="1:1">
-      <c r="A356" s="4"/>
+      <c r="A356" s="5"/>
     </row>
     <row r="357" spans="1:1">
-      <c r="A357" s="4"/>
+      <c r="A357" s="5"/>
     </row>
     <row r="358" spans="1:1">
-      <c r="A358" s="4"/>
+      <c r="A358" s="5"/>
     </row>
     <row r="359" spans="1:1">
-      <c r="A359" s="4"/>
+      <c r="A359" s="5"/>
     </row>
     <row r="360" spans="1:1">
-      <c r="A360" s="4"/>
+      <c r="A360" s="5"/>
     </row>
     <row r="361" spans="1:1">
-      <c r="A361" s="4"/>
+      <c r="A361" s="5"/>
     </row>
     <row r="362" spans="1:1">
-      <c r="A362" s="4"/>
+      <c r="A362" s="5"/>
     </row>
     <row r="363" spans="1:1">
-      <c r="A363" s="4"/>
+      <c r="A363" s="5"/>
     </row>
     <row r="364" spans="1:1">
-      <c r="A364" s="4"/>
+      <c r="A364" s="5"/>
     </row>
     <row r="365" spans="1:1">
-      <c r="A365" s="4"/>
+      <c r="A365" s="5"/>
     </row>
     <row r="366" spans="1:1">
-      <c r="A366" s="4"/>
+      <c r="A366" s="5"/>
     </row>
     <row r="367" spans="1:1">
-      <c r="A367" s="4"/>
+      <c r="A367" s="5"/>
     </row>
     <row r="368" spans="1:1">
-      <c r="A368" s="4"/>
+      <c r="A368" s="5"/>
     </row>
     <row r="369" spans="1:1">
-      <c r="A369" s="4"/>
+      <c r="A369" s="5"/>
     </row>
     <row r="370" spans="1:1">
-      <c r="A370" s="4"/>
+      <c r="A370" s="5"/>
     </row>
     <row r="371" spans="1:1">
-      <c r="A371" s="4"/>
+      <c r="A371" s="5"/>
     </row>
     <row r="372" spans="1:1">
-      <c r="A372" s="4"/>
+      <c r="A372" s="5"/>
     </row>
     <row r="373" spans="1:1">
-      <c r="A373" s="4"/>
+      <c r="A373" s="5"/>
     </row>
     <row r="374" spans="1:1">
-      <c r="A374" s="4"/>
+      <c r="A374" s="5"/>
     </row>
     <row r="375" spans="1:1">
-      <c r="A375" s="4"/>
+      <c r="A375" s="5"/>
     </row>
     <row r="376" spans="1:1">
-      <c r="A376" s="4"/>
+      <c r="A376" s="5"/>
     </row>
     <row r="377" spans="1:1">
-      <c r="A377" s="4"/>
+      <c r="A377" s="5"/>
     </row>
     <row r="378" spans="1:1">
-      <c r="A378" s="4"/>
+      <c r="A378" s="5"/>
     </row>
     <row r="379" spans="1:1">
-      <c r="A379" s="4"/>
+      <c r="A379" s="5"/>
     </row>
     <row r="380" spans="1:1">
-      <c r="A380" s="4"/>
+      <c r="A380" s="5"/>
     </row>
     <row r="381" spans="1:1">
-      <c r="A381" s="4"/>
+      <c r="A381" s="5"/>
     </row>
     <row r="382" spans="1:1">
-      <c r="A382" s="4"/>
+      <c r="A382" s="5"/>
     </row>
     <row r="383" spans="1:1">
-      <c r="A383" s="4"/>
+      <c r="A383" s="5"/>
     </row>
     <row r="384" spans="1:1">
-      <c r="A384" s="4"/>
+      <c r="A384" s="5"/>
     </row>
     <row r="385" spans="1:1">
-      <c r="A385" s="4"/>
+      <c r="A385" s="5"/>
     </row>
     <row r="386" spans="1:1">
-      <c r="A386" s="4"/>
+      <c r="A386" s="5"/>
     </row>
     <row r="387" spans="1:1">
-      <c r="A387" s="4"/>
+      <c r="A387" s="5"/>
     </row>
     <row r="388" spans="1:1">
-      <c r="A388" s="4"/>
+      <c r="A388" s="5"/>
     </row>
     <row r="389" spans="1:1">
-      <c r="A389" s="4"/>
+      <c r="A389" s="5"/>
     </row>
     <row r="390" spans="1:1">
-      <c r="A390" s="4"/>
+      <c r="A390" s="5"/>
     </row>
     <row r="391" spans="1:1">
-      <c r="A391" s="4"/>
+      <c r="A391" s="5"/>
     </row>
     <row r="392" spans="1:1">
-      <c r="A392" s="4"/>
+      <c r="A392" s="5"/>
     </row>
     <row r="393" spans="1:1">
-      <c r="A393" s="4"/>
+      <c r="A393" s="5"/>
     </row>
     <row r="394" spans="1:1">
-      <c r="A394" s="4"/>
+      <c r="A394" s="5"/>
     </row>
     <row r="395" spans="1:1">
-      <c r="A395" s="4"/>
+      <c r="A395" s="5"/>
     </row>
     <row r="396" spans="1:1">
-      <c r="A396" s="4"/>
+      <c r="A396" s="5"/>
     </row>
     <row r="397" spans="1:1">
-      <c r="A397" s="4"/>
+      <c r="A397" s="5"/>
     </row>
     <row r="398" spans="1:1">
-      <c r="A398" s="4"/>
+      <c r="A398" s="5"/>
     </row>
     <row r="399" spans="1:1">
-      <c r="A399" s="4"/>
+      <c r="A399" s="5"/>
     </row>
     <row r="400" spans="1:1">
-      <c r="A400" s="4"/>
+      <c r="A400" s="5"/>
     </row>
     <row r="401" spans="1:1">
-      <c r="A401" s="4"/>
+      <c r="A401" s="5"/>
     </row>
     <row r="402" spans="1:1">
-      <c r="A402" s="4"/>
+      <c r="A402" s="5"/>
     </row>
     <row r="403" spans="1:1">
-      <c r="A403" s="4"/>
+      <c r="A403" s="5"/>
     </row>
     <row r="404" spans="1:1">
-      <c r="A404" s="4"/>
+      <c r="A404" s="5"/>
     </row>
     <row r="405" spans="1:1">
-      <c r="A405" s="4"/>
+      <c r="A405" s="5"/>
     </row>
     <row r="406" spans="1:1">
-      <c r="A406" s="4"/>
+      <c r="A406" s="5"/>
     </row>
     <row r="407" spans="1:1">
-      <c r="A407" s="4"/>
+      <c r="A407" s="5"/>
     </row>
     <row r="408" spans="1:1">
-      <c r="A408" s="4"/>
+      <c r="A408" s="5"/>
     </row>
     <row r="409" spans="1:1">
-      <c r="A409" s="4"/>
+      <c r="A409" s="5"/>
     </row>
     <row r="410" spans="1:1">
-      <c r="A410" s="4"/>
+      <c r="A410" s="5"/>
     </row>
     <row r="411" spans="1:1">
-      <c r="A411" s="4"/>
+      <c r="A411" s="5"/>
     </row>
     <row r="412" spans="1:1">
-      <c r="A412" s="4"/>
+      <c r="A412" s="5"/>
     </row>
     <row r="413" spans="1:1">
-      <c r="A413" s="4"/>
+      <c r="A413" s="5"/>
     </row>
     <row r="414" spans="1:1">
-      <c r="A414" s="4"/>
+      <c r="A414" s="5"/>
     </row>
     <row r="415" spans="1:1">
-      <c r="A415" s="4"/>
+      <c r="A415" s="5"/>
     </row>
     <row r="416" spans="1:1">
-      <c r="A416" s="4"/>
+      <c r="A416" s="5"/>
     </row>
     <row r="417" spans="1:1">
-      <c r="A417" s="4"/>
+      <c r="A417" s="5"/>
     </row>
     <row r="418" spans="1:1">
-      <c r="A418" s="4"/>
+      <c r="A418" s="5"/>
     </row>
     <row r="419" spans="1:1">
-      <c r="A419" s="4"/>
+      <c r="A419" s="5"/>
     </row>
     <row r="420" spans="1:1">
-      <c r="A420" s="4"/>
+      <c r="A420" s="5"/>
     </row>
     <row r="421" spans="1:1">
-      <c r="A421" s="4"/>
+      <c r="A421" s="5"/>
     </row>
     <row r="422" spans="1:1">
-      <c r="A422" s="4"/>
+      <c r="A422" s="5"/>
     </row>
     <row r="423" spans="1:1">
-      <c r="A423" s="4"/>
+      <c r="A423" s="5"/>
     </row>
     <row r="424" spans="1:1">
-      <c r="A424" s="4"/>
+      <c r="A424" s="5"/>
     </row>
     <row r="425" spans="1:1">
-      <c r="A425" s="4"/>
+      <c r="A425" s="5"/>
     </row>
     <row r="426" spans="1:1">
-      <c r="A426" s="4"/>
+      <c r="A426" s="5"/>
     </row>
     <row r="427" spans="1:1">
-      <c r="A427" s="4"/>
+      <c r="A427" s="5"/>
     </row>
     <row r="428" spans="1:1">
-      <c r="A428" s="4"/>
+      <c r="A428" s="5"/>
     </row>
     <row r="429" spans="1:1">
-      <c r="A429" s="4"/>
+      <c r="A429" s="5"/>
     </row>
     <row r="430" spans="1:1">
-      <c r="A430" s="4"/>
+      <c r="A430" s="5"/>
     </row>
     <row r="431" spans="1:1">
-      <c r="A431" s="4"/>
+      <c r="A431" s="5"/>
     </row>
     <row r="432" spans="1:1">
-      <c r="A432" s="4"/>
+      <c r="A432" s="5"/>
     </row>
     <row r="433" spans="1:1">
-      <c r="A433" s="4"/>
+      <c r="A433" s="5"/>
     </row>
   </sheetData>
   <mergeCells count="144">
+    <mergeCell ref="A431:A433"/>
+    <mergeCell ref="A416:A418"/>
+    <mergeCell ref="A419:A421"/>
+    <mergeCell ref="A422:A424"/>
+    <mergeCell ref="A425:A427"/>
+    <mergeCell ref="A428:A430"/>
+    <mergeCell ref="A401:A403"/>
+    <mergeCell ref="A404:A406"/>
+    <mergeCell ref="A407:A409"/>
+    <mergeCell ref="A410:A412"/>
+    <mergeCell ref="A413:A415"/>
+    <mergeCell ref="A386:A388"/>
+    <mergeCell ref="A389:A391"/>
+    <mergeCell ref="A392:A394"/>
+    <mergeCell ref="A395:A397"/>
+    <mergeCell ref="A398:A400"/>
+    <mergeCell ref="A371:A373"/>
+    <mergeCell ref="A374:A376"/>
+    <mergeCell ref="A377:A379"/>
+    <mergeCell ref="A380:A382"/>
+    <mergeCell ref="A383:A385"/>
+    <mergeCell ref="A356:A358"/>
+    <mergeCell ref="A359:A361"/>
+    <mergeCell ref="A362:A364"/>
+    <mergeCell ref="A365:A367"/>
+    <mergeCell ref="A368:A370"/>
+    <mergeCell ref="A341:A343"/>
+    <mergeCell ref="A344:A346"/>
+    <mergeCell ref="A347:A349"/>
+    <mergeCell ref="A350:A352"/>
+    <mergeCell ref="A353:A355"/>
+    <mergeCell ref="A326:A328"/>
+    <mergeCell ref="A329:A331"/>
+    <mergeCell ref="A332:A334"/>
+    <mergeCell ref="A335:A337"/>
+    <mergeCell ref="A338:A340"/>
+    <mergeCell ref="A311:A313"/>
+    <mergeCell ref="A314:A316"/>
+    <mergeCell ref="A317:A319"/>
+    <mergeCell ref="A320:A322"/>
+    <mergeCell ref="A323:A325"/>
+    <mergeCell ref="A296:A298"/>
+    <mergeCell ref="A299:A301"/>
+    <mergeCell ref="A302:A304"/>
+    <mergeCell ref="A305:A307"/>
+    <mergeCell ref="A308:A310"/>
+    <mergeCell ref="A281:A283"/>
+    <mergeCell ref="A284:A286"/>
+    <mergeCell ref="A287:A289"/>
+    <mergeCell ref="A290:A292"/>
+    <mergeCell ref="A293:A295"/>
+    <mergeCell ref="A266:A268"/>
+    <mergeCell ref="A269:A271"/>
+    <mergeCell ref="A272:A274"/>
+    <mergeCell ref="A275:A277"/>
+    <mergeCell ref="A278:A280"/>
+    <mergeCell ref="A251:A253"/>
+    <mergeCell ref="A254:A256"/>
+    <mergeCell ref="A257:A259"/>
+    <mergeCell ref="A260:A262"/>
+    <mergeCell ref="A263:A265"/>
+    <mergeCell ref="A236:A238"/>
+    <mergeCell ref="A239:A241"/>
+    <mergeCell ref="A242:A244"/>
+    <mergeCell ref="A245:A247"/>
+    <mergeCell ref="A248:A250"/>
+    <mergeCell ref="A221:A223"/>
+    <mergeCell ref="A224:A226"/>
+    <mergeCell ref="A227:A229"/>
+    <mergeCell ref="A230:A232"/>
+    <mergeCell ref="A233:A235"/>
+    <mergeCell ref="A206:A208"/>
+    <mergeCell ref="A209:A211"/>
+    <mergeCell ref="A212:A214"/>
+    <mergeCell ref="A215:A217"/>
+    <mergeCell ref="A218:A220"/>
+    <mergeCell ref="A191:A193"/>
+    <mergeCell ref="A194:A196"/>
+    <mergeCell ref="A197:A199"/>
+    <mergeCell ref="A200:A202"/>
+    <mergeCell ref="A203:A205"/>
+    <mergeCell ref="A176:A178"/>
+    <mergeCell ref="A179:A181"/>
+    <mergeCell ref="A182:A184"/>
+    <mergeCell ref="A185:A187"/>
+    <mergeCell ref="A188:A190"/>
+    <mergeCell ref="A161:A163"/>
+    <mergeCell ref="A164:A166"/>
+    <mergeCell ref="A167:A169"/>
+    <mergeCell ref="A170:A172"/>
+    <mergeCell ref="A173:A175"/>
+    <mergeCell ref="A146:A148"/>
+    <mergeCell ref="A149:A151"/>
+    <mergeCell ref="A152:A154"/>
+    <mergeCell ref="A155:A157"/>
+    <mergeCell ref="A158:A160"/>
+    <mergeCell ref="A131:A133"/>
+    <mergeCell ref="A134:A136"/>
+    <mergeCell ref="A137:A139"/>
+    <mergeCell ref="A140:A142"/>
+    <mergeCell ref="A143:A145"/>
+    <mergeCell ref="A116:A118"/>
+    <mergeCell ref="A119:A121"/>
+    <mergeCell ref="A122:A124"/>
+    <mergeCell ref="A125:A127"/>
+    <mergeCell ref="A128:A130"/>
+    <mergeCell ref="A101:A103"/>
+    <mergeCell ref="A104:A106"/>
+    <mergeCell ref="A107:A109"/>
+    <mergeCell ref="A110:A112"/>
+    <mergeCell ref="A113:A115"/>
+    <mergeCell ref="A86:A88"/>
+    <mergeCell ref="A89:A91"/>
+    <mergeCell ref="A92:A94"/>
+    <mergeCell ref="A95:A97"/>
+    <mergeCell ref="A98:A100"/>
+    <mergeCell ref="A71:A73"/>
+    <mergeCell ref="A74:A76"/>
+    <mergeCell ref="A77:A79"/>
+    <mergeCell ref="A80:A82"/>
+    <mergeCell ref="A83:A85"/>
+    <mergeCell ref="A56:A58"/>
+    <mergeCell ref="A59:A61"/>
+    <mergeCell ref="A62:A64"/>
+    <mergeCell ref="A65:A67"/>
+    <mergeCell ref="A68:A70"/>
+    <mergeCell ref="A41:A43"/>
+    <mergeCell ref="A44:A46"/>
+    <mergeCell ref="A47:A49"/>
+    <mergeCell ref="A50:A52"/>
+    <mergeCell ref="A53:A55"/>
     <mergeCell ref="A26:A28"/>
     <mergeCell ref="A29:A31"/>
     <mergeCell ref="A32:A34"/>
@@ -1788,137 +1925,6 @@
     <mergeCell ref="A8:A10"/>
     <mergeCell ref="A11:A13"/>
     <mergeCell ref="A14:A16"/>
-    <mergeCell ref="A56:A58"/>
-    <mergeCell ref="A59:A61"/>
-    <mergeCell ref="A62:A64"/>
-    <mergeCell ref="A65:A67"/>
-    <mergeCell ref="A68:A70"/>
-    <mergeCell ref="A41:A43"/>
-    <mergeCell ref="A44:A46"/>
-    <mergeCell ref="A47:A49"/>
-    <mergeCell ref="A50:A52"/>
-    <mergeCell ref="A53:A55"/>
-    <mergeCell ref="A86:A88"/>
-    <mergeCell ref="A89:A91"/>
-    <mergeCell ref="A92:A94"/>
-    <mergeCell ref="A95:A97"/>
-    <mergeCell ref="A98:A100"/>
-    <mergeCell ref="A71:A73"/>
-    <mergeCell ref="A74:A76"/>
-    <mergeCell ref="A77:A79"/>
-    <mergeCell ref="A80:A82"/>
-    <mergeCell ref="A83:A85"/>
-    <mergeCell ref="A116:A118"/>
-    <mergeCell ref="A119:A121"/>
-    <mergeCell ref="A122:A124"/>
-    <mergeCell ref="A125:A127"/>
-    <mergeCell ref="A128:A130"/>
-    <mergeCell ref="A101:A103"/>
-    <mergeCell ref="A104:A106"/>
-    <mergeCell ref="A107:A109"/>
-    <mergeCell ref="A110:A112"/>
-    <mergeCell ref="A113:A115"/>
-    <mergeCell ref="A146:A148"/>
-    <mergeCell ref="A149:A151"/>
-    <mergeCell ref="A152:A154"/>
-    <mergeCell ref="A155:A157"/>
-    <mergeCell ref="A158:A160"/>
-    <mergeCell ref="A131:A133"/>
-    <mergeCell ref="A134:A136"/>
-    <mergeCell ref="A137:A139"/>
-    <mergeCell ref="A140:A142"/>
-    <mergeCell ref="A143:A145"/>
-    <mergeCell ref="A176:A178"/>
-    <mergeCell ref="A179:A181"/>
-    <mergeCell ref="A182:A184"/>
-    <mergeCell ref="A185:A187"/>
-    <mergeCell ref="A188:A190"/>
-    <mergeCell ref="A161:A163"/>
-    <mergeCell ref="A164:A166"/>
-    <mergeCell ref="A167:A169"/>
-    <mergeCell ref="A170:A172"/>
-    <mergeCell ref="A173:A175"/>
-    <mergeCell ref="A206:A208"/>
-    <mergeCell ref="A209:A211"/>
-    <mergeCell ref="A212:A214"/>
-    <mergeCell ref="A215:A217"/>
-    <mergeCell ref="A218:A220"/>
-    <mergeCell ref="A191:A193"/>
-    <mergeCell ref="A194:A196"/>
-    <mergeCell ref="A197:A199"/>
-    <mergeCell ref="A200:A202"/>
-    <mergeCell ref="A203:A205"/>
-    <mergeCell ref="A236:A238"/>
-    <mergeCell ref="A239:A241"/>
-    <mergeCell ref="A242:A244"/>
-    <mergeCell ref="A245:A247"/>
-    <mergeCell ref="A248:A250"/>
-    <mergeCell ref="A221:A223"/>
-    <mergeCell ref="A224:A226"/>
-    <mergeCell ref="A227:A229"/>
-    <mergeCell ref="A230:A232"/>
-    <mergeCell ref="A233:A235"/>
-    <mergeCell ref="A266:A268"/>
-    <mergeCell ref="A269:A271"/>
-    <mergeCell ref="A272:A274"/>
-    <mergeCell ref="A275:A277"/>
-    <mergeCell ref="A278:A280"/>
-    <mergeCell ref="A251:A253"/>
-    <mergeCell ref="A254:A256"/>
-    <mergeCell ref="A257:A259"/>
-    <mergeCell ref="A260:A262"/>
-    <mergeCell ref="A263:A265"/>
-    <mergeCell ref="A296:A298"/>
-    <mergeCell ref="A299:A301"/>
-    <mergeCell ref="A302:A304"/>
-    <mergeCell ref="A305:A307"/>
-    <mergeCell ref="A308:A310"/>
-    <mergeCell ref="A281:A283"/>
-    <mergeCell ref="A284:A286"/>
-    <mergeCell ref="A287:A289"/>
-    <mergeCell ref="A290:A292"/>
-    <mergeCell ref="A293:A295"/>
-    <mergeCell ref="A326:A328"/>
-    <mergeCell ref="A329:A331"/>
-    <mergeCell ref="A332:A334"/>
-    <mergeCell ref="A335:A337"/>
-    <mergeCell ref="A338:A340"/>
-    <mergeCell ref="A311:A313"/>
-    <mergeCell ref="A314:A316"/>
-    <mergeCell ref="A317:A319"/>
-    <mergeCell ref="A320:A322"/>
-    <mergeCell ref="A323:A325"/>
-    <mergeCell ref="A356:A358"/>
-    <mergeCell ref="A359:A361"/>
-    <mergeCell ref="A362:A364"/>
-    <mergeCell ref="A365:A367"/>
-    <mergeCell ref="A368:A370"/>
-    <mergeCell ref="A341:A343"/>
-    <mergeCell ref="A344:A346"/>
-    <mergeCell ref="A347:A349"/>
-    <mergeCell ref="A350:A352"/>
-    <mergeCell ref="A353:A355"/>
-    <mergeCell ref="A386:A388"/>
-    <mergeCell ref="A389:A391"/>
-    <mergeCell ref="A392:A394"/>
-    <mergeCell ref="A395:A397"/>
-    <mergeCell ref="A398:A400"/>
-    <mergeCell ref="A371:A373"/>
-    <mergeCell ref="A374:A376"/>
-    <mergeCell ref="A377:A379"/>
-    <mergeCell ref="A380:A382"/>
-    <mergeCell ref="A383:A385"/>
-    <mergeCell ref="A431:A433"/>
-    <mergeCell ref="A416:A418"/>
-    <mergeCell ref="A419:A421"/>
-    <mergeCell ref="A422:A424"/>
-    <mergeCell ref="A425:A427"/>
-    <mergeCell ref="A428:A430"/>
-    <mergeCell ref="A401:A403"/>
-    <mergeCell ref="A404:A406"/>
-    <mergeCell ref="A407:A409"/>
-    <mergeCell ref="A410:A412"/>
-    <mergeCell ref="A413:A415"/>
   </mergeCells>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" r:id="rId1"/>

--- a/planilhas/Planilha de Base para Cotacao.xlsx
+++ b/planilhas/Planilha de Base para Cotacao.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/0a19316afdd125d6/Documentos/GitHub/hawks-automations/planilhas/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="390" documentId="8_{B6B05E56-6ADC-4554-A921-81DFAB966C0D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0B32C1AE-7E22-4C86-A523-74AF08821354}"/>
+  <xr:revisionPtr revIDLastSave="419" documentId="8_{B6B05E56-6ADC-4554-A921-81DFAB966C0D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0A015A2A-0D5F-4772-BE4A-F77452162B70}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="21840" windowHeight="13140" xr2:uid="{AB0A4C4E-1938-46F3-8FAE-9EC8B05F0B3E}"/>
   </bookViews>
@@ -447,7 +447,7 @@
   <dimension ref="A1:J433"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="45" style="3" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="57" style="3" customWidth="1"/>
     <col min="2" max="2" width="11.7109375" style="3" customWidth="1"/>
     <col min="3" max="3" width="11.85546875" style="3" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="13.7109375" style="3" bestFit="1" customWidth="1"/>
@@ -1781,137 +1781,6 @@
     </row>
   </sheetData>
   <mergeCells count="144">
-    <mergeCell ref="A431:A433"/>
-    <mergeCell ref="A416:A418"/>
-    <mergeCell ref="A419:A421"/>
-    <mergeCell ref="A422:A424"/>
-    <mergeCell ref="A425:A427"/>
-    <mergeCell ref="A428:A430"/>
-    <mergeCell ref="A401:A403"/>
-    <mergeCell ref="A404:A406"/>
-    <mergeCell ref="A407:A409"/>
-    <mergeCell ref="A410:A412"/>
-    <mergeCell ref="A413:A415"/>
-    <mergeCell ref="A386:A388"/>
-    <mergeCell ref="A389:A391"/>
-    <mergeCell ref="A392:A394"/>
-    <mergeCell ref="A395:A397"/>
-    <mergeCell ref="A398:A400"/>
-    <mergeCell ref="A371:A373"/>
-    <mergeCell ref="A374:A376"/>
-    <mergeCell ref="A377:A379"/>
-    <mergeCell ref="A380:A382"/>
-    <mergeCell ref="A383:A385"/>
-    <mergeCell ref="A356:A358"/>
-    <mergeCell ref="A359:A361"/>
-    <mergeCell ref="A362:A364"/>
-    <mergeCell ref="A365:A367"/>
-    <mergeCell ref="A368:A370"/>
-    <mergeCell ref="A341:A343"/>
-    <mergeCell ref="A344:A346"/>
-    <mergeCell ref="A347:A349"/>
-    <mergeCell ref="A350:A352"/>
-    <mergeCell ref="A353:A355"/>
-    <mergeCell ref="A326:A328"/>
-    <mergeCell ref="A329:A331"/>
-    <mergeCell ref="A332:A334"/>
-    <mergeCell ref="A335:A337"/>
-    <mergeCell ref="A338:A340"/>
-    <mergeCell ref="A311:A313"/>
-    <mergeCell ref="A314:A316"/>
-    <mergeCell ref="A317:A319"/>
-    <mergeCell ref="A320:A322"/>
-    <mergeCell ref="A323:A325"/>
-    <mergeCell ref="A296:A298"/>
-    <mergeCell ref="A299:A301"/>
-    <mergeCell ref="A302:A304"/>
-    <mergeCell ref="A305:A307"/>
-    <mergeCell ref="A308:A310"/>
-    <mergeCell ref="A281:A283"/>
-    <mergeCell ref="A284:A286"/>
-    <mergeCell ref="A287:A289"/>
-    <mergeCell ref="A290:A292"/>
-    <mergeCell ref="A293:A295"/>
-    <mergeCell ref="A266:A268"/>
-    <mergeCell ref="A269:A271"/>
-    <mergeCell ref="A272:A274"/>
-    <mergeCell ref="A275:A277"/>
-    <mergeCell ref="A278:A280"/>
-    <mergeCell ref="A251:A253"/>
-    <mergeCell ref="A254:A256"/>
-    <mergeCell ref="A257:A259"/>
-    <mergeCell ref="A260:A262"/>
-    <mergeCell ref="A263:A265"/>
-    <mergeCell ref="A236:A238"/>
-    <mergeCell ref="A239:A241"/>
-    <mergeCell ref="A242:A244"/>
-    <mergeCell ref="A245:A247"/>
-    <mergeCell ref="A248:A250"/>
-    <mergeCell ref="A221:A223"/>
-    <mergeCell ref="A224:A226"/>
-    <mergeCell ref="A227:A229"/>
-    <mergeCell ref="A230:A232"/>
-    <mergeCell ref="A233:A235"/>
-    <mergeCell ref="A206:A208"/>
-    <mergeCell ref="A209:A211"/>
-    <mergeCell ref="A212:A214"/>
-    <mergeCell ref="A215:A217"/>
-    <mergeCell ref="A218:A220"/>
-    <mergeCell ref="A191:A193"/>
-    <mergeCell ref="A194:A196"/>
-    <mergeCell ref="A197:A199"/>
-    <mergeCell ref="A200:A202"/>
-    <mergeCell ref="A203:A205"/>
-    <mergeCell ref="A176:A178"/>
-    <mergeCell ref="A179:A181"/>
-    <mergeCell ref="A182:A184"/>
-    <mergeCell ref="A185:A187"/>
-    <mergeCell ref="A188:A190"/>
-    <mergeCell ref="A161:A163"/>
-    <mergeCell ref="A164:A166"/>
-    <mergeCell ref="A167:A169"/>
-    <mergeCell ref="A170:A172"/>
-    <mergeCell ref="A173:A175"/>
-    <mergeCell ref="A146:A148"/>
-    <mergeCell ref="A149:A151"/>
-    <mergeCell ref="A152:A154"/>
-    <mergeCell ref="A155:A157"/>
-    <mergeCell ref="A158:A160"/>
-    <mergeCell ref="A131:A133"/>
-    <mergeCell ref="A134:A136"/>
-    <mergeCell ref="A137:A139"/>
-    <mergeCell ref="A140:A142"/>
-    <mergeCell ref="A143:A145"/>
-    <mergeCell ref="A116:A118"/>
-    <mergeCell ref="A119:A121"/>
-    <mergeCell ref="A122:A124"/>
-    <mergeCell ref="A125:A127"/>
-    <mergeCell ref="A128:A130"/>
-    <mergeCell ref="A101:A103"/>
-    <mergeCell ref="A104:A106"/>
-    <mergeCell ref="A107:A109"/>
-    <mergeCell ref="A110:A112"/>
-    <mergeCell ref="A113:A115"/>
-    <mergeCell ref="A86:A88"/>
-    <mergeCell ref="A89:A91"/>
-    <mergeCell ref="A92:A94"/>
-    <mergeCell ref="A95:A97"/>
-    <mergeCell ref="A98:A100"/>
-    <mergeCell ref="A71:A73"/>
-    <mergeCell ref="A74:A76"/>
-    <mergeCell ref="A77:A79"/>
-    <mergeCell ref="A80:A82"/>
-    <mergeCell ref="A83:A85"/>
-    <mergeCell ref="A56:A58"/>
-    <mergeCell ref="A59:A61"/>
-    <mergeCell ref="A62:A64"/>
-    <mergeCell ref="A65:A67"/>
-    <mergeCell ref="A68:A70"/>
-    <mergeCell ref="A41:A43"/>
-    <mergeCell ref="A44:A46"/>
-    <mergeCell ref="A47:A49"/>
-    <mergeCell ref="A50:A52"/>
-    <mergeCell ref="A53:A55"/>
     <mergeCell ref="A26:A28"/>
     <mergeCell ref="A29:A31"/>
     <mergeCell ref="A32:A34"/>
@@ -1925,6 +1794,137 @@
     <mergeCell ref="A8:A10"/>
     <mergeCell ref="A11:A13"/>
     <mergeCell ref="A14:A16"/>
+    <mergeCell ref="A56:A58"/>
+    <mergeCell ref="A59:A61"/>
+    <mergeCell ref="A62:A64"/>
+    <mergeCell ref="A65:A67"/>
+    <mergeCell ref="A68:A70"/>
+    <mergeCell ref="A41:A43"/>
+    <mergeCell ref="A44:A46"/>
+    <mergeCell ref="A47:A49"/>
+    <mergeCell ref="A50:A52"/>
+    <mergeCell ref="A53:A55"/>
+    <mergeCell ref="A86:A88"/>
+    <mergeCell ref="A89:A91"/>
+    <mergeCell ref="A92:A94"/>
+    <mergeCell ref="A95:A97"/>
+    <mergeCell ref="A98:A100"/>
+    <mergeCell ref="A71:A73"/>
+    <mergeCell ref="A74:A76"/>
+    <mergeCell ref="A77:A79"/>
+    <mergeCell ref="A80:A82"/>
+    <mergeCell ref="A83:A85"/>
+    <mergeCell ref="A116:A118"/>
+    <mergeCell ref="A119:A121"/>
+    <mergeCell ref="A122:A124"/>
+    <mergeCell ref="A125:A127"/>
+    <mergeCell ref="A128:A130"/>
+    <mergeCell ref="A101:A103"/>
+    <mergeCell ref="A104:A106"/>
+    <mergeCell ref="A107:A109"/>
+    <mergeCell ref="A110:A112"/>
+    <mergeCell ref="A113:A115"/>
+    <mergeCell ref="A146:A148"/>
+    <mergeCell ref="A149:A151"/>
+    <mergeCell ref="A152:A154"/>
+    <mergeCell ref="A155:A157"/>
+    <mergeCell ref="A158:A160"/>
+    <mergeCell ref="A131:A133"/>
+    <mergeCell ref="A134:A136"/>
+    <mergeCell ref="A137:A139"/>
+    <mergeCell ref="A140:A142"/>
+    <mergeCell ref="A143:A145"/>
+    <mergeCell ref="A176:A178"/>
+    <mergeCell ref="A179:A181"/>
+    <mergeCell ref="A182:A184"/>
+    <mergeCell ref="A185:A187"/>
+    <mergeCell ref="A188:A190"/>
+    <mergeCell ref="A161:A163"/>
+    <mergeCell ref="A164:A166"/>
+    <mergeCell ref="A167:A169"/>
+    <mergeCell ref="A170:A172"/>
+    <mergeCell ref="A173:A175"/>
+    <mergeCell ref="A206:A208"/>
+    <mergeCell ref="A209:A211"/>
+    <mergeCell ref="A212:A214"/>
+    <mergeCell ref="A215:A217"/>
+    <mergeCell ref="A218:A220"/>
+    <mergeCell ref="A191:A193"/>
+    <mergeCell ref="A194:A196"/>
+    <mergeCell ref="A197:A199"/>
+    <mergeCell ref="A200:A202"/>
+    <mergeCell ref="A203:A205"/>
+    <mergeCell ref="A236:A238"/>
+    <mergeCell ref="A239:A241"/>
+    <mergeCell ref="A242:A244"/>
+    <mergeCell ref="A245:A247"/>
+    <mergeCell ref="A248:A250"/>
+    <mergeCell ref="A221:A223"/>
+    <mergeCell ref="A224:A226"/>
+    <mergeCell ref="A227:A229"/>
+    <mergeCell ref="A230:A232"/>
+    <mergeCell ref="A233:A235"/>
+    <mergeCell ref="A266:A268"/>
+    <mergeCell ref="A269:A271"/>
+    <mergeCell ref="A272:A274"/>
+    <mergeCell ref="A275:A277"/>
+    <mergeCell ref="A278:A280"/>
+    <mergeCell ref="A251:A253"/>
+    <mergeCell ref="A254:A256"/>
+    <mergeCell ref="A257:A259"/>
+    <mergeCell ref="A260:A262"/>
+    <mergeCell ref="A263:A265"/>
+    <mergeCell ref="A296:A298"/>
+    <mergeCell ref="A299:A301"/>
+    <mergeCell ref="A302:A304"/>
+    <mergeCell ref="A305:A307"/>
+    <mergeCell ref="A308:A310"/>
+    <mergeCell ref="A281:A283"/>
+    <mergeCell ref="A284:A286"/>
+    <mergeCell ref="A287:A289"/>
+    <mergeCell ref="A290:A292"/>
+    <mergeCell ref="A293:A295"/>
+    <mergeCell ref="A326:A328"/>
+    <mergeCell ref="A329:A331"/>
+    <mergeCell ref="A332:A334"/>
+    <mergeCell ref="A335:A337"/>
+    <mergeCell ref="A338:A340"/>
+    <mergeCell ref="A311:A313"/>
+    <mergeCell ref="A314:A316"/>
+    <mergeCell ref="A317:A319"/>
+    <mergeCell ref="A320:A322"/>
+    <mergeCell ref="A323:A325"/>
+    <mergeCell ref="A356:A358"/>
+    <mergeCell ref="A359:A361"/>
+    <mergeCell ref="A362:A364"/>
+    <mergeCell ref="A365:A367"/>
+    <mergeCell ref="A368:A370"/>
+    <mergeCell ref="A341:A343"/>
+    <mergeCell ref="A344:A346"/>
+    <mergeCell ref="A347:A349"/>
+    <mergeCell ref="A350:A352"/>
+    <mergeCell ref="A353:A355"/>
+    <mergeCell ref="A386:A388"/>
+    <mergeCell ref="A389:A391"/>
+    <mergeCell ref="A392:A394"/>
+    <mergeCell ref="A395:A397"/>
+    <mergeCell ref="A398:A400"/>
+    <mergeCell ref="A371:A373"/>
+    <mergeCell ref="A374:A376"/>
+    <mergeCell ref="A377:A379"/>
+    <mergeCell ref="A380:A382"/>
+    <mergeCell ref="A383:A385"/>
+    <mergeCell ref="A431:A433"/>
+    <mergeCell ref="A416:A418"/>
+    <mergeCell ref="A419:A421"/>
+    <mergeCell ref="A422:A424"/>
+    <mergeCell ref="A425:A427"/>
+    <mergeCell ref="A428:A430"/>
+    <mergeCell ref="A401:A403"/>
+    <mergeCell ref="A404:A406"/>
+    <mergeCell ref="A407:A409"/>
+    <mergeCell ref="A410:A412"/>
+    <mergeCell ref="A413:A415"/>
   </mergeCells>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" r:id="rId1"/>

--- a/planilhas/Planilha de Base para Cotacao.xlsx
+++ b/planilhas/Planilha de Base para Cotacao.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/0a19316afdd125d6/Documentos/GitHub/hawks-automations/planilhas/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="419" documentId="8_{B6B05E56-6ADC-4554-A921-81DFAB966C0D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0A015A2A-0D5F-4772-BE4A-F77452162B70}"/>
+  <xr:revisionPtr revIDLastSave="435" documentId="8_{B6B05E56-6ADC-4554-A921-81DFAB966C0D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{79574DE5-2498-4818-9B86-2B285351EB8E}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="21840" windowHeight="13140" xr2:uid="{AB0A4C4E-1938-46F3-8FAE-9EC8B05F0B3E}"/>
   </bookViews>
@@ -145,6 +145,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -447,7 +451,7 @@
   <dimension ref="A1:J433"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="57" style="3" customWidth="1"/>
+    <col min="1" max="1" width="65.5703125" style="3" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="11.7109375" style="3" customWidth="1"/>
     <col min="3" max="3" width="11.85546875" style="3" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="13.7109375" style="3" bestFit="1" customWidth="1"/>
@@ -1781,6 +1785,137 @@
     </row>
   </sheetData>
   <mergeCells count="144">
+    <mergeCell ref="A431:A433"/>
+    <mergeCell ref="A416:A418"/>
+    <mergeCell ref="A419:A421"/>
+    <mergeCell ref="A422:A424"/>
+    <mergeCell ref="A425:A427"/>
+    <mergeCell ref="A428:A430"/>
+    <mergeCell ref="A401:A403"/>
+    <mergeCell ref="A404:A406"/>
+    <mergeCell ref="A407:A409"/>
+    <mergeCell ref="A410:A412"/>
+    <mergeCell ref="A413:A415"/>
+    <mergeCell ref="A386:A388"/>
+    <mergeCell ref="A389:A391"/>
+    <mergeCell ref="A392:A394"/>
+    <mergeCell ref="A395:A397"/>
+    <mergeCell ref="A398:A400"/>
+    <mergeCell ref="A371:A373"/>
+    <mergeCell ref="A374:A376"/>
+    <mergeCell ref="A377:A379"/>
+    <mergeCell ref="A380:A382"/>
+    <mergeCell ref="A383:A385"/>
+    <mergeCell ref="A356:A358"/>
+    <mergeCell ref="A359:A361"/>
+    <mergeCell ref="A362:A364"/>
+    <mergeCell ref="A365:A367"/>
+    <mergeCell ref="A368:A370"/>
+    <mergeCell ref="A341:A343"/>
+    <mergeCell ref="A344:A346"/>
+    <mergeCell ref="A347:A349"/>
+    <mergeCell ref="A350:A352"/>
+    <mergeCell ref="A353:A355"/>
+    <mergeCell ref="A326:A328"/>
+    <mergeCell ref="A329:A331"/>
+    <mergeCell ref="A332:A334"/>
+    <mergeCell ref="A335:A337"/>
+    <mergeCell ref="A338:A340"/>
+    <mergeCell ref="A311:A313"/>
+    <mergeCell ref="A314:A316"/>
+    <mergeCell ref="A317:A319"/>
+    <mergeCell ref="A320:A322"/>
+    <mergeCell ref="A323:A325"/>
+    <mergeCell ref="A296:A298"/>
+    <mergeCell ref="A299:A301"/>
+    <mergeCell ref="A302:A304"/>
+    <mergeCell ref="A305:A307"/>
+    <mergeCell ref="A308:A310"/>
+    <mergeCell ref="A281:A283"/>
+    <mergeCell ref="A284:A286"/>
+    <mergeCell ref="A287:A289"/>
+    <mergeCell ref="A290:A292"/>
+    <mergeCell ref="A293:A295"/>
+    <mergeCell ref="A266:A268"/>
+    <mergeCell ref="A269:A271"/>
+    <mergeCell ref="A272:A274"/>
+    <mergeCell ref="A275:A277"/>
+    <mergeCell ref="A278:A280"/>
+    <mergeCell ref="A251:A253"/>
+    <mergeCell ref="A254:A256"/>
+    <mergeCell ref="A257:A259"/>
+    <mergeCell ref="A260:A262"/>
+    <mergeCell ref="A263:A265"/>
+    <mergeCell ref="A236:A238"/>
+    <mergeCell ref="A239:A241"/>
+    <mergeCell ref="A242:A244"/>
+    <mergeCell ref="A245:A247"/>
+    <mergeCell ref="A248:A250"/>
+    <mergeCell ref="A221:A223"/>
+    <mergeCell ref="A224:A226"/>
+    <mergeCell ref="A227:A229"/>
+    <mergeCell ref="A230:A232"/>
+    <mergeCell ref="A233:A235"/>
+    <mergeCell ref="A206:A208"/>
+    <mergeCell ref="A209:A211"/>
+    <mergeCell ref="A212:A214"/>
+    <mergeCell ref="A215:A217"/>
+    <mergeCell ref="A218:A220"/>
+    <mergeCell ref="A191:A193"/>
+    <mergeCell ref="A194:A196"/>
+    <mergeCell ref="A197:A199"/>
+    <mergeCell ref="A200:A202"/>
+    <mergeCell ref="A203:A205"/>
+    <mergeCell ref="A176:A178"/>
+    <mergeCell ref="A179:A181"/>
+    <mergeCell ref="A182:A184"/>
+    <mergeCell ref="A185:A187"/>
+    <mergeCell ref="A188:A190"/>
+    <mergeCell ref="A161:A163"/>
+    <mergeCell ref="A164:A166"/>
+    <mergeCell ref="A167:A169"/>
+    <mergeCell ref="A170:A172"/>
+    <mergeCell ref="A173:A175"/>
+    <mergeCell ref="A146:A148"/>
+    <mergeCell ref="A149:A151"/>
+    <mergeCell ref="A152:A154"/>
+    <mergeCell ref="A155:A157"/>
+    <mergeCell ref="A158:A160"/>
+    <mergeCell ref="A131:A133"/>
+    <mergeCell ref="A134:A136"/>
+    <mergeCell ref="A137:A139"/>
+    <mergeCell ref="A140:A142"/>
+    <mergeCell ref="A143:A145"/>
+    <mergeCell ref="A116:A118"/>
+    <mergeCell ref="A119:A121"/>
+    <mergeCell ref="A122:A124"/>
+    <mergeCell ref="A125:A127"/>
+    <mergeCell ref="A128:A130"/>
+    <mergeCell ref="A101:A103"/>
+    <mergeCell ref="A104:A106"/>
+    <mergeCell ref="A107:A109"/>
+    <mergeCell ref="A110:A112"/>
+    <mergeCell ref="A113:A115"/>
+    <mergeCell ref="A86:A88"/>
+    <mergeCell ref="A89:A91"/>
+    <mergeCell ref="A92:A94"/>
+    <mergeCell ref="A95:A97"/>
+    <mergeCell ref="A98:A100"/>
+    <mergeCell ref="A71:A73"/>
+    <mergeCell ref="A74:A76"/>
+    <mergeCell ref="A77:A79"/>
+    <mergeCell ref="A80:A82"/>
+    <mergeCell ref="A83:A85"/>
+    <mergeCell ref="A56:A58"/>
+    <mergeCell ref="A59:A61"/>
+    <mergeCell ref="A62:A64"/>
+    <mergeCell ref="A65:A67"/>
+    <mergeCell ref="A68:A70"/>
+    <mergeCell ref="A41:A43"/>
+    <mergeCell ref="A44:A46"/>
+    <mergeCell ref="A47:A49"/>
+    <mergeCell ref="A50:A52"/>
+    <mergeCell ref="A53:A55"/>
     <mergeCell ref="A26:A28"/>
     <mergeCell ref="A29:A31"/>
     <mergeCell ref="A32:A34"/>
@@ -1794,137 +1929,6 @@
     <mergeCell ref="A8:A10"/>
     <mergeCell ref="A11:A13"/>
     <mergeCell ref="A14:A16"/>
-    <mergeCell ref="A56:A58"/>
-    <mergeCell ref="A59:A61"/>
-    <mergeCell ref="A62:A64"/>
-    <mergeCell ref="A65:A67"/>
-    <mergeCell ref="A68:A70"/>
-    <mergeCell ref="A41:A43"/>
-    <mergeCell ref="A44:A46"/>
-    <mergeCell ref="A47:A49"/>
-    <mergeCell ref="A50:A52"/>
-    <mergeCell ref="A53:A55"/>
-    <mergeCell ref="A86:A88"/>
-    <mergeCell ref="A89:A91"/>
-    <mergeCell ref="A92:A94"/>
-    <mergeCell ref="A95:A97"/>
-    <mergeCell ref="A98:A100"/>
-    <mergeCell ref="A71:A73"/>
-    <mergeCell ref="A74:A76"/>
-    <mergeCell ref="A77:A79"/>
-    <mergeCell ref="A80:A82"/>
-    <mergeCell ref="A83:A85"/>
-    <mergeCell ref="A116:A118"/>
-    <mergeCell ref="A119:A121"/>
-    <mergeCell ref="A122:A124"/>
-    <mergeCell ref="A125:A127"/>
-    <mergeCell ref="A128:A130"/>
-    <mergeCell ref="A101:A103"/>
-    <mergeCell ref="A104:A106"/>
-    <mergeCell ref="A107:A109"/>
-    <mergeCell ref="A110:A112"/>
-    <mergeCell ref="A113:A115"/>
-    <mergeCell ref="A146:A148"/>
-    <mergeCell ref="A149:A151"/>
-    <mergeCell ref="A152:A154"/>
-    <mergeCell ref="A155:A157"/>
-    <mergeCell ref="A158:A160"/>
-    <mergeCell ref="A131:A133"/>
-    <mergeCell ref="A134:A136"/>
-    <mergeCell ref="A137:A139"/>
-    <mergeCell ref="A140:A142"/>
-    <mergeCell ref="A143:A145"/>
-    <mergeCell ref="A176:A178"/>
-    <mergeCell ref="A179:A181"/>
-    <mergeCell ref="A182:A184"/>
-    <mergeCell ref="A185:A187"/>
-    <mergeCell ref="A188:A190"/>
-    <mergeCell ref="A161:A163"/>
-    <mergeCell ref="A164:A166"/>
-    <mergeCell ref="A167:A169"/>
-    <mergeCell ref="A170:A172"/>
-    <mergeCell ref="A173:A175"/>
-    <mergeCell ref="A206:A208"/>
-    <mergeCell ref="A209:A211"/>
-    <mergeCell ref="A212:A214"/>
-    <mergeCell ref="A215:A217"/>
-    <mergeCell ref="A218:A220"/>
-    <mergeCell ref="A191:A193"/>
-    <mergeCell ref="A194:A196"/>
-    <mergeCell ref="A197:A199"/>
-    <mergeCell ref="A200:A202"/>
-    <mergeCell ref="A203:A205"/>
-    <mergeCell ref="A236:A238"/>
-    <mergeCell ref="A239:A241"/>
-    <mergeCell ref="A242:A244"/>
-    <mergeCell ref="A245:A247"/>
-    <mergeCell ref="A248:A250"/>
-    <mergeCell ref="A221:A223"/>
-    <mergeCell ref="A224:A226"/>
-    <mergeCell ref="A227:A229"/>
-    <mergeCell ref="A230:A232"/>
-    <mergeCell ref="A233:A235"/>
-    <mergeCell ref="A266:A268"/>
-    <mergeCell ref="A269:A271"/>
-    <mergeCell ref="A272:A274"/>
-    <mergeCell ref="A275:A277"/>
-    <mergeCell ref="A278:A280"/>
-    <mergeCell ref="A251:A253"/>
-    <mergeCell ref="A254:A256"/>
-    <mergeCell ref="A257:A259"/>
-    <mergeCell ref="A260:A262"/>
-    <mergeCell ref="A263:A265"/>
-    <mergeCell ref="A296:A298"/>
-    <mergeCell ref="A299:A301"/>
-    <mergeCell ref="A302:A304"/>
-    <mergeCell ref="A305:A307"/>
-    <mergeCell ref="A308:A310"/>
-    <mergeCell ref="A281:A283"/>
-    <mergeCell ref="A284:A286"/>
-    <mergeCell ref="A287:A289"/>
-    <mergeCell ref="A290:A292"/>
-    <mergeCell ref="A293:A295"/>
-    <mergeCell ref="A326:A328"/>
-    <mergeCell ref="A329:A331"/>
-    <mergeCell ref="A332:A334"/>
-    <mergeCell ref="A335:A337"/>
-    <mergeCell ref="A338:A340"/>
-    <mergeCell ref="A311:A313"/>
-    <mergeCell ref="A314:A316"/>
-    <mergeCell ref="A317:A319"/>
-    <mergeCell ref="A320:A322"/>
-    <mergeCell ref="A323:A325"/>
-    <mergeCell ref="A356:A358"/>
-    <mergeCell ref="A359:A361"/>
-    <mergeCell ref="A362:A364"/>
-    <mergeCell ref="A365:A367"/>
-    <mergeCell ref="A368:A370"/>
-    <mergeCell ref="A341:A343"/>
-    <mergeCell ref="A344:A346"/>
-    <mergeCell ref="A347:A349"/>
-    <mergeCell ref="A350:A352"/>
-    <mergeCell ref="A353:A355"/>
-    <mergeCell ref="A386:A388"/>
-    <mergeCell ref="A389:A391"/>
-    <mergeCell ref="A392:A394"/>
-    <mergeCell ref="A395:A397"/>
-    <mergeCell ref="A398:A400"/>
-    <mergeCell ref="A371:A373"/>
-    <mergeCell ref="A374:A376"/>
-    <mergeCell ref="A377:A379"/>
-    <mergeCell ref="A380:A382"/>
-    <mergeCell ref="A383:A385"/>
-    <mergeCell ref="A431:A433"/>
-    <mergeCell ref="A416:A418"/>
-    <mergeCell ref="A419:A421"/>
-    <mergeCell ref="A422:A424"/>
-    <mergeCell ref="A425:A427"/>
-    <mergeCell ref="A428:A430"/>
-    <mergeCell ref="A401:A403"/>
-    <mergeCell ref="A404:A406"/>
-    <mergeCell ref="A407:A409"/>
-    <mergeCell ref="A410:A412"/>
-    <mergeCell ref="A413:A415"/>
   </mergeCells>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" r:id="rId1"/>

--- a/planilhas/Planilha de Base para Cotacao.xlsx
+++ b/planilhas/Planilha de Base para Cotacao.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/0a19316afdd125d6/Documentos/GitHub/hawks-automations/planilhas/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="583" documentId="8_{B6B05E56-6ADC-4554-A921-81DFAB966C0D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9671BB51-7C92-4E20-8103-3CBA696F343D}"/>
+  <xr:revisionPtr revIDLastSave="617" documentId="8_{B6B05E56-6ADC-4554-A921-81DFAB966C0D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6FA55701-10BF-4054-9E6E-05811B8A888A}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="21840" windowHeight="13140" xr2:uid="{AB0A4C4E-1938-46F3-8FAE-9EC8B05F0B3E}"/>
   </bookViews>
@@ -109,20 +109,20 @@
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection hidden="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
   </cellXfs>
@@ -446,13 +446,13 @@
   <dimension ref="A1:I433"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="68.42578125" style="3" customWidth="1"/>
-    <col min="2" max="2" width="11.7109375" style="3" customWidth="1"/>
-    <col min="3" max="3" width="11.85546875" style="3" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13.7109375" style="3" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="11.85546875" style="3" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="22" style="3" bestFit="1" customWidth="1"/>
-    <col min="8" max="16384" width="9.140625" style="3"/>
+    <col min="1" max="1" width="74" style="2" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.7109375" style="2" customWidth="1"/>
+    <col min="3" max="3" width="11.85546875" style="2" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.7109375" style="2" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="11.85546875" style="2" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="22" style="2" bestFit="1" customWidth="1"/>
+    <col min="8" max="16384" width="9.140625" style="2"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9" s="1" customFormat="1" x14ac:dyDescent="0.25">
@@ -479,1437 +479,1306 @@
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A2" s="2"/>
+      <c r="A2" s="5"/>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A3" s="2"/>
-      <c r="G3" s="4"/>
+      <c r="A3" s="5"/>
+      <c r="G3" s="3"/>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A4" s="2"/>
-      <c r="G4" s="4"/>
+      <c r="A4" s="5"/>
+      <c r="G4" s="3"/>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A5" s="2"/>
+      <c r="A5" s="5"/>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A6" s="2"/>
+      <c r="A6" s="5"/>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A7" s="2"/>
-      <c r="I7" s="5"/>
+      <c r="A7" s="5"/>
+      <c r="I7" s="4"/>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A8" s="2"/>
+      <c r="A8" s="5"/>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A9" s="2"/>
+      <c r="A9" s="5"/>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A10" s="2"/>
+      <c r="A10" s="5"/>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A11" s="2"/>
+      <c r="A11" s="5"/>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A12" s="2"/>
+      <c r="A12" s="5"/>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A13" s="2"/>
+      <c r="A13" s="5"/>
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A14" s="2"/>
+      <c r="A14" s="5"/>
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A15" s="2"/>
+      <c r="A15" s="5"/>
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A16" s="2"/>
+      <c r="A16" s="5"/>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A17" s="2"/>
+      <c r="A17" s="5"/>
     </row>
     <row r="18" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A18" s="2"/>
+      <c r="A18" s="5"/>
     </row>
     <row r="19" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A19" s="2"/>
+      <c r="A19" s="5"/>
     </row>
     <row r="20" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A20" s="2"/>
+      <c r="A20" s="5"/>
     </row>
     <row r="21" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A21" s="2"/>
+      <c r="A21" s="5"/>
     </row>
     <row r="22" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A22" s="2"/>
+      <c r="A22" s="5"/>
     </row>
     <row r="23" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A23" s="2"/>
+      <c r="A23" s="5"/>
     </row>
     <row r="24" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A24" s="2"/>
+      <c r="A24" s="5"/>
     </row>
     <row r="25" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A25" s="2"/>
+      <c r="A25" s="5"/>
     </row>
     <row r="26" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A26" s="2"/>
+      <c r="A26" s="5"/>
     </row>
     <row r="27" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A27" s="2"/>
+      <c r="A27" s="5"/>
     </row>
     <row r="28" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A28" s="2"/>
+      <c r="A28" s="5"/>
     </row>
     <row r="29" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A29" s="2"/>
+      <c r="A29" s="5"/>
     </row>
     <row r="30" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A30" s="2"/>
+      <c r="A30" s="5"/>
     </row>
     <row r="31" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A31" s="2"/>
+      <c r="A31" s="5"/>
     </row>
     <row r="32" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A32" s="2"/>
+      <c r="A32" s="5"/>
     </row>
     <row r="33" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A33" s="2"/>
+      <c r="A33" s="5"/>
     </row>
     <row r="34" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A34" s="2"/>
+      <c r="A34" s="5"/>
     </row>
     <row r="35" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A35" s="2"/>
+      <c r="A35" s="5"/>
     </row>
     <row r="36" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A36" s="2"/>
+      <c r="A36" s="5"/>
     </row>
     <row r="37" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A37" s="2"/>
+      <c r="A37" s="5"/>
     </row>
     <row r="38" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A38" s="2"/>
+      <c r="A38" s="5"/>
     </row>
     <row r="39" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A39" s="2"/>
+      <c r="A39" s="5"/>
     </row>
     <row r="40" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A40" s="2"/>
+      <c r="A40" s="5"/>
     </row>
     <row r="41" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A41" s="2"/>
+      <c r="A41" s="5"/>
     </row>
     <row r="42" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A42" s="2"/>
+      <c r="A42" s="5"/>
     </row>
     <row r="43" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A43" s="2"/>
+      <c r="A43" s="5"/>
     </row>
     <row r="44" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A44" s="2"/>
+      <c r="A44" s="5"/>
     </row>
     <row r="45" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A45" s="2"/>
+      <c r="A45" s="5"/>
     </row>
     <row r="46" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A46" s="2"/>
+      <c r="A46" s="5"/>
     </row>
     <row r="47" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A47" s="2"/>
+      <c r="A47" s="5"/>
     </row>
     <row r="48" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A48" s="2"/>
+      <c r="A48" s="5"/>
     </row>
     <row r="49" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A49" s="2"/>
+      <c r="A49" s="5"/>
     </row>
     <row r="50" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A50" s="2"/>
+      <c r="A50" s="5"/>
     </row>
     <row r="51" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A51" s="2"/>
+      <c r="A51" s="5"/>
     </row>
     <row r="52" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A52" s="2"/>
+      <c r="A52" s="5"/>
     </row>
     <row r="53" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A53" s="2"/>
+      <c r="A53" s="5"/>
     </row>
     <row r="54" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A54" s="2"/>
+      <c r="A54" s="5"/>
     </row>
     <row r="55" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A55" s="2"/>
+      <c r="A55" s="5"/>
     </row>
     <row r="56" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A56" s="2"/>
+      <c r="A56" s="5"/>
     </row>
     <row r="57" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A57" s="2"/>
+      <c r="A57" s="5"/>
     </row>
     <row r="58" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A58" s="2"/>
+      <c r="A58" s="5"/>
     </row>
     <row r="59" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A59" s="2"/>
+      <c r="A59" s="5"/>
     </row>
     <row r="60" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A60" s="2"/>
+      <c r="A60" s="5"/>
     </row>
     <row r="61" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A61" s="2"/>
+      <c r="A61" s="5"/>
     </row>
     <row r="62" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A62" s="2"/>
+      <c r="A62" s="5"/>
     </row>
     <row r="63" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A63" s="2"/>
+      <c r="A63" s="5"/>
     </row>
     <row r="64" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A64" s="2"/>
+      <c r="A64" s="5"/>
     </row>
     <row r="65" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A65" s="2"/>
+      <c r="A65" s="5"/>
     </row>
     <row r="66" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A66" s="2"/>
+      <c r="A66" s="5"/>
     </row>
     <row r="67" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A67" s="2"/>
+      <c r="A67" s="5"/>
     </row>
     <row r="68" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A68" s="2"/>
+      <c r="A68" s="5"/>
     </row>
     <row r="69" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A69" s="2"/>
+      <c r="A69" s="5"/>
     </row>
     <row r="70" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A70" s="2"/>
+      <c r="A70" s="5"/>
     </row>
     <row r="71" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A71" s="2"/>
+      <c r="A71" s="5"/>
     </row>
     <row r="72" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A72" s="2"/>
+      <c r="A72" s="5"/>
     </row>
     <row r="73" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A73" s="2"/>
+      <c r="A73" s="5"/>
     </row>
     <row r="74" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A74" s="2"/>
+      <c r="A74" s="5"/>
     </row>
     <row r="75" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A75" s="2"/>
+      <c r="A75" s="5"/>
     </row>
     <row r="76" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A76" s="2"/>
+      <c r="A76" s="5"/>
     </row>
     <row r="77" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A77" s="2"/>
+      <c r="A77" s="5"/>
     </row>
     <row r="78" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A78" s="2"/>
+      <c r="A78" s="5"/>
     </row>
     <row r="79" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A79" s="2"/>
+      <c r="A79" s="5"/>
     </row>
     <row r="80" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A80" s="2"/>
+      <c r="A80" s="5"/>
     </row>
     <row r="81" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A81" s="2"/>
+      <c r="A81" s="5"/>
     </row>
     <row r="82" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A82" s="2"/>
+      <c r="A82" s="5"/>
     </row>
     <row r="83" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A83" s="2"/>
+      <c r="A83" s="5"/>
     </row>
     <row r="84" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A84" s="2"/>
+      <c r="A84" s="5"/>
     </row>
     <row r="85" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A85" s="2"/>
+      <c r="A85" s="5"/>
     </row>
     <row r="86" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A86" s="2"/>
+      <c r="A86" s="5"/>
     </row>
     <row r="87" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A87" s="2"/>
+      <c r="A87" s="5"/>
     </row>
     <row r="88" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A88" s="2"/>
+      <c r="A88" s="5"/>
     </row>
     <row r="89" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A89" s="2"/>
+      <c r="A89" s="5"/>
     </row>
     <row r="90" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A90" s="2"/>
+      <c r="A90" s="5"/>
     </row>
     <row r="91" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A91" s="2"/>
+      <c r="A91" s="5"/>
     </row>
     <row r="92" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A92" s="2"/>
+      <c r="A92" s="5"/>
     </row>
     <row r="93" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A93" s="2"/>
+      <c r="A93" s="5"/>
     </row>
     <row r="94" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A94" s="2"/>
+      <c r="A94" s="5"/>
     </row>
     <row r="95" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A95" s="2"/>
+      <c r="A95" s="5"/>
     </row>
     <row r="96" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A96" s="2"/>
+      <c r="A96" s="5"/>
     </row>
     <row r="97" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A97" s="2"/>
+      <c r="A97" s="5"/>
     </row>
     <row r="98" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A98" s="2"/>
+      <c r="A98" s="5"/>
     </row>
     <row r="99" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A99" s="2"/>
+      <c r="A99" s="5"/>
     </row>
     <row r="100" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A100" s="2"/>
+      <c r="A100" s="5"/>
     </row>
     <row r="101" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A101" s="2"/>
+      <c r="A101" s="5"/>
     </row>
     <row r="102" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A102" s="2"/>
+      <c r="A102" s="5"/>
     </row>
     <row r="103" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A103" s="2"/>
+      <c r="A103" s="5"/>
     </row>
     <row r="104" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A104" s="2"/>
+      <c r="A104" s="5"/>
     </row>
     <row r="105" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A105" s="2"/>
+      <c r="A105" s="5"/>
     </row>
     <row r="106" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A106" s="2"/>
+      <c r="A106" s="5"/>
     </row>
     <row r="107" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A107" s="2"/>
+      <c r="A107" s="5"/>
     </row>
     <row r="108" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A108" s="2"/>
+      <c r="A108" s="5"/>
     </row>
     <row r="109" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A109" s="2"/>
+      <c r="A109" s="5"/>
     </row>
     <row r="110" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A110" s="2"/>
+      <c r="A110" s="5"/>
     </row>
     <row r="111" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A111" s="2"/>
+      <c r="A111" s="5"/>
     </row>
     <row r="112" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A112" s="2"/>
+      <c r="A112" s="5"/>
     </row>
     <row r="113" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A113" s="2"/>
+      <c r="A113" s="5"/>
     </row>
     <row r="114" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A114" s="2"/>
+      <c r="A114" s="5"/>
     </row>
     <row r="115" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A115" s="2"/>
+      <c r="A115" s="5"/>
     </row>
     <row r="116" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A116" s="2"/>
+      <c r="A116" s="5"/>
     </row>
     <row r="117" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A117" s="2"/>
+      <c r="A117" s="5"/>
     </row>
     <row r="118" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A118" s="2"/>
+      <c r="A118" s="5"/>
     </row>
     <row r="119" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A119" s="2"/>
+      <c r="A119" s="5"/>
     </row>
     <row r="120" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A120" s="2"/>
+      <c r="A120" s="5"/>
     </row>
     <row r="121" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A121" s="2"/>
+      <c r="A121" s="5"/>
     </row>
     <row r="122" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A122" s="2"/>
+      <c r="A122" s="5"/>
     </row>
     <row r="123" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A123" s="2"/>
+      <c r="A123" s="5"/>
     </row>
     <row r="124" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A124" s="2"/>
+      <c r="A124" s="5"/>
     </row>
     <row r="125" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A125" s="2"/>
+      <c r="A125" s="5"/>
     </row>
     <row r="126" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A126" s="2"/>
+      <c r="A126" s="5"/>
     </row>
     <row r="127" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A127" s="2"/>
+      <c r="A127" s="5"/>
     </row>
     <row r="128" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A128" s="2"/>
+      <c r="A128" s="5"/>
     </row>
     <row r="129" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A129" s="2"/>
+      <c r="A129" s="5"/>
     </row>
     <row r="130" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A130" s="2"/>
+      <c r="A130" s="5"/>
     </row>
     <row r="131" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A131" s="2"/>
+      <c r="A131" s="5"/>
     </row>
     <row r="132" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A132" s="2"/>
+      <c r="A132" s="5"/>
     </row>
     <row r="133" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A133" s="2"/>
+      <c r="A133" s="5"/>
     </row>
     <row r="134" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A134" s="2"/>
+      <c r="A134" s="5"/>
     </row>
     <row r="135" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A135" s="2"/>
+      <c r="A135" s="5"/>
     </row>
     <row r="136" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A136" s="2"/>
+      <c r="A136" s="5"/>
     </row>
     <row r="137" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A137" s="2"/>
+      <c r="A137" s="5"/>
     </row>
     <row r="138" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A138" s="2"/>
+      <c r="A138" s="5"/>
     </row>
     <row r="139" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A139" s="2"/>
+      <c r="A139" s="5"/>
     </row>
     <row r="140" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A140" s="2"/>
+      <c r="A140" s="5"/>
     </row>
     <row r="141" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A141" s="2"/>
+      <c r="A141" s="5"/>
     </row>
     <row r="142" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A142" s="2"/>
+      <c r="A142" s="5"/>
     </row>
     <row r="143" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A143" s="2"/>
+      <c r="A143" s="5"/>
     </row>
     <row r="144" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A144" s="2"/>
+      <c r="A144" s="5"/>
     </row>
     <row r="145" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A145" s="2"/>
+      <c r="A145" s="5"/>
     </row>
     <row r="146" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A146" s="2"/>
+      <c r="A146" s="5"/>
     </row>
     <row r="147" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A147" s="2"/>
+      <c r="A147" s="5"/>
     </row>
     <row r="148" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A148" s="2"/>
+      <c r="A148" s="5"/>
     </row>
     <row r="149" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A149" s="2"/>
+      <c r="A149" s="5"/>
     </row>
     <row r="150" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A150" s="2"/>
+      <c r="A150" s="5"/>
     </row>
     <row r="151" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A151" s="2"/>
+      <c r="A151" s="5"/>
     </row>
     <row r="152" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A152" s="2"/>
+      <c r="A152" s="5"/>
     </row>
     <row r="153" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A153" s="2"/>
+      <c r="A153" s="5"/>
     </row>
     <row r="154" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A154" s="2"/>
+      <c r="A154" s="5"/>
     </row>
     <row r="155" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A155" s="2"/>
+      <c r="A155" s="5"/>
     </row>
     <row r="156" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A156" s="2"/>
+      <c r="A156" s="5"/>
     </row>
     <row r="157" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A157" s="2"/>
+      <c r="A157" s="5"/>
     </row>
     <row r="158" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A158" s="2"/>
+      <c r="A158" s="5"/>
     </row>
     <row r="159" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A159" s="2"/>
+      <c r="A159" s="5"/>
     </row>
     <row r="160" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A160" s="2"/>
+      <c r="A160" s="5"/>
     </row>
     <row r="161" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A161" s="2"/>
+      <c r="A161" s="5"/>
     </row>
     <row r="162" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A162" s="2"/>
+      <c r="A162" s="5"/>
     </row>
     <row r="163" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A163" s="2"/>
+      <c r="A163" s="5"/>
     </row>
     <row r="164" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A164" s="2"/>
+      <c r="A164" s="5"/>
     </row>
     <row r="165" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A165" s="2"/>
+      <c r="A165" s="5"/>
     </row>
     <row r="166" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A166" s="2"/>
+      <c r="A166" s="5"/>
     </row>
     <row r="167" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A167" s="2"/>
+      <c r="A167" s="5"/>
     </row>
     <row r="168" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A168" s="2"/>
+      <c r="A168" s="5"/>
     </row>
     <row r="169" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A169" s="2"/>
+      <c r="A169" s="5"/>
     </row>
     <row r="170" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A170" s="2"/>
+      <c r="A170" s="5"/>
     </row>
     <row r="171" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A171" s="2"/>
+      <c r="A171" s="5"/>
     </row>
     <row r="172" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A172" s="2"/>
+      <c r="A172" s="5"/>
     </row>
     <row r="173" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A173" s="2"/>
+      <c r="A173" s="5"/>
     </row>
     <row r="174" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A174" s="2"/>
+      <c r="A174" s="5"/>
     </row>
     <row r="175" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A175" s="2"/>
+      <c r="A175" s="5"/>
     </row>
     <row r="176" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A176" s="2"/>
+      <c r="A176" s="5"/>
     </row>
     <row r="177" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A177" s="2"/>
+      <c r="A177" s="5"/>
     </row>
     <row r="178" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A178" s="2"/>
+      <c r="A178" s="5"/>
     </row>
     <row r="179" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A179" s="2"/>
+      <c r="A179" s="5"/>
     </row>
     <row r="180" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A180" s="2"/>
+      <c r="A180" s="5"/>
     </row>
     <row r="181" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A181" s="2"/>
+      <c r="A181" s="5"/>
     </row>
     <row r="182" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A182" s="2"/>
+      <c r="A182" s="5"/>
     </row>
     <row r="183" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A183" s="2"/>
+      <c r="A183" s="5"/>
     </row>
     <row r="184" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A184" s="2"/>
+      <c r="A184" s="5"/>
     </row>
     <row r="185" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A185" s="2"/>
+      <c r="A185" s="5"/>
     </row>
     <row r="186" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A186" s="2"/>
+      <c r="A186" s="5"/>
     </row>
     <row r="187" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A187" s="2"/>
+      <c r="A187" s="5"/>
     </row>
     <row r="188" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A188" s="2"/>
+      <c r="A188" s="5"/>
     </row>
     <row r="189" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A189" s="2"/>
+      <c r="A189" s="5"/>
     </row>
     <row r="190" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A190" s="2"/>
+      <c r="A190" s="5"/>
     </row>
     <row r="191" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A191" s="2"/>
+      <c r="A191" s="5"/>
     </row>
     <row r="192" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A192" s="2"/>
+      <c r="A192" s="5"/>
     </row>
     <row r="193" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A193" s="2"/>
+      <c r="A193" s="5"/>
     </row>
     <row r="194" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A194" s="2"/>
+      <c r="A194" s="5"/>
     </row>
     <row r="195" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A195" s="2"/>
+      <c r="A195" s="5"/>
     </row>
     <row r="196" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A196" s="2"/>
+      <c r="A196" s="5"/>
     </row>
     <row r="197" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A197" s="2"/>
+      <c r="A197" s="5"/>
     </row>
     <row r="198" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A198" s="2"/>
+      <c r="A198" s="5"/>
     </row>
     <row r="199" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A199" s="2"/>
+      <c r="A199" s="5"/>
     </row>
     <row r="200" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A200" s="2"/>
+      <c r="A200" s="5"/>
     </row>
     <row r="201" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A201" s="2"/>
+      <c r="A201" s="5"/>
     </row>
     <row r="202" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A202" s="2"/>
+      <c r="A202" s="5"/>
     </row>
     <row r="203" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A203" s="2"/>
+      <c r="A203" s="5"/>
     </row>
     <row r="204" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A204" s="2"/>
+      <c r="A204" s="5"/>
     </row>
     <row r="205" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A205" s="2"/>
+      <c r="A205" s="5"/>
     </row>
     <row r="206" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A206" s="2"/>
+      <c r="A206" s="5"/>
     </row>
     <row r="207" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A207" s="2"/>
+      <c r="A207" s="5"/>
     </row>
     <row r="208" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A208" s="2"/>
+      <c r="A208" s="5"/>
     </row>
     <row r="209" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A209" s="2"/>
+      <c r="A209" s="5"/>
     </row>
     <row r="210" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A210" s="2"/>
+      <c r="A210" s="5"/>
     </row>
     <row r="211" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A211" s="2"/>
+      <c r="A211" s="5"/>
     </row>
     <row r="212" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A212" s="2"/>
+      <c r="A212" s="5"/>
     </row>
     <row r="213" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A213" s="2"/>
+      <c r="A213" s="5"/>
     </row>
     <row r="214" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A214" s="2"/>
+      <c r="A214" s="5"/>
     </row>
     <row r="215" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A215" s="2"/>
+      <c r="A215" s="5"/>
     </row>
     <row r="216" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A216" s="2"/>
+      <c r="A216" s="5"/>
     </row>
     <row r="217" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A217" s="2"/>
+      <c r="A217" s="5"/>
     </row>
     <row r="218" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A218" s="2"/>
+      <c r="A218" s="5"/>
     </row>
     <row r="219" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A219" s="2"/>
+      <c r="A219" s="5"/>
     </row>
     <row r="220" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A220" s="2"/>
+      <c r="A220" s="5"/>
     </row>
     <row r="221" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A221" s="2"/>
+      <c r="A221" s="5"/>
     </row>
     <row r="222" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A222" s="2"/>
+      <c r="A222" s="5"/>
     </row>
     <row r="223" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A223" s="2"/>
+      <c r="A223" s="5"/>
     </row>
     <row r="224" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A224" s="2"/>
+      <c r="A224" s="5"/>
     </row>
     <row r="225" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A225" s="2"/>
+      <c r="A225" s="5"/>
     </row>
     <row r="226" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A226" s="2"/>
+      <c r="A226" s="5"/>
     </row>
     <row r="227" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A227" s="2"/>
+      <c r="A227" s="5"/>
     </row>
     <row r="228" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A228" s="2"/>
+      <c r="A228" s="5"/>
     </row>
     <row r="229" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A229" s="2"/>
+      <c r="A229" s="5"/>
     </row>
     <row r="230" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A230" s="2"/>
+      <c r="A230" s="5"/>
     </row>
     <row r="231" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A231" s="2"/>
+      <c r="A231" s="5"/>
     </row>
     <row r="232" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A232" s="2"/>
+      <c r="A232" s="5"/>
     </row>
     <row r="233" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A233" s="2"/>
+      <c r="A233" s="5"/>
     </row>
     <row r="234" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A234" s="2"/>
+      <c r="A234" s="5"/>
     </row>
     <row r="235" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A235" s="2"/>
+      <c r="A235" s="5"/>
     </row>
     <row r="236" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A236" s="2"/>
+      <c r="A236" s="5"/>
     </row>
     <row r="237" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A237" s="2"/>
+      <c r="A237" s="5"/>
     </row>
     <row r="238" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A238" s="2"/>
+      <c r="A238" s="5"/>
     </row>
     <row r="239" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A239" s="2"/>
+      <c r="A239" s="5"/>
     </row>
     <row r="240" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A240" s="2"/>
+      <c r="A240" s="5"/>
     </row>
     <row r="241" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A241" s="2"/>
+      <c r="A241" s="5"/>
     </row>
     <row r="242" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A242" s="2"/>
+      <c r="A242" s="5"/>
     </row>
     <row r="243" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A243" s="2"/>
+      <c r="A243" s="5"/>
     </row>
     <row r="244" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A244" s="2"/>
+      <c r="A244" s="5"/>
     </row>
     <row r="245" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A245" s="2"/>
+      <c r="A245" s="5"/>
     </row>
     <row r="246" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A246" s="2"/>
+      <c r="A246" s="5"/>
     </row>
     <row r="247" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A247" s="2"/>
+      <c r="A247" s="5"/>
     </row>
     <row r="248" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A248" s="2"/>
+      <c r="A248" s="5"/>
     </row>
     <row r="249" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A249" s="2"/>
+      <c r="A249" s="5"/>
     </row>
     <row r="250" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A250" s="2"/>
+      <c r="A250" s="5"/>
     </row>
     <row r="251" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A251" s="2"/>
+      <c r="A251" s="5"/>
     </row>
     <row r="252" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A252" s="2"/>
+      <c r="A252" s="5"/>
     </row>
     <row r="253" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A253" s="2"/>
+      <c r="A253" s="5"/>
     </row>
     <row r="254" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A254" s="2"/>
+      <c r="A254" s="5"/>
     </row>
     <row r="255" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A255" s="2"/>
+      <c r="A255" s="5"/>
     </row>
     <row r="256" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A256" s="2"/>
+      <c r="A256" s="5"/>
     </row>
     <row r="257" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A257" s="2"/>
+      <c r="A257" s="5"/>
     </row>
     <row r="258" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A258" s="2"/>
+      <c r="A258" s="5"/>
     </row>
     <row r="259" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A259" s="2"/>
+      <c r="A259" s="5"/>
     </row>
     <row r="260" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A260" s="2"/>
+      <c r="A260" s="5"/>
     </row>
     <row r="261" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A261" s="2"/>
+      <c r="A261" s="5"/>
     </row>
     <row r="262" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A262" s="2"/>
+      <c r="A262" s="5"/>
     </row>
     <row r="263" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A263" s="2"/>
+      <c r="A263" s="5"/>
     </row>
     <row r="264" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A264" s="2"/>
+      <c r="A264" s="5"/>
     </row>
     <row r="265" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A265" s="2"/>
+      <c r="A265" s="5"/>
     </row>
     <row r="266" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A266" s="2"/>
+      <c r="A266" s="5"/>
     </row>
     <row r="267" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A267" s="2"/>
+      <c r="A267" s="5"/>
     </row>
     <row r="268" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A268" s="2"/>
+      <c r="A268" s="5"/>
     </row>
     <row r="269" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A269" s="2"/>
+      <c r="A269" s="5"/>
     </row>
     <row r="270" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A270" s="2"/>
+      <c r="A270" s="5"/>
     </row>
     <row r="271" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A271" s="2"/>
+      <c r="A271" s="5"/>
     </row>
     <row r="272" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A272" s="2"/>
+      <c r="A272" s="5"/>
     </row>
     <row r="273" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A273" s="2"/>
+      <c r="A273" s="5"/>
     </row>
     <row r="274" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A274" s="2"/>
+      <c r="A274" s="5"/>
     </row>
     <row r="275" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A275" s="2"/>
+      <c r="A275" s="5"/>
     </row>
     <row r="276" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A276" s="2"/>
+      <c r="A276" s="5"/>
     </row>
     <row r="277" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A277" s="2"/>
+      <c r="A277" s="5"/>
     </row>
     <row r="278" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A278" s="2"/>
+      <c r="A278" s="5"/>
     </row>
     <row r="279" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A279" s="2"/>
+      <c r="A279" s="5"/>
     </row>
     <row r="280" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A280" s="2"/>
+      <c r="A280" s="5"/>
     </row>
     <row r="281" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A281" s="2"/>
+      <c r="A281" s="5"/>
     </row>
     <row r="282" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A282" s="2"/>
+      <c r="A282" s="5"/>
     </row>
     <row r="283" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A283" s="2"/>
+      <c r="A283" s="5"/>
     </row>
     <row r="284" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A284" s="2"/>
+      <c r="A284" s="5"/>
     </row>
     <row r="285" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A285" s="2"/>
+      <c r="A285" s="5"/>
     </row>
     <row r="286" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A286" s="2"/>
+      <c r="A286" s="5"/>
     </row>
     <row r="287" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A287" s="2"/>
+      <c r="A287" s="5"/>
     </row>
     <row r="288" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A288" s="2"/>
+      <c r="A288" s="5"/>
     </row>
     <row r="289" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A289" s="2"/>
+      <c r="A289" s="5"/>
     </row>
     <row r="290" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A290" s="2"/>
+      <c r="A290" s="5"/>
     </row>
     <row r="291" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A291" s="2"/>
+      <c r="A291" s="5"/>
     </row>
     <row r="292" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A292" s="2"/>
+      <c r="A292" s="5"/>
     </row>
     <row r="293" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A293" s="2"/>
+      <c r="A293" s="5"/>
     </row>
     <row r="294" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A294" s="2"/>
+      <c r="A294" s="5"/>
     </row>
     <row r="295" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A295" s="2"/>
+      <c r="A295" s="5"/>
     </row>
     <row r="296" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A296" s="2"/>
+      <c r="A296" s="5"/>
     </row>
     <row r="297" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A297" s="2"/>
+      <c r="A297" s="5"/>
     </row>
     <row r="298" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A298" s="2"/>
+      <c r="A298" s="5"/>
     </row>
     <row r="299" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A299" s="2"/>
+      <c r="A299" s="5"/>
     </row>
     <row r="300" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A300" s="2"/>
+      <c r="A300" s="5"/>
     </row>
     <row r="301" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A301" s="2"/>
+      <c r="A301" s="5"/>
     </row>
     <row r="302" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A302" s="2"/>
+      <c r="A302" s="5"/>
     </row>
     <row r="303" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A303" s="2"/>
+      <c r="A303" s="5"/>
     </row>
     <row r="304" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A304" s="2"/>
+      <c r="A304" s="5"/>
     </row>
     <row r="305" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A305" s="2"/>
+      <c r="A305" s="5"/>
     </row>
     <row r="306" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A306" s="2"/>
+      <c r="A306" s="5"/>
     </row>
     <row r="307" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A307" s="2"/>
+      <c r="A307" s="5"/>
     </row>
     <row r="308" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A308" s="2"/>
+      <c r="A308" s="5"/>
     </row>
     <row r="309" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A309" s="2"/>
+      <c r="A309" s="5"/>
     </row>
     <row r="310" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A310" s="2"/>
+      <c r="A310" s="5"/>
     </row>
     <row r="311" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A311" s="2"/>
+      <c r="A311" s="5"/>
     </row>
     <row r="312" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A312" s="2"/>
+      <c r="A312" s="5"/>
     </row>
     <row r="313" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A313" s="2"/>
+      <c r="A313" s="5"/>
     </row>
     <row r="314" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A314" s="2"/>
+      <c r="A314" s="5"/>
     </row>
     <row r="315" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A315" s="2"/>
+      <c r="A315" s="5"/>
     </row>
     <row r="316" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A316" s="2"/>
+      <c r="A316" s="5"/>
     </row>
     <row r="317" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A317" s="2"/>
+      <c r="A317" s="5"/>
     </row>
     <row r="318" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A318" s="2"/>
+      <c r="A318" s="5"/>
     </row>
     <row r="319" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A319" s="2"/>
+      <c r="A319" s="5"/>
     </row>
     <row r="320" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A320" s="2"/>
+      <c r="A320" s="5"/>
     </row>
     <row r="321" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A321" s="2"/>
+      <c r="A321" s="5"/>
     </row>
     <row r="322" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A322" s="2"/>
+      <c r="A322" s="5"/>
     </row>
     <row r="323" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A323" s="2"/>
+      <c r="A323" s="5"/>
     </row>
     <row r="324" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A324" s="2"/>
+      <c r="A324" s="5"/>
     </row>
     <row r="325" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A325" s="2"/>
+      <c r="A325" s="5"/>
     </row>
     <row r="326" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A326" s="2"/>
+      <c r="A326" s="5"/>
     </row>
     <row r="327" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A327" s="2"/>
+      <c r="A327" s="5"/>
     </row>
     <row r="328" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A328" s="2"/>
+      <c r="A328" s="5"/>
     </row>
     <row r="329" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A329" s="2"/>
+      <c r="A329" s="5"/>
     </row>
     <row r="330" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A330" s="2"/>
+      <c r="A330" s="5"/>
     </row>
     <row r="331" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A331" s="2"/>
+      <c r="A331" s="5"/>
     </row>
     <row r="332" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A332" s="2"/>
+      <c r="A332" s="5"/>
     </row>
     <row r="333" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A333" s="2"/>
+      <c r="A333" s="5"/>
     </row>
     <row r="334" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A334" s="2"/>
+      <c r="A334" s="5"/>
     </row>
     <row r="335" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A335" s="2"/>
+      <c r="A335" s="5"/>
     </row>
     <row r="336" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A336" s="2"/>
+      <c r="A336" s="5"/>
     </row>
     <row r="337" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A337" s="2"/>
+      <c r="A337" s="5"/>
     </row>
     <row r="338" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A338" s="2"/>
+      <c r="A338" s="5"/>
     </row>
     <row r="339" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A339" s="2"/>
+      <c r="A339" s="5"/>
     </row>
     <row r="340" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A340" s="2"/>
+      <c r="A340" s="5"/>
     </row>
     <row r="341" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A341" s="2"/>
+      <c r="A341" s="5"/>
     </row>
     <row r="342" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A342" s="2"/>
+      <c r="A342" s="5"/>
     </row>
     <row r="343" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A343" s="2"/>
+      <c r="A343" s="5"/>
     </row>
     <row r="344" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A344" s="2"/>
+      <c r="A344" s="5"/>
     </row>
     <row r="345" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A345" s="2"/>
+      <c r="A345" s="5"/>
     </row>
     <row r="346" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A346" s="2"/>
+      <c r="A346" s="5"/>
     </row>
     <row r="347" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A347" s="2"/>
+      <c r="A347" s="5"/>
     </row>
     <row r="348" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A348" s="2"/>
+      <c r="A348" s="5"/>
     </row>
     <row r="349" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A349" s="2"/>
+      <c r="A349" s="5"/>
     </row>
     <row r="350" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A350" s="2"/>
+      <c r="A350" s="5"/>
     </row>
     <row r="351" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A351" s="2"/>
+      <c r="A351" s="5"/>
     </row>
     <row r="352" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A352" s="2"/>
+      <c r="A352" s="5"/>
     </row>
     <row r="353" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A353" s="2"/>
+      <c r="A353" s="5"/>
     </row>
     <row r="354" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A354" s="2"/>
+      <c r="A354" s="5"/>
     </row>
     <row r="355" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A355" s="2"/>
+      <c r="A355" s="5"/>
     </row>
     <row r="356" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A356" s="2"/>
+      <c r="A356" s="5"/>
     </row>
     <row r="357" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A357" s="2"/>
+      <c r="A357" s="5"/>
     </row>
     <row r="358" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A358" s="2"/>
+      <c r="A358" s="5"/>
     </row>
     <row r="359" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A359" s="2"/>
+      <c r="A359" s="5"/>
     </row>
     <row r="360" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A360" s="2"/>
+      <c r="A360" s="5"/>
     </row>
     <row r="361" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A361" s="2"/>
+      <c r="A361" s="5"/>
     </row>
     <row r="362" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A362" s="2"/>
+      <c r="A362" s="5"/>
     </row>
     <row r="363" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A363" s="2"/>
+      <c r="A363" s="5"/>
     </row>
     <row r="364" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A364" s="2"/>
+      <c r="A364" s="5"/>
     </row>
     <row r="365" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A365" s="2"/>
+      <c r="A365" s="5"/>
     </row>
     <row r="366" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A366" s="2"/>
+      <c r="A366" s="5"/>
     </row>
     <row r="367" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A367" s="2"/>
+      <c r="A367" s="5"/>
     </row>
     <row r="368" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A368" s="2"/>
+      <c r="A368" s="5"/>
     </row>
     <row r="369" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A369" s="2"/>
+      <c r="A369" s="5"/>
     </row>
     <row r="370" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A370" s="2"/>
+      <c r="A370" s="5"/>
     </row>
     <row r="371" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A371" s="2"/>
+      <c r="A371" s="5"/>
     </row>
     <row r="372" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A372" s="2"/>
+      <c r="A372" s="5"/>
     </row>
     <row r="373" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A373" s="2"/>
+      <c r="A373" s="5"/>
     </row>
     <row r="374" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A374" s="2"/>
+      <c r="A374" s="5"/>
     </row>
     <row r="375" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A375" s="2"/>
+      <c r="A375" s="5"/>
     </row>
     <row r="376" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A376" s="2"/>
+      <c r="A376" s="5"/>
     </row>
     <row r="377" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A377" s="2"/>
+      <c r="A377" s="5"/>
     </row>
     <row r="378" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A378" s="2"/>
+      <c r="A378" s="5"/>
     </row>
     <row r="379" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A379" s="2"/>
+      <c r="A379" s="5"/>
     </row>
     <row r="380" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A380" s="2"/>
+      <c r="A380" s="5"/>
     </row>
     <row r="381" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A381" s="2"/>
+      <c r="A381" s="5"/>
     </row>
     <row r="382" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A382" s="2"/>
+      <c r="A382" s="5"/>
     </row>
     <row r="383" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A383" s="2"/>
+      <c r="A383" s="5"/>
     </row>
     <row r="384" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A384" s="2"/>
+      <c r="A384" s="5"/>
     </row>
     <row r="385" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A385" s="2"/>
+      <c r="A385" s="5"/>
     </row>
     <row r="386" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A386" s="2"/>
+      <c r="A386" s="5"/>
     </row>
     <row r="387" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A387" s="2"/>
+      <c r="A387" s="5"/>
     </row>
     <row r="388" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A388" s="2"/>
+      <c r="A388" s="5"/>
     </row>
     <row r="389" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A389" s="2"/>
+      <c r="A389" s="5"/>
     </row>
     <row r="390" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A390" s="2"/>
+      <c r="A390" s="5"/>
     </row>
     <row r="391" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A391" s="2"/>
+      <c r="A391" s="5"/>
     </row>
     <row r="392" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A392" s="2"/>
+      <c r="A392" s="5"/>
     </row>
     <row r="393" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A393" s="2"/>
+      <c r="A393" s="5"/>
     </row>
     <row r="394" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A394" s="2"/>
+      <c r="A394" s="5"/>
     </row>
     <row r="395" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A395" s="2"/>
+      <c r="A395" s="5"/>
     </row>
     <row r="396" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A396" s="2"/>
+      <c r="A396" s="5"/>
     </row>
     <row r="397" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A397" s="2"/>
+      <c r="A397" s="5"/>
     </row>
     <row r="398" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A398" s="2"/>
+      <c r="A398" s="5"/>
     </row>
     <row r="399" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A399" s="2"/>
+      <c r="A399" s="5"/>
     </row>
     <row r="400" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A400" s="2"/>
+      <c r="A400" s="5"/>
     </row>
     <row r="401" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A401" s="2"/>
+      <c r="A401" s="5"/>
     </row>
     <row r="402" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A402" s="2"/>
+      <c r="A402" s="5"/>
     </row>
     <row r="403" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A403" s="2"/>
+      <c r="A403" s="5"/>
     </row>
     <row r="404" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A404" s="2"/>
+      <c r="A404" s="5"/>
     </row>
     <row r="405" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A405" s="2"/>
+      <c r="A405" s="5"/>
     </row>
     <row r="406" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A406" s="2"/>
+      <c r="A406" s="5"/>
     </row>
     <row r="407" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A407" s="2"/>
+      <c r="A407" s="5"/>
     </row>
     <row r="408" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A408" s="2"/>
+      <c r="A408" s="5"/>
     </row>
     <row r="409" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A409" s="2"/>
+      <c r="A409" s="5"/>
     </row>
     <row r="410" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A410" s="2"/>
+      <c r="A410" s="5"/>
     </row>
     <row r="411" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A411" s="2"/>
+      <c r="A411" s="5"/>
     </row>
     <row r="412" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A412" s="2"/>
+      <c r="A412" s="5"/>
     </row>
     <row r="413" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A413" s="2"/>
+      <c r="A413" s="5"/>
     </row>
     <row r="414" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A414" s="2"/>
+      <c r="A414" s="5"/>
     </row>
     <row r="415" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A415" s="2"/>
+      <c r="A415" s="5"/>
     </row>
     <row r="416" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A416" s="2"/>
+      <c r="A416" s="5"/>
     </row>
     <row r="417" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A417" s="2"/>
+      <c r="A417" s="5"/>
     </row>
     <row r="418" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A418" s="2"/>
+      <c r="A418" s="5"/>
     </row>
     <row r="419" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A419" s="2"/>
+      <c r="A419" s="5"/>
     </row>
     <row r="420" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A420" s="2"/>
+      <c r="A420" s="5"/>
     </row>
     <row r="421" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A421" s="2"/>
+      <c r="A421" s="5"/>
     </row>
     <row r="422" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A422" s="2"/>
+      <c r="A422" s="5"/>
     </row>
     <row r="423" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A423" s="2"/>
+      <c r="A423" s="5"/>
     </row>
     <row r="424" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A424" s="2"/>
+      <c r="A424" s="5"/>
     </row>
     <row r="425" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A425" s="2"/>
+      <c r="A425" s="5"/>
     </row>
     <row r="426" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A426" s="2"/>
+      <c r="A426" s="5"/>
     </row>
     <row r="427" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A427" s="2"/>
+      <c r="A427" s="5"/>
     </row>
     <row r="428" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A428" s="2"/>
+      <c r="A428" s="5"/>
     </row>
     <row r="429" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A429" s="2"/>
+      <c r="A429" s="5"/>
     </row>
     <row r="430" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A430" s="2"/>
+      <c r="A430" s="5"/>
     </row>
     <row r="431" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A431" s="2"/>
+      <c r="A431" s="5"/>
     </row>
     <row r="432" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A432" s="2"/>
+      <c r="A432" s="5"/>
     </row>
     <row r="433" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A433" s="2"/>
+      <c r="A433" s="5"/>
     </row>
   </sheetData>
   <mergeCells count="144">
-    <mergeCell ref="A431:A433"/>
-    <mergeCell ref="A416:A418"/>
-    <mergeCell ref="A419:A421"/>
-    <mergeCell ref="A422:A424"/>
-    <mergeCell ref="A425:A427"/>
-    <mergeCell ref="A428:A430"/>
-    <mergeCell ref="A401:A403"/>
-    <mergeCell ref="A404:A406"/>
-    <mergeCell ref="A407:A409"/>
-    <mergeCell ref="A410:A412"/>
-    <mergeCell ref="A413:A415"/>
-    <mergeCell ref="A386:A388"/>
-    <mergeCell ref="A389:A391"/>
-    <mergeCell ref="A392:A394"/>
-    <mergeCell ref="A395:A397"/>
-    <mergeCell ref="A398:A400"/>
-    <mergeCell ref="A371:A373"/>
-    <mergeCell ref="A374:A376"/>
-    <mergeCell ref="A377:A379"/>
-    <mergeCell ref="A380:A382"/>
-    <mergeCell ref="A383:A385"/>
-    <mergeCell ref="A356:A358"/>
-    <mergeCell ref="A359:A361"/>
-    <mergeCell ref="A362:A364"/>
-    <mergeCell ref="A365:A367"/>
-    <mergeCell ref="A368:A370"/>
-    <mergeCell ref="A341:A343"/>
-    <mergeCell ref="A344:A346"/>
-    <mergeCell ref="A347:A349"/>
-    <mergeCell ref="A350:A352"/>
-    <mergeCell ref="A353:A355"/>
-    <mergeCell ref="A326:A328"/>
-    <mergeCell ref="A329:A331"/>
-    <mergeCell ref="A332:A334"/>
-    <mergeCell ref="A335:A337"/>
-    <mergeCell ref="A338:A340"/>
-    <mergeCell ref="A311:A313"/>
-    <mergeCell ref="A314:A316"/>
-    <mergeCell ref="A317:A319"/>
-    <mergeCell ref="A320:A322"/>
-    <mergeCell ref="A323:A325"/>
-    <mergeCell ref="A296:A298"/>
-    <mergeCell ref="A299:A301"/>
-    <mergeCell ref="A302:A304"/>
-    <mergeCell ref="A305:A307"/>
-    <mergeCell ref="A308:A310"/>
-    <mergeCell ref="A281:A283"/>
-    <mergeCell ref="A284:A286"/>
-    <mergeCell ref="A287:A289"/>
-    <mergeCell ref="A290:A292"/>
-    <mergeCell ref="A293:A295"/>
-    <mergeCell ref="A266:A268"/>
-    <mergeCell ref="A269:A271"/>
-    <mergeCell ref="A272:A274"/>
-    <mergeCell ref="A275:A277"/>
-    <mergeCell ref="A278:A280"/>
-    <mergeCell ref="A251:A253"/>
-    <mergeCell ref="A254:A256"/>
-    <mergeCell ref="A257:A259"/>
-    <mergeCell ref="A260:A262"/>
-    <mergeCell ref="A263:A265"/>
-    <mergeCell ref="A236:A238"/>
-    <mergeCell ref="A239:A241"/>
-    <mergeCell ref="A242:A244"/>
-    <mergeCell ref="A245:A247"/>
-    <mergeCell ref="A248:A250"/>
-    <mergeCell ref="A221:A223"/>
-    <mergeCell ref="A224:A226"/>
-    <mergeCell ref="A227:A229"/>
-    <mergeCell ref="A230:A232"/>
-    <mergeCell ref="A233:A235"/>
-    <mergeCell ref="A206:A208"/>
-    <mergeCell ref="A209:A211"/>
-    <mergeCell ref="A212:A214"/>
-    <mergeCell ref="A215:A217"/>
-    <mergeCell ref="A218:A220"/>
-    <mergeCell ref="A191:A193"/>
-    <mergeCell ref="A194:A196"/>
-    <mergeCell ref="A197:A199"/>
-    <mergeCell ref="A200:A202"/>
-    <mergeCell ref="A203:A205"/>
-    <mergeCell ref="A176:A178"/>
-    <mergeCell ref="A179:A181"/>
-    <mergeCell ref="A182:A184"/>
-    <mergeCell ref="A185:A187"/>
-    <mergeCell ref="A188:A190"/>
-    <mergeCell ref="A161:A163"/>
-    <mergeCell ref="A164:A166"/>
-    <mergeCell ref="A167:A169"/>
-    <mergeCell ref="A170:A172"/>
-    <mergeCell ref="A173:A175"/>
-    <mergeCell ref="A146:A148"/>
-    <mergeCell ref="A149:A151"/>
-    <mergeCell ref="A152:A154"/>
-    <mergeCell ref="A155:A157"/>
-    <mergeCell ref="A158:A160"/>
-    <mergeCell ref="A131:A133"/>
-    <mergeCell ref="A134:A136"/>
-    <mergeCell ref="A137:A139"/>
-    <mergeCell ref="A140:A142"/>
-    <mergeCell ref="A143:A145"/>
-    <mergeCell ref="A116:A118"/>
-    <mergeCell ref="A119:A121"/>
-    <mergeCell ref="A122:A124"/>
-    <mergeCell ref="A125:A127"/>
-    <mergeCell ref="A128:A130"/>
-    <mergeCell ref="A101:A103"/>
-    <mergeCell ref="A104:A106"/>
-    <mergeCell ref="A107:A109"/>
-    <mergeCell ref="A110:A112"/>
-    <mergeCell ref="A113:A115"/>
-    <mergeCell ref="A86:A88"/>
-    <mergeCell ref="A89:A91"/>
-    <mergeCell ref="A92:A94"/>
-    <mergeCell ref="A95:A97"/>
-    <mergeCell ref="A98:A100"/>
-    <mergeCell ref="A71:A73"/>
-    <mergeCell ref="A74:A76"/>
-    <mergeCell ref="A77:A79"/>
-    <mergeCell ref="A80:A82"/>
-    <mergeCell ref="A83:A85"/>
-    <mergeCell ref="A56:A58"/>
-    <mergeCell ref="A59:A61"/>
-    <mergeCell ref="A62:A64"/>
-    <mergeCell ref="A65:A67"/>
-    <mergeCell ref="A68:A70"/>
-    <mergeCell ref="A41:A43"/>
-    <mergeCell ref="A44:A46"/>
-    <mergeCell ref="A47:A49"/>
-    <mergeCell ref="A50:A52"/>
-    <mergeCell ref="A53:A55"/>
     <mergeCell ref="A26:A28"/>
     <mergeCell ref="A29:A31"/>
     <mergeCell ref="A32:A34"/>
@@ -1923,6 +1792,137 @@
     <mergeCell ref="A8:A10"/>
     <mergeCell ref="A11:A13"/>
     <mergeCell ref="A14:A16"/>
+    <mergeCell ref="A56:A58"/>
+    <mergeCell ref="A59:A61"/>
+    <mergeCell ref="A62:A64"/>
+    <mergeCell ref="A65:A67"/>
+    <mergeCell ref="A68:A70"/>
+    <mergeCell ref="A41:A43"/>
+    <mergeCell ref="A44:A46"/>
+    <mergeCell ref="A47:A49"/>
+    <mergeCell ref="A50:A52"/>
+    <mergeCell ref="A53:A55"/>
+    <mergeCell ref="A86:A88"/>
+    <mergeCell ref="A89:A91"/>
+    <mergeCell ref="A92:A94"/>
+    <mergeCell ref="A95:A97"/>
+    <mergeCell ref="A98:A100"/>
+    <mergeCell ref="A71:A73"/>
+    <mergeCell ref="A74:A76"/>
+    <mergeCell ref="A77:A79"/>
+    <mergeCell ref="A80:A82"/>
+    <mergeCell ref="A83:A85"/>
+    <mergeCell ref="A116:A118"/>
+    <mergeCell ref="A119:A121"/>
+    <mergeCell ref="A122:A124"/>
+    <mergeCell ref="A125:A127"/>
+    <mergeCell ref="A128:A130"/>
+    <mergeCell ref="A101:A103"/>
+    <mergeCell ref="A104:A106"/>
+    <mergeCell ref="A107:A109"/>
+    <mergeCell ref="A110:A112"/>
+    <mergeCell ref="A113:A115"/>
+    <mergeCell ref="A146:A148"/>
+    <mergeCell ref="A149:A151"/>
+    <mergeCell ref="A152:A154"/>
+    <mergeCell ref="A155:A157"/>
+    <mergeCell ref="A158:A160"/>
+    <mergeCell ref="A131:A133"/>
+    <mergeCell ref="A134:A136"/>
+    <mergeCell ref="A137:A139"/>
+    <mergeCell ref="A140:A142"/>
+    <mergeCell ref="A143:A145"/>
+    <mergeCell ref="A176:A178"/>
+    <mergeCell ref="A179:A181"/>
+    <mergeCell ref="A182:A184"/>
+    <mergeCell ref="A185:A187"/>
+    <mergeCell ref="A188:A190"/>
+    <mergeCell ref="A161:A163"/>
+    <mergeCell ref="A164:A166"/>
+    <mergeCell ref="A167:A169"/>
+    <mergeCell ref="A170:A172"/>
+    <mergeCell ref="A173:A175"/>
+    <mergeCell ref="A206:A208"/>
+    <mergeCell ref="A209:A211"/>
+    <mergeCell ref="A212:A214"/>
+    <mergeCell ref="A215:A217"/>
+    <mergeCell ref="A218:A220"/>
+    <mergeCell ref="A191:A193"/>
+    <mergeCell ref="A194:A196"/>
+    <mergeCell ref="A197:A199"/>
+    <mergeCell ref="A200:A202"/>
+    <mergeCell ref="A203:A205"/>
+    <mergeCell ref="A236:A238"/>
+    <mergeCell ref="A239:A241"/>
+    <mergeCell ref="A242:A244"/>
+    <mergeCell ref="A245:A247"/>
+    <mergeCell ref="A248:A250"/>
+    <mergeCell ref="A221:A223"/>
+    <mergeCell ref="A224:A226"/>
+    <mergeCell ref="A227:A229"/>
+    <mergeCell ref="A230:A232"/>
+    <mergeCell ref="A233:A235"/>
+    <mergeCell ref="A266:A268"/>
+    <mergeCell ref="A269:A271"/>
+    <mergeCell ref="A272:A274"/>
+    <mergeCell ref="A275:A277"/>
+    <mergeCell ref="A278:A280"/>
+    <mergeCell ref="A251:A253"/>
+    <mergeCell ref="A254:A256"/>
+    <mergeCell ref="A257:A259"/>
+    <mergeCell ref="A260:A262"/>
+    <mergeCell ref="A263:A265"/>
+    <mergeCell ref="A296:A298"/>
+    <mergeCell ref="A299:A301"/>
+    <mergeCell ref="A302:A304"/>
+    <mergeCell ref="A305:A307"/>
+    <mergeCell ref="A308:A310"/>
+    <mergeCell ref="A281:A283"/>
+    <mergeCell ref="A284:A286"/>
+    <mergeCell ref="A287:A289"/>
+    <mergeCell ref="A290:A292"/>
+    <mergeCell ref="A293:A295"/>
+    <mergeCell ref="A326:A328"/>
+    <mergeCell ref="A329:A331"/>
+    <mergeCell ref="A332:A334"/>
+    <mergeCell ref="A335:A337"/>
+    <mergeCell ref="A338:A340"/>
+    <mergeCell ref="A311:A313"/>
+    <mergeCell ref="A314:A316"/>
+    <mergeCell ref="A317:A319"/>
+    <mergeCell ref="A320:A322"/>
+    <mergeCell ref="A323:A325"/>
+    <mergeCell ref="A356:A358"/>
+    <mergeCell ref="A359:A361"/>
+    <mergeCell ref="A362:A364"/>
+    <mergeCell ref="A365:A367"/>
+    <mergeCell ref="A368:A370"/>
+    <mergeCell ref="A341:A343"/>
+    <mergeCell ref="A344:A346"/>
+    <mergeCell ref="A347:A349"/>
+    <mergeCell ref="A350:A352"/>
+    <mergeCell ref="A353:A355"/>
+    <mergeCell ref="A386:A388"/>
+    <mergeCell ref="A389:A391"/>
+    <mergeCell ref="A392:A394"/>
+    <mergeCell ref="A395:A397"/>
+    <mergeCell ref="A398:A400"/>
+    <mergeCell ref="A371:A373"/>
+    <mergeCell ref="A374:A376"/>
+    <mergeCell ref="A377:A379"/>
+    <mergeCell ref="A380:A382"/>
+    <mergeCell ref="A383:A385"/>
+    <mergeCell ref="A431:A433"/>
+    <mergeCell ref="A416:A418"/>
+    <mergeCell ref="A419:A421"/>
+    <mergeCell ref="A422:A424"/>
+    <mergeCell ref="A425:A427"/>
+    <mergeCell ref="A428:A430"/>
+    <mergeCell ref="A401:A403"/>
+    <mergeCell ref="A404:A406"/>
+    <mergeCell ref="A407:A409"/>
+    <mergeCell ref="A410:A412"/>
+    <mergeCell ref="A413:A415"/>
   </mergeCells>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" r:id="rId1"/>

--- a/planilhas/Planilha de Base para Cotacao.xlsx
+++ b/planilhas/Planilha de Base para Cotacao.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/0a19316afdd125d6/Documentos/GitHub/hawks-automations/planilhas/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="617" documentId="8_{B6B05E56-6ADC-4554-A921-81DFAB966C0D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6FA55701-10BF-4054-9E6E-05811B8A888A}"/>
+  <xr:revisionPtr revIDLastSave="633" documentId="8_{B6B05E56-6ADC-4554-A921-81DFAB966C0D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0005AC5C-663B-4F20-B498-C90DA5113D46}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="21840" windowHeight="13140" xr2:uid="{AB0A4C4E-1938-46F3-8FAE-9EC8B05F0B3E}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="7">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
   <si>
     <t>Peça</t>
   </si>
@@ -60,6 +60,9 @@
   </si>
   <si>
     <t>Código</t>
+  </si>
+  <si>
+    <t>Rmp (40)</t>
   </si>
 </sst>
 </file>
@@ -450,9 +453,9 @@
     <col min="2" max="2" width="11.7109375" style="2" customWidth="1"/>
     <col min="3" max="3" width="11.85546875" style="2" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="13.7109375" style="2" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="11.85546875" style="2" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="22" style="2" bestFit="1" customWidth="1"/>
-    <col min="8" max="16384" width="9.140625" style="2"/>
+    <col min="5" max="7" width="11.85546875" style="2" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="22" style="2" bestFit="1" customWidth="1"/>
+    <col min="9" max="16384" width="9.140625" style="2"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9" s="1" customFormat="1" x14ac:dyDescent="0.25">
@@ -475,6 +478,9 @@
         <v>4</v>
       </c>
       <c r="G1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1" s="1" t="s">
         <v>5</v>
       </c>
     </row>
@@ -483,11 +489,11 @@
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3" s="5"/>
-      <c r="G3" s="3"/>
+      <c r="H3" s="3"/>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" s="5"/>
-      <c r="G4" s="3"/>
+      <c r="H4" s="3"/>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A5" s="5"/>
@@ -1779,6 +1785,137 @@
     </row>
   </sheetData>
   <mergeCells count="144">
+    <mergeCell ref="A431:A433"/>
+    <mergeCell ref="A416:A418"/>
+    <mergeCell ref="A419:A421"/>
+    <mergeCell ref="A422:A424"/>
+    <mergeCell ref="A425:A427"/>
+    <mergeCell ref="A428:A430"/>
+    <mergeCell ref="A401:A403"/>
+    <mergeCell ref="A404:A406"/>
+    <mergeCell ref="A407:A409"/>
+    <mergeCell ref="A410:A412"/>
+    <mergeCell ref="A413:A415"/>
+    <mergeCell ref="A386:A388"/>
+    <mergeCell ref="A389:A391"/>
+    <mergeCell ref="A392:A394"/>
+    <mergeCell ref="A395:A397"/>
+    <mergeCell ref="A398:A400"/>
+    <mergeCell ref="A371:A373"/>
+    <mergeCell ref="A374:A376"/>
+    <mergeCell ref="A377:A379"/>
+    <mergeCell ref="A380:A382"/>
+    <mergeCell ref="A383:A385"/>
+    <mergeCell ref="A356:A358"/>
+    <mergeCell ref="A359:A361"/>
+    <mergeCell ref="A362:A364"/>
+    <mergeCell ref="A365:A367"/>
+    <mergeCell ref="A368:A370"/>
+    <mergeCell ref="A341:A343"/>
+    <mergeCell ref="A344:A346"/>
+    <mergeCell ref="A347:A349"/>
+    <mergeCell ref="A350:A352"/>
+    <mergeCell ref="A353:A355"/>
+    <mergeCell ref="A326:A328"/>
+    <mergeCell ref="A329:A331"/>
+    <mergeCell ref="A332:A334"/>
+    <mergeCell ref="A335:A337"/>
+    <mergeCell ref="A338:A340"/>
+    <mergeCell ref="A311:A313"/>
+    <mergeCell ref="A314:A316"/>
+    <mergeCell ref="A317:A319"/>
+    <mergeCell ref="A320:A322"/>
+    <mergeCell ref="A323:A325"/>
+    <mergeCell ref="A296:A298"/>
+    <mergeCell ref="A299:A301"/>
+    <mergeCell ref="A302:A304"/>
+    <mergeCell ref="A305:A307"/>
+    <mergeCell ref="A308:A310"/>
+    <mergeCell ref="A281:A283"/>
+    <mergeCell ref="A284:A286"/>
+    <mergeCell ref="A287:A289"/>
+    <mergeCell ref="A290:A292"/>
+    <mergeCell ref="A293:A295"/>
+    <mergeCell ref="A266:A268"/>
+    <mergeCell ref="A269:A271"/>
+    <mergeCell ref="A272:A274"/>
+    <mergeCell ref="A275:A277"/>
+    <mergeCell ref="A278:A280"/>
+    <mergeCell ref="A251:A253"/>
+    <mergeCell ref="A254:A256"/>
+    <mergeCell ref="A257:A259"/>
+    <mergeCell ref="A260:A262"/>
+    <mergeCell ref="A263:A265"/>
+    <mergeCell ref="A236:A238"/>
+    <mergeCell ref="A239:A241"/>
+    <mergeCell ref="A242:A244"/>
+    <mergeCell ref="A245:A247"/>
+    <mergeCell ref="A248:A250"/>
+    <mergeCell ref="A221:A223"/>
+    <mergeCell ref="A224:A226"/>
+    <mergeCell ref="A227:A229"/>
+    <mergeCell ref="A230:A232"/>
+    <mergeCell ref="A233:A235"/>
+    <mergeCell ref="A206:A208"/>
+    <mergeCell ref="A209:A211"/>
+    <mergeCell ref="A212:A214"/>
+    <mergeCell ref="A215:A217"/>
+    <mergeCell ref="A218:A220"/>
+    <mergeCell ref="A191:A193"/>
+    <mergeCell ref="A194:A196"/>
+    <mergeCell ref="A197:A199"/>
+    <mergeCell ref="A200:A202"/>
+    <mergeCell ref="A203:A205"/>
+    <mergeCell ref="A176:A178"/>
+    <mergeCell ref="A179:A181"/>
+    <mergeCell ref="A182:A184"/>
+    <mergeCell ref="A185:A187"/>
+    <mergeCell ref="A188:A190"/>
+    <mergeCell ref="A161:A163"/>
+    <mergeCell ref="A164:A166"/>
+    <mergeCell ref="A167:A169"/>
+    <mergeCell ref="A170:A172"/>
+    <mergeCell ref="A173:A175"/>
+    <mergeCell ref="A146:A148"/>
+    <mergeCell ref="A149:A151"/>
+    <mergeCell ref="A152:A154"/>
+    <mergeCell ref="A155:A157"/>
+    <mergeCell ref="A158:A160"/>
+    <mergeCell ref="A131:A133"/>
+    <mergeCell ref="A134:A136"/>
+    <mergeCell ref="A137:A139"/>
+    <mergeCell ref="A140:A142"/>
+    <mergeCell ref="A143:A145"/>
+    <mergeCell ref="A116:A118"/>
+    <mergeCell ref="A119:A121"/>
+    <mergeCell ref="A122:A124"/>
+    <mergeCell ref="A125:A127"/>
+    <mergeCell ref="A128:A130"/>
+    <mergeCell ref="A101:A103"/>
+    <mergeCell ref="A104:A106"/>
+    <mergeCell ref="A107:A109"/>
+    <mergeCell ref="A110:A112"/>
+    <mergeCell ref="A113:A115"/>
+    <mergeCell ref="A86:A88"/>
+    <mergeCell ref="A89:A91"/>
+    <mergeCell ref="A92:A94"/>
+    <mergeCell ref="A95:A97"/>
+    <mergeCell ref="A98:A100"/>
+    <mergeCell ref="A71:A73"/>
+    <mergeCell ref="A74:A76"/>
+    <mergeCell ref="A77:A79"/>
+    <mergeCell ref="A80:A82"/>
+    <mergeCell ref="A83:A85"/>
+    <mergeCell ref="A56:A58"/>
+    <mergeCell ref="A59:A61"/>
+    <mergeCell ref="A62:A64"/>
+    <mergeCell ref="A65:A67"/>
+    <mergeCell ref="A68:A70"/>
+    <mergeCell ref="A41:A43"/>
+    <mergeCell ref="A44:A46"/>
+    <mergeCell ref="A47:A49"/>
+    <mergeCell ref="A50:A52"/>
+    <mergeCell ref="A53:A55"/>
     <mergeCell ref="A26:A28"/>
     <mergeCell ref="A29:A31"/>
     <mergeCell ref="A32:A34"/>
@@ -1792,137 +1929,6 @@
     <mergeCell ref="A8:A10"/>
     <mergeCell ref="A11:A13"/>
     <mergeCell ref="A14:A16"/>
-    <mergeCell ref="A56:A58"/>
-    <mergeCell ref="A59:A61"/>
-    <mergeCell ref="A62:A64"/>
-    <mergeCell ref="A65:A67"/>
-    <mergeCell ref="A68:A70"/>
-    <mergeCell ref="A41:A43"/>
-    <mergeCell ref="A44:A46"/>
-    <mergeCell ref="A47:A49"/>
-    <mergeCell ref="A50:A52"/>
-    <mergeCell ref="A53:A55"/>
-    <mergeCell ref="A86:A88"/>
-    <mergeCell ref="A89:A91"/>
-    <mergeCell ref="A92:A94"/>
-    <mergeCell ref="A95:A97"/>
-    <mergeCell ref="A98:A100"/>
-    <mergeCell ref="A71:A73"/>
-    <mergeCell ref="A74:A76"/>
-    <mergeCell ref="A77:A79"/>
-    <mergeCell ref="A80:A82"/>
-    <mergeCell ref="A83:A85"/>
-    <mergeCell ref="A116:A118"/>
-    <mergeCell ref="A119:A121"/>
-    <mergeCell ref="A122:A124"/>
-    <mergeCell ref="A125:A127"/>
-    <mergeCell ref="A128:A130"/>
-    <mergeCell ref="A101:A103"/>
-    <mergeCell ref="A104:A106"/>
-    <mergeCell ref="A107:A109"/>
-    <mergeCell ref="A110:A112"/>
-    <mergeCell ref="A113:A115"/>
-    <mergeCell ref="A146:A148"/>
-    <mergeCell ref="A149:A151"/>
-    <mergeCell ref="A152:A154"/>
-    <mergeCell ref="A155:A157"/>
-    <mergeCell ref="A158:A160"/>
-    <mergeCell ref="A131:A133"/>
-    <mergeCell ref="A134:A136"/>
-    <mergeCell ref="A137:A139"/>
-    <mergeCell ref="A140:A142"/>
-    <mergeCell ref="A143:A145"/>
-    <mergeCell ref="A176:A178"/>
-    <mergeCell ref="A179:A181"/>
-    <mergeCell ref="A182:A184"/>
-    <mergeCell ref="A185:A187"/>
-    <mergeCell ref="A188:A190"/>
-    <mergeCell ref="A161:A163"/>
-    <mergeCell ref="A164:A166"/>
-    <mergeCell ref="A167:A169"/>
-    <mergeCell ref="A170:A172"/>
-    <mergeCell ref="A173:A175"/>
-    <mergeCell ref="A206:A208"/>
-    <mergeCell ref="A209:A211"/>
-    <mergeCell ref="A212:A214"/>
-    <mergeCell ref="A215:A217"/>
-    <mergeCell ref="A218:A220"/>
-    <mergeCell ref="A191:A193"/>
-    <mergeCell ref="A194:A196"/>
-    <mergeCell ref="A197:A199"/>
-    <mergeCell ref="A200:A202"/>
-    <mergeCell ref="A203:A205"/>
-    <mergeCell ref="A236:A238"/>
-    <mergeCell ref="A239:A241"/>
-    <mergeCell ref="A242:A244"/>
-    <mergeCell ref="A245:A247"/>
-    <mergeCell ref="A248:A250"/>
-    <mergeCell ref="A221:A223"/>
-    <mergeCell ref="A224:A226"/>
-    <mergeCell ref="A227:A229"/>
-    <mergeCell ref="A230:A232"/>
-    <mergeCell ref="A233:A235"/>
-    <mergeCell ref="A266:A268"/>
-    <mergeCell ref="A269:A271"/>
-    <mergeCell ref="A272:A274"/>
-    <mergeCell ref="A275:A277"/>
-    <mergeCell ref="A278:A280"/>
-    <mergeCell ref="A251:A253"/>
-    <mergeCell ref="A254:A256"/>
-    <mergeCell ref="A257:A259"/>
-    <mergeCell ref="A260:A262"/>
-    <mergeCell ref="A263:A265"/>
-    <mergeCell ref="A296:A298"/>
-    <mergeCell ref="A299:A301"/>
-    <mergeCell ref="A302:A304"/>
-    <mergeCell ref="A305:A307"/>
-    <mergeCell ref="A308:A310"/>
-    <mergeCell ref="A281:A283"/>
-    <mergeCell ref="A284:A286"/>
-    <mergeCell ref="A287:A289"/>
-    <mergeCell ref="A290:A292"/>
-    <mergeCell ref="A293:A295"/>
-    <mergeCell ref="A326:A328"/>
-    <mergeCell ref="A329:A331"/>
-    <mergeCell ref="A332:A334"/>
-    <mergeCell ref="A335:A337"/>
-    <mergeCell ref="A338:A340"/>
-    <mergeCell ref="A311:A313"/>
-    <mergeCell ref="A314:A316"/>
-    <mergeCell ref="A317:A319"/>
-    <mergeCell ref="A320:A322"/>
-    <mergeCell ref="A323:A325"/>
-    <mergeCell ref="A356:A358"/>
-    <mergeCell ref="A359:A361"/>
-    <mergeCell ref="A362:A364"/>
-    <mergeCell ref="A365:A367"/>
-    <mergeCell ref="A368:A370"/>
-    <mergeCell ref="A341:A343"/>
-    <mergeCell ref="A344:A346"/>
-    <mergeCell ref="A347:A349"/>
-    <mergeCell ref="A350:A352"/>
-    <mergeCell ref="A353:A355"/>
-    <mergeCell ref="A386:A388"/>
-    <mergeCell ref="A389:A391"/>
-    <mergeCell ref="A392:A394"/>
-    <mergeCell ref="A395:A397"/>
-    <mergeCell ref="A398:A400"/>
-    <mergeCell ref="A371:A373"/>
-    <mergeCell ref="A374:A376"/>
-    <mergeCell ref="A377:A379"/>
-    <mergeCell ref="A380:A382"/>
-    <mergeCell ref="A383:A385"/>
-    <mergeCell ref="A431:A433"/>
-    <mergeCell ref="A416:A418"/>
-    <mergeCell ref="A419:A421"/>
-    <mergeCell ref="A422:A424"/>
-    <mergeCell ref="A425:A427"/>
-    <mergeCell ref="A428:A430"/>
-    <mergeCell ref="A401:A403"/>
-    <mergeCell ref="A404:A406"/>
-    <mergeCell ref="A407:A409"/>
-    <mergeCell ref="A410:A412"/>
-    <mergeCell ref="A413:A415"/>
   </mergeCells>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" r:id="rId1"/>

--- a/planilhas/Planilha de Base para Cotacao.xlsx
+++ b/planilhas/Planilha de Base para Cotacao.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/0a19316afdd125d6/Documentos/GitHub/hawks-automations/planilhas/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="633" documentId="8_{B6B05E56-6ADC-4554-A921-81DFAB966C0D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0005AC5C-663B-4F20-B498-C90DA5113D46}"/>
+  <xr:revisionPtr revIDLastSave="669" documentId="8_{B6B05E56-6ADC-4554-A921-81DFAB966C0D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3D5FCF2D-A3D6-4171-992B-D2F3DF5FB523}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="21840" windowHeight="13140" xr2:uid="{AB0A4C4E-1938-46F3-8FAE-9EC8B05F0B3E}"/>
   </bookViews>
@@ -38,8 +38,30 @@
 </workbook>
 </file>
 
+<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+  <metadataTypes count="1">
+    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
+  </metadataTypes>
+  <futureMetadata name="XLDAPR" count="1">
+    <bk>
+      <extLst>
+        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
+          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
+        </ext>
+      </extLst>
+    </bk>
+  </futureMetadata>
+  <cellMetadata count="1">
+    <bk>
+      <rc t="1" v="0"/>
+    </bk>
+  </cellMetadata>
+</metadata>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="17">
   <si>
     <t>Peça</t>
   </si>
@@ -63,6 +85,33 @@
   </si>
   <si>
     <t>Rmp (40)</t>
+  </si>
+  <si>
+    <t>LFR6B</t>
+  </si>
+  <si>
+    <t xml:space="preserve">VELA DE IGNIÇÃO BOSCH </t>
+  </si>
+  <si>
+    <t>Indisponível</t>
+  </si>
+  <si>
+    <t>F000KE0P31</t>
+  </si>
+  <si>
+    <t>OX3392D</t>
+  </si>
+  <si>
+    <t>HU71151X</t>
+  </si>
+  <si>
+    <t>WOE710</t>
+  </si>
+  <si>
+    <t>LX1745</t>
+  </si>
+  <si>
+    <t>C42922</t>
   </si>
 </sst>
 </file>
@@ -143,10 +192,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -485,10 +530,49 @@
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A2" s="5"/>
+      <c r="A2" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C2" s="2">
+        <f>36.5 +15</f>
+        <v>51.5</v>
+      </c>
+      <c r="D2" s="2" t="e" cm="1">
+        <f t="array" ref="D2">F000KE0P51+7</f>
+        <v>#NAME?</v>
+      </c>
+      <c r="E2" s="2">
+        <f>29.09+10</f>
+        <v>39.090000000000003</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>10</v>
+      </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3" s="5"/>
+      <c r="B3" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C3" s="2">
+        <f>36.5 +15</f>
+        <v>51.5</v>
+      </c>
+      <c r="D3" s="2">
+        <f>155.34+7</f>
+        <v>162.34</v>
+      </c>
+      <c r="E3" s="2">
+        <f>33.29+10</f>
+        <v>43.29</v>
+      </c>
+      <c r="F3" s="2">
+        <f>30.42+10</f>
+        <v>40.42</v>
+      </c>
       <c r="H3" s="3"/>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.25">
@@ -497,19 +581,108 @@
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A5" s="5"/>
+      <c r="B5" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D5" s="2">
+        <f>41.3+7</f>
+        <v>48.3</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="F5" s="2" t="s">
+        <v>10</v>
+      </c>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A6" s="5"/>
+      <c r="B6" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C6" s="2">
+        <f>21.2+15</f>
+        <v>36.200000000000003</v>
+      </c>
+      <c r="D6" s="2">
+        <f>19.69+7</f>
+        <v>26.69</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="F6" s="2">
+        <f>19.08+10</f>
+        <v>29.08</v>
+      </c>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A7" s="5"/>
+      <c r="B7" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C7" s="2">
+        <f>16.7+15</f>
+        <v>31.7</v>
+      </c>
+      <c r="D7" s="2">
+        <f>15.52+7</f>
+        <v>22.52</v>
+      </c>
+      <c r="E7" s="2">
+        <f>16.47+10</f>
+        <v>26.47</v>
+      </c>
+      <c r="F7" s="2" t="s">
+        <v>10</v>
+      </c>
       <c r="I7" s="4"/>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A8" s="5"/>
+      <c r="B8" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C8" s="2">
+        <f>47.3+15</f>
+        <v>62.3</v>
+      </c>
+      <c r="D8" s="2">
+        <f>42.87+7</f>
+        <v>49.87</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="F8" s="2">
+        <f>43.23+10</f>
+        <v>53.23</v>
+      </c>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A9" s="5"/>
+      <c r="B9" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C9" s="2">
+        <f>43.6+15</f>
+        <v>58.6</v>
+      </c>
+      <c r="D9" s="2">
+        <f>60.37+7</f>
+        <v>67.37</v>
+      </c>
+      <c r="E9" s="2">
+        <f>51.75+10</f>
+        <v>61.75</v>
+      </c>
+      <c r="F9" s="2">
+        <f>51.58+10</f>
+        <v>61.58</v>
+      </c>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A10" s="5"/>
@@ -1785,137 +1958,6 @@
     </row>
   </sheetData>
   <mergeCells count="144">
-    <mergeCell ref="A431:A433"/>
-    <mergeCell ref="A416:A418"/>
-    <mergeCell ref="A419:A421"/>
-    <mergeCell ref="A422:A424"/>
-    <mergeCell ref="A425:A427"/>
-    <mergeCell ref="A428:A430"/>
-    <mergeCell ref="A401:A403"/>
-    <mergeCell ref="A404:A406"/>
-    <mergeCell ref="A407:A409"/>
-    <mergeCell ref="A410:A412"/>
-    <mergeCell ref="A413:A415"/>
-    <mergeCell ref="A386:A388"/>
-    <mergeCell ref="A389:A391"/>
-    <mergeCell ref="A392:A394"/>
-    <mergeCell ref="A395:A397"/>
-    <mergeCell ref="A398:A400"/>
-    <mergeCell ref="A371:A373"/>
-    <mergeCell ref="A374:A376"/>
-    <mergeCell ref="A377:A379"/>
-    <mergeCell ref="A380:A382"/>
-    <mergeCell ref="A383:A385"/>
-    <mergeCell ref="A356:A358"/>
-    <mergeCell ref="A359:A361"/>
-    <mergeCell ref="A362:A364"/>
-    <mergeCell ref="A365:A367"/>
-    <mergeCell ref="A368:A370"/>
-    <mergeCell ref="A341:A343"/>
-    <mergeCell ref="A344:A346"/>
-    <mergeCell ref="A347:A349"/>
-    <mergeCell ref="A350:A352"/>
-    <mergeCell ref="A353:A355"/>
-    <mergeCell ref="A326:A328"/>
-    <mergeCell ref="A329:A331"/>
-    <mergeCell ref="A332:A334"/>
-    <mergeCell ref="A335:A337"/>
-    <mergeCell ref="A338:A340"/>
-    <mergeCell ref="A311:A313"/>
-    <mergeCell ref="A314:A316"/>
-    <mergeCell ref="A317:A319"/>
-    <mergeCell ref="A320:A322"/>
-    <mergeCell ref="A323:A325"/>
-    <mergeCell ref="A296:A298"/>
-    <mergeCell ref="A299:A301"/>
-    <mergeCell ref="A302:A304"/>
-    <mergeCell ref="A305:A307"/>
-    <mergeCell ref="A308:A310"/>
-    <mergeCell ref="A281:A283"/>
-    <mergeCell ref="A284:A286"/>
-    <mergeCell ref="A287:A289"/>
-    <mergeCell ref="A290:A292"/>
-    <mergeCell ref="A293:A295"/>
-    <mergeCell ref="A266:A268"/>
-    <mergeCell ref="A269:A271"/>
-    <mergeCell ref="A272:A274"/>
-    <mergeCell ref="A275:A277"/>
-    <mergeCell ref="A278:A280"/>
-    <mergeCell ref="A251:A253"/>
-    <mergeCell ref="A254:A256"/>
-    <mergeCell ref="A257:A259"/>
-    <mergeCell ref="A260:A262"/>
-    <mergeCell ref="A263:A265"/>
-    <mergeCell ref="A236:A238"/>
-    <mergeCell ref="A239:A241"/>
-    <mergeCell ref="A242:A244"/>
-    <mergeCell ref="A245:A247"/>
-    <mergeCell ref="A248:A250"/>
-    <mergeCell ref="A221:A223"/>
-    <mergeCell ref="A224:A226"/>
-    <mergeCell ref="A227:A229"/>
-    <mergeCell ref="A230:A232"/>
-    <mergeCell ref="A233:A235"/>
-    <mergeCell ref="A206:A208"/>
-    <mergeCell ref="A209:A211"/>
-    <mergeCell ref="A212:A214"/>
-    <mergeCell ref="A215:A217"/>
-    <mergeCell ref="A218:A220"/>
-    <mergeCell ref="A191:A193"/>
-    <mergeCell ref="A194:A196"/>
-    <mergeCell ref="A197:A199"/>
-    <mergeCell ref="A200:A202"/>
-    <mergeCell ref="A203:A205"/>
-    <mergeCell ref="A176:A178"/>
-    <mergeCell ref="A179:A181"/>
-    <mergeCell ref="A182:A184"/>
-    <mergeCell ref="A185:A187"/>
-    <mergeCell ref="A188:A190"/>
-    <mergeCell ref="A161:A163"/>
-    <mergeCell ref="A164:A166"/>
-    <mergeCell ref="A167:A169"/>
-    <mergeCell ref="A170:A172"/>
-    <mergeCell ref="A173:A175"/>
-    <mergeCell ref="A146:A148"/>
-    <mergeCell ref="A149:A151"/>
-    <mergeCell ref="A152:A154"/>
-    <mergeCell ref="A155:A157"/>
-    <mergeCell ref="A158:A160"/>
-    <mergeCell ref="A131:A133"/>
-    <mergeCell ref="A134:A136"/>
-    <mergeCell ref="A137:A139"/>
-    <mergeCell ref="A140:A142"/>
-    <mergeCell ref="A143:A145"/>
-    <mergeCell ref="A116:A118"/>
-    <mergeCell ref="A119:A121"/>
-    <mergeCell ref="A122:A124"/>
-    <mergeCell ref="A125:A127"/>
-    <mergeCell ref="A128:A130"/>
-    <mergeCell ref="A101:A103"/>
-    <mergeCell ref="A104:A106"/>
-    <mergeCell ref="A107:A109"/>
-    <mergeCell ref="A110:A112"/>
-    <mergeCell ref="A113:A115"/>
-    <mergeCell ref="A86:A88"/>
-    <mergeCell ref="A89:A91"/>
-    <mergeCell ref="A92:A94"/>
-    <mergeCell ref="A95:A97"/>
-    <mergeCell ref="A98:A100"/>
-    <mergeCell ref="A71:A73"/>
-    <mergeCell ref="A74:A76"/>
-    <mergeCell ref="A77:A79"/>
-    <mergeCell ref="A80:A82"/>
-    <mergeCell ref="A83:A85"/>
-    <mergeCell ref="A56:A58"/>
-    <mergeCell ref="A59:A61"/>
-    <mergeCell ref="A62:A64"/>
-    <mergeCell ref="A65:A67"/>
-    <mergeCell ref="A68:A70"/>
-    <mergeCell ref="A41:A43"/>
-    <mergeCell ref="A44:A46"/>
-    <mergeCell ref="A47:A49"/>
-    <mergeCell ref="A50:A52"/>
-    <mergeCell ref="A53:A55"/>
     <mergeCell ref="A26:A28"/>
     <mergeCell ref="A29:A31"/>
     <mergeCell ref="A32:A34"/>
@@ -1929,6 +1971,137 @@
     <mergeCell ref="A8:A10"/>
     <mergeCell ref="A11:A13"/>
     <mergeCell ref="A14:A16"/>
+    <mergeCell ref="A56:A58"/>
+    <mergeCell ref="A59:A61"/>
+    <mergeCell ref="A62:A64"/>
+    <mergeCell ref="A65:A67"/>
+    <mergeCell ref="A68:A70"/>
+    <mergeCell ref="A41:A43"/>
+    <mergeCell ref="A44:A46"/>
+    <mergeCell ref="A47:A49"/>
+    <mergeCell ref="A50:A52"/>
+    <mergeCell ref="A53:A55"/>
+    <mergeCell ref="A86:A88"/>
+    <mergeCell ref="A89:A91"/>
+    <mergeCell ref="A92:A94"/>
+    <mergeCell ref="A95:A97"/>
+    <mergeCell ref="A98:A100"/>
+    <mergeCell ref="A71:A73"/>
+    <mergeCell ref="A74:A76"/>
+    <mergeCell ref="A77:A79"/>
+    <mergeCell ref="A80:A82"/>
+    <mergeCell ref="A83:A85"/>
+    <mergeCell ref="A116:A118"/>
+    <mergeCell ref="A119:A121"/>
+    <mergeCell ref="A122:A124"/>
+    <mergeCell ref="A125:A127"/>
+    <mergeCell ref="A128:A130"/>
+    <mergeCell ref="A101:A103"/>
+    <mergeCell ref="A104:A106"/>
+    <mergeCell ref="A107:A109"/>
+    <mergeCell ref="A110:A112"/>
+    <mergeCell ref="A113:A115"/>
+    <mergeCell ref="A146:A148"/>
+    <mergeCell ref="A149:A151"/>
+    <mergeCell ref="A152:A154"/>
+    <mergeCell ref="A155:A157"/>
+    <mergeCell ref="A158:A160"/>
+    <mergeCell ref="A131:A133"/>
+    <mergeCell ref="A134:A136"/>
+    <mergeCell ref="A137:A139"/>
+    <mergeCell ref="A140:A142"/>
+    <mergeCell ref="A143:A145"/>
+    <mergeCell ref="A176:A178"/>
+    <mergeCell ref="A179:A181"/>
+    <mergeCell ref="A182:A184"/>
+    <mergeCell ref="A185:A187"/>
+    <mergeCell ref="A188:A190"/>
+    <mergeCell ref="A161:A163"/>
+    <mergeCell ref="A164:A166"/>
+    <mergeCell ref="A167:A169"/>
+    <mergeCell ref="A170:A172"/>
+    <mergeCell ref="A173:A175"/>
+    <mergeCell ref="A206:A208"/>
+    <mergeCell ref="A209:A211"/>
+    <mergeCell ref="A212:A214"/>
+    <mergeCell ref="A215:A217"/>
+    <mergeCell ref="A218:A220"/>
+    <mergeCell ref="A191:A193"/>
+    <mergeCell ref="A194:A196"/>
+    <mergeCell ref="A197:A199"/>
+    <mergeCell ref="A200:A202"/>
+    <mergeCell ref="A203:A205"/>
+    <mergeCell ref="A236:A238"/>
+    <mergeCell ref="A239:A241"/>
+    <mergeCell ref="A242:A244"/>
+    <mergeCell ref="A245:A247"/>
+    <mergeCell ref="A248:A250"/>
+    <mergeCell ref="A221:A223"/>
+    <mergeCell ref="A224:A226"/>
+    <mergeCell ref="A227:A229"/>
+    <mergeCell ref="A230:A232"/>
+    <mergeCell ref="A233:A235"/>
+    <mergeCell ref="A266:A268"/>
+    <mergeCell ref="A269:A271"/>
+    <mergeCell ref="A272:A274"/>
+    <mergeCell ref="A275:A277"/>
+    <mergeCell ref="A278:A280"/>
+    <mergeCell ref="A251:A253"/>
+    <mergeCell ref="A254:A256"/>
+    <mergeCell ref="A257:A259"/>
+    <mergeCell ref="A260:A262"/>
+    <mergeCell ref="A263:A265"/>
+    <mergeCell ref="A296:A298"/>
+    <mergeCell ref="A299:A301"/>
+    <mergeCell ref="A302:A304"/>
+    <mergeCell ref="A305:A307"/>
+    <mergeCell ref="A308:A310"/>
+    <mergeCell ref="A281:A283"/>
+    <mergeCell ref="A284:A286"/>
+    <mergeCell ref="A287:A289"/>
+    <mergeCell ref="A290:A292"/>
+    <mergeCell ref="A293:A295"/>
+    <mergeCell ref="A326:A328"/>
+    <mergeCell ref="A329:A331"/>
+    <mergeCell ref="A332:A334"/>
+    <mergeCell ref="A335:A337"/>
+    <mergeCell ref="A338:A340"/>
+    <mergeCell ref="A311:A313"/>
+    <mergeCell ref="A314:A316"/>
+    <mergeCell ref="A317:A319"/>
+    <mergeCell ref="A320:A322"/>
+    <mergeCell ref="A323:A325"/>
+    <mergeCell ref="A356:A358"/>
+    <mergeCell ref="A359:A361"/>
+    <mergeCell ref="A362:A364"/>
+    <mergeCell ref="A365:A367"/>
+    <mergeCell ref="A368:A370"/>
+    <mergeCell ref="A341:A343"/>
+    <mergeCell ref="A344:A346"/>
+    <mergeCell ref="A347:A349"/>
+    <mergeCell ref="A350:A352"/>
+    <mergeCell ref="A353:A355"/>
+    <mergeCell ref="A386:A388"/>
+    <mergeCell ref="A389:A391"/>
+    <mergeCell ref="A392:A394"/>
+    <mergeCell ref="A395:A397"/>
+    <mergeCell ref="A398:A400"/>
+    <mergeCell ref="A371:A373"/>
+    <mergeCell ref="A374:A376"/>
+    <mergeCell ref="A377:A379"/>
+    <mergeCell ref="A380:A382"/>
+    <mergeCell ref="A383:A385"/>
+    <mergeCell ref="A431:A433"/>
+    <mergeCell ref="A416:A418"/>
+    <mergeCell ref="A419:A421"/>
+    <mergeCell ref="A422:A424"/>
+    <mergeCell ref="A425:A427"/>
+    <mergeCell ref="A428:A430"/>
+    <mergeCell ref="A401:A403"/>
+    <mergeCell ref="A404:A406"/>
+    <mergeCell ref="A407:A409"/>
+    <mergeCell ref="A410:A412"/>
+    <mergeCell ref="A413:A415"/>
   </mergeCells>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" r:id="rId1"/>

--- a/planilhas/Planilha de Base para Cotacao.xlsx
+++ b/planilhas/Planilha de Base para Cotacao.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/0a19316afdd125d6/Documentos/GitHub/hawks-automations/planilhas/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="669" documentId="8_{B6B05E56-6ADC-4554-A921-81DFAB966C0D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3D5FCF2D-A3D6-4171-992B-D2F3DF5FB523}"/>
+  <xr:revisionPtr revIDLastSave="670" documentId="8_{B6B05E56-6ADC-4554-A921-81DFAB966C0D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C10EC37B-2BDA-4D1C-A6BF-BDEF01CE98EB}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="21840" windowHeight="13140" xr2:uid="{AB0A4C4E-1938-46F3-8FAE-9EC8B05F0B3E}"/>
   </bookViews>
@@ -38,30 +38,8 @@
 </workbook>
 </file>
 
-<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
-  <metadataTypes count="1">
-    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
-  </metadataTypes>
-  <futureMetadata name="XLDAPR" count="1">
-    <bk>
-      <extLst>
-        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
-          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
-        </ext>
-      </extLst>
-    </bk>
-  </futureMetadata>
-  <cellMetadata count="1">
-    <bk>
-      <rc t="1" v="0"/>
-    </bk>
-  </cellMetadata>
-</metadata>
-</file>
-
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
   <si>
     <t>Peça</t>
   </si>
@@ -85,33 +63,6 @@
   </si>
   <si>
     <t>Rmp (40)</t>
-  </si>
-  <si>
-    <t>LFR6B</t>
-  </si>
-  <si>
-    <t xml:space="preserve">VELA DE IGNIÇÃO BOSCH </t>
-  </si>
-  <si>
-    <t>Indisponível</t>
-  </si>
-  <si>
-    <t>F000KE0P31</t>
-  </si>
-  <si>
-    <t>OX3392D</t>
-  </si>
-  <si>
-    <t>HU71151X</t>
-  </si>
-  <si>
-    <t>WOE710</t>
-  </si>
-  <si>
-    <t>LX1745</t>
-  </si>
-  <si>
-    <t>C42922</t>
   </si>
 </sst>
 </file>
@@ -530,49 +481,10 @@
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A2" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="C2" s="2">
-        <f>36.5 +15</f>
-        <v>51.5</v>
-      </c>
-      <c r="D2" s="2" t="e" cm="1">
-        <f t="array" ref="D2">F000KE0P51+7</f>
-        <v>#NAME?</v>
-      </c>
-      <c r="E2" s="2">
-        <f>29.09+10</f>
-        <v>39.090000000000003</v>
-      </c>
-      <c r="F2" s="2" t="s">
-        <v>10</v>
-      </c>
+      <c r="A2" s="5"/>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3" s="5"/>
-      <c r="B3" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="C3" s="2">
-        <f>36.5 +15</f>
-        <v>51.5</v>
-      </c>
-      <c r="D3" s="2">
-        <f>155.34+7</f>
-        <v>162.34</v>
-      </c>
-      <c r="E3" s="2">
-        <f>33.29+10</f>
-        <v>43.29</v>
-      </c>
-      <c r="F3" s="2">
-        <f>30.42+10</f>
-        <v>40.42</v>
-      </c>
       <c r="H3" s="3"/>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.25">
@@ -581,108 +493,19 @@
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A5" s="5"/>
-      <c r="B5" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="D5" s="2">
-        <f>41.3+7</f>
-        <v>48.3</v>
-      </c>
-      <c r="E5" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="F5" s="2" t="s">
-        <v>10</v>
-      </c>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A6" s="5"/>
-      <c r="B6" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="C6" s="2">
-        <f>21.2+15</f>
-        <v>36.200000000000003</v>
-      </c>
-      <c r="D6" s="2">
-        <f>19.69+7</f>
-        <v>26.69</v>
-      </c>
-      <c r="E6" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="F6" s="2">
-        <f>19.08+10</f>
-        <v>29.08</v>
-      </c>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A7" s="5"/>
-      <c r="B7" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="C7" s="2">
-        <f>16.7+15</f>
-        <v>31.7</v>
-      </c>
-      <c r="D7" s="2">
-        <f>15.52+7</f>
-        <v>22.52</v>
-      </c>
-      <c r="E7" s="2">
-        <f>16.47+10</f>
-        <v>26.47</v>
-      </c>
-      <c r="F7" s="2" t="s">
-        <v>10</v>
-      </c>
       <c r="I7" s="4"/>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A8" s="5"/>
-      <c r="B8" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="C8" s="2">
-        <f>47.3+15</f>
-        <v>62.3</v>
-      </c>
-      <c r="D8" s="2">
-        <f>42.87+7</f>
-        <v>49.87</v>
-      </c>
-      <c r="E8" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="F8" s="2">
-        <f>43.23+10</f>
-        <v>53.23</v>
-      </c>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A9" s="5"/>
-      <c r="B9" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="C9" s="2">
-        <f>43.6+15</f>
-        <v>58.6</v>
-      </c>
-      <c r="D9" s="2">
-        <f>60.37+7</f>
-        <v>67.37</v>
-      </c>
-      <c r="E9" s="2">
-        <f>51.75+10</f>
-        <v>61.75</v>
-      </c>
-      <c r="F9" s="2">
-        <f>51.58+10</f>
-        <v>61.58</v>
-      </c>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A10" s="5"/>
@@ -1958,6 +1781,137 @@
     </row>
   </sheetData>
   <mergeCells count="144">
+    <mergeCell ref="A431:A433"/>
+    <mergeCell ref="A416:A418"/>
+    <mergeCell ref="A419:A421"/>
+    <mergeCell ref="A422:A424"/>
+    <mergeCell ref="A425:A427"/>
+    <mergeCell ref="A428:A430"/>
+    <mergeCell ref="A401:A403"/>
+    <mergeCell ref="A404:A406"/>
+    <mergeCell ref="A407:A409"/>
+    <mergeCell ref="A410:A412"/>
+    <mergeCell ref="A413:A415"/>
+    <mergeCell ref="A386:A388"/>
+    <mergeCell ref="A389:A391"/>
+    <mergeCell ref="A392:A394"/>
+    <mergeCell ref="A395:A397"/>
+    <mergeCell ref="A398:A400"/>
+    <mergeCell ref="A371:A373"/>
+    <mergeCell ref="A374:A376"/>
+    <mergeCell ref="A377:A379"/>
+    <mergeCell ref="A380:A382"/>
+    <mergeCell ref="A383:A385"/>
+    <mergeCell ref="A356:A358"/>
+    <mergeCell ref="A359:A361"/>
+    <mergeCell ref="A362:A364"/>
+    <mergeCell ref="A365:A367"/>
+    <mergeCell ref="A368:A370"/>
+    <mergeCell ref="A341:A343"/>
+    <mergeCell ref="A344:A346"/>
+    <mergeCell ref="A347:A349"/>
+    <mergeCell ref="A350:A352"/>
+    <mergeCell ref="A353:A355"/>
+    <mergeCell ref="A326:A328"/>
+    <mergeCell ref="A329:A331"/>
+    <mergeCell ref="A332:A334"/>
+    <mergeCell ref="A335:A337"/>
+    <mergeCell ref="A338:A340"/>
+    <mergeCell ref="A311:A313"/>
+    <mergeCell ref="A314:A316"/>
+    <mergeCell ref="A317:A319"/>
+    <mergeCell ref="A320:A322"/>
+    <mergeCell ref="A323:A325"/>
+    <mergeCell ref="A296:A298"/>
+    <mergeCell ref="A299:A301"/>
+    <mergeCell ref="A302:A304"/>
+    <mergeCell ref="A305:A307"/>
+    <mergeCell ref="A308:A310"/>
+    <mergeCell ref="A281:A283"/>
+    <mergeCell ref="A284:A286"/>
+    <mergeCell ref="A287:A289"/>
+    <mergeCell ref="A290:A292"/>
+    <mergeCell ref="A293:A295"/>
+    <mergeCell ref="A266:A268"/>
+    <mergeCell ref="A269:A271"/>
+    <mergeCell ref="A272:A274"/>
+    <mergeCell ref="A275:A277"/>
+    <mergeCell ref="A278:A280"/>
+    <mergeCell ref="A251:A253"/>
+    <mergeCell ref="A254:A256"/>
+    <mergeCell ref="A257:A259"/>
+    <mergeCell ref="A260:A262"/>
+    <mergeCell ref="A263:A265"/>
+    <mergeCell ref="A236:A238"/>
+    <mergeCell ref="A239:A241"/>
+    <mergeCell ref="A242:A244"/>
+    <mergeCell ref="A245:A247"/>
+    <mergeCell ref="A248:A250"/>
+    <mergeCell ref="A221:A223"/>
+    <mergeCell ref="A224:A226"/>
+    <mergeCell ref="A227:A229"/>
+    <mergeCell ref="A230:A232"/>
+    <mergeCell ref="A233:A235"/>
+    <mergeCell ref="A206:A208"/>
+    <mergeCell ref="A209:A211"/>
+    <mergeCell ref="A212:A214"/>
+    <mergeCell ref="A215:A217"/>
+    <mergeCell ref="A218:A220"/>
+    <mergeCell ref="A191:A193"/>
+    <mergeCell ref="A194:A196"/>
+    <mergeCell ref="A197:A199"/>
+    <mergeCell ref="A200:A202"/>
+    <mergeCell ref="A203:A205"/>
+    <mergeCell ref="A176:A178"/>
+    <mergeCell ref="A179:A181"/>
+    <mergeCell ref="A182:A184"/>
+    <mergeCell ref="A185:A187"/>
+    <mergeCell ref="A188:A190"/>
+    <mergeCell ref="A161:A163"/>
+    <mergeCell ref="A164:A166"/>
+    <mergeCell ref="A167:A169"/>
+    <mergeCell ref="A170:A172"/>
+    <mergeCell ref="A173:A175"/>
+    <mergeCell ref="A146:A148"/>
+    <mergeCell ref="A149:A151"/>
+    <mergeCell ref="A152:A154"/>
+    <mergeCell ref="A155:A157"/>
+    <mergeCell ref="A158:A160"/>
+    <mergeCell ref="A131:A133"/>
+    <mergeCell ref="A134:A136"/>
+    <mergeCell ref="A137:A139"/>
+    <mergeCell ref="A140:A142"/>
+    <mergeCell ref="A143:A145"/>
+    <mergeCell ref="A116:A118"/>
+    <mergeCell ref="A119:A121"/>
+    <mergeCell ref="A122:A124"/>
+    <mergeCell ref="A125:A127"/>
+    <mergeCell ref="A128:A130"/>
+    <mergeCell ref="A101:A103"/>
+    <mergeCell ref="A104:A106"/>
+    <mergeCell ref="A107:A109"/>
+    <mergeCell ref="A110:A112"/>
+    <mergeCell ref="A113:A115"/>
+    <mergeCell ref="A86:A88"/>
+    <mergeCell ref="A89:A91"/>
+    <mergeCell ref="A92:A94"/>
+    <mergeCell ref="A95:A97"/>
+    <mergeCell ref="A98:A100"/>
+    <mergeCell ref="A71:A73"/>
+    <mergeCell ref="A74:A76"/>
+    <mergeCell ref="A77:A79"/>
+    <mergeCell ref="A80:A82"/>
+    <mergeCell ref="A83:A85"/>
+    <mergeCell ref="A56:A58"/>
+    <mergeCell ref="A59:A61"/>
+    <mergeCell ref="A62:A64"/>
+    <mergeCell ref="A65:A67"/>
+    <mergeCell ref="A68:A70"/>
+    <mergeCell ref="A41:A43"/>
+    <mergeCell ref="A44:A46"/>
+    <mergeCell ref="A47:A49"/>
+    <mergeCell ref="A50:A52"/>
+    <mergeCell ref="A53:A55"/>
     <mergeCell ref="A26:A28"/>
     <mergeCell ref="A29:A31"/>
     <mergeCell ref="A32:A34"/>
@@ -1971,137 +1925,6 @@
     <mergeCell ref="A8:A10"/>
     <mergeCell ref="A11:A13"/>
     <mergeCell ref="A14:A16"/>
-    <mergeCell ref="A56:A58"/>
-    <mergeCell ref="A59:A61"/>
-    <mergeCell ref="A62:A64"/>
-    <mergeCell ref="A65:A67"/>
-    <mergeCell ref="A68:A70"/>
-    <mergeCell ref="A41:A43"/>
-    <mergeCell ref="A44:A46"/>
-    <mergeCell ref="A47:A49"/>
-    <mergeCell ref="A50:A52"/>
-    <mergeCell ref="A53:A55"/>
-    <mergeCell ref="A86:A88"/>
-    <mergeCell ref="A89:A91"/>
-    <mergeCell ref="A92:A94"/>
-    <mergeCell ref="A95:A97"/>
-    <mergeCell ref="A98:A100"/>
-    <mergeCell ref="A71:A73"/>
-    <mergeCell ref="A74:A76"/>
-    <mergeCell ref="A77:A79"/>
-    <mergeCell ref="A80:A82"/>
-    <mergeCell ref="A83:A85"/>
-    <mergeCell ref="A116:A118"/>
-    <mergeCell ref="A119:A121"/>
-    <mergeCell ref="A122:A124"/>
-    <mergeCell ref="A125:A127"/>
-    <mergeCell ref="A128:A130"/>
-    <mergeCell ref="A101:A103"/>
-    <mergeCell ref="A104:A106"/>
-    <mergeCell ref="A107:A109"/>
-    <mergeCell ref="A110:A112"/>
-    <mergeCell ref="A113:A115"/>
-    <mergeCell ref="A146:A148"/>
-    <mergeCell ref="A149:A151"/>
-    <mergeCell ref="A152:A154"/>
-    <mergeCell ref="A155:A157"/>
-    <mergeCell ref="A158:A160"/>
-    <mergeCell ref="A131:A133"/>
-    <mergeCell ref="A134:A136"/>
-    <mergeCell ref="A137:A139"/>
-    <mergeCell ref="A140:A142"/>
-    <mergeCell ref="A143:A145"/>
-    <mergeCell ref="A176:A178"/>
-    <mergeCell ref="A179:A181"/>
-    <mergeCell ref="A182:A184"/>
-    <mergeCell ref="A185:A187"/>
-    <mergeCell ref="A188:A190"/>
-    <mergeCell ref="A161:A163"/>
-    <mergeCell ref="A164:A166"/>
-    <mergeCell ref="A167:A169"/>
-    <mergeCell ref="A170:A172"/>
-    <mergeCell ref="A173:A175"/>
-    <mergeCell ref="A206:A208"/>
-    <mergeCell ref="A209:A211"/>
-    <mergeCell ref="A212:A214"/>
-    <mergeCell ref="A215:A217"/>
-    <mergeCell ref="A218:A220"/>
-    <mergeCell ref="A191:A193"/>
-    <mergeCell ref="A194:A196"/>
-    <mergeCell ref="A197:A199"/>
-    <mergeCell ref="A200:A202"/>
-    <mergeCell ref="A203:A205"/>
-    <mergeCell ref="A236:A238"/>
-    <mergeCell ref="A239:A241"/>
-    <mergeCell ref="A242:A244"/>
-    <mergeCell ref="A245:A247"/>
-    <mergeCell ref="A248:A250"/>
-    <mergeCell ref="A221:A223"/>
-    <mergeCell ref="A224:A226"/>
-    <mergeCell ref="A227:A229"/>
-    <mergeCell ref="A230:A232"/>
-    <mergeCell ref="A233:A235"/>
-    <mergeCell ref="A266:A268"/>
-    <mergeCell ref="A269:A271"/>
-    <mergeCell ref="A272:A274"/>
-    <mergeCell ref="A275:A277"/>
-    <mergeCell ref="A278:A280"/>
-    <mergeCell ref="A251:A253"/>
-    <mergeCell ref="A254:A256"/>
-    <mergeCell ref="A257:A259"/>
-    <mergeCell ref="A260:A262"/>
-    <mergeCell ref="A263:A265"/>
-    <mergeCell ref="A296:A298"/>
-    <mergeCell ref="A299:A301"/>
-    <mergeCell ref="A302:A304"/>
-    <mergeCell ref="A305:A307"/>
-    <mergeCell ref="A308:A310"/>
-    <mergeCell ref="A281:A283"/>
-    <mergeCell ref="A284:A286"/>
-    <mergeCell ref="A287:A289"/>
-    <mergeCell ref="A290:A292"/>
-    <mergeCell ref="A293:A295"/>
-    <mergeCell ref="A326:A328"/>
-    <mergeCell ref="A329:A331"/>
-    <mergeCell ref="A332:A334"/>
-    <mergeCell ref="A335:A337"/>
-    <mergeCell ref="A338:A340"/>
-    <mergeCell ref="A311:A313"/>
-    <mergeCell ref="A314:A316"/>
-    <mergeCell ref="A317:A319"/>
-    <mergeCell ref="A320:A322"/>
-    <mergeCell ref="A323:A325"/>
-    <mergeCell ref="A356:A358"/>
-    <mergeCell ref="A359:A361"/>
-    <mergeCell ref="A362:A364"/>
-    <mergeCell ref="A365:A367"/>
-    <mergeCell ref="A368:A370"/>
-    <mergeCell ref="A341:A343"/>
-    <mergeCell ref="A344:A346"/>
-    <mergeCell ref="A347:A349"/>
-    <mergeCell ref="A350:A352"/>
-    <mergeCell ref="A353:A355"/>
-    <mergeCell ref="A386:A388"/>
-    <mergeCell ref="A389:A391"/>
-    <mergeCell ref="A392:A394"/>
-    <mergeCell ref="A395:A397"/>
-    <mergeCell ref="A398:A400"/>
-    <mergeCell ref="A371:A373"/>
-    <mergeCell ref="A374:A376"/>
-    <mergeCell ref="A377:A379"/>
-    <mergeCell ref="A380:A382"/>
-    <mergeCell ref="A383:A385"/>
-    <mergeCell ref="A431:A433"/>
-    <mergeCell ref="A416:A418"/>
-    <mergeCell ref="A419:A421"/>
-    <mergeCell ref="A422:A424"/>
-    <mergeCell ref="A425:A427"/>
-    <mergeCell ref="A428:A430"/>
-    <mergeCell ref="A401:A403"/>
-    <mergeCell ref="A404:A406"/>
-    <mergeCell ref="A407:A409"/>
-    <mergeCell ref="A410:A412"/>
-    <mergeCell ref="A413:A415"/>
   </mergeCells>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" r:id="rId1"/>
